--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>26154.66</v>
+        <v>27830.090000000004</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>3769</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/12 09:36:41</v>
+        <v>2026/4/13 09:16:15</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1721,34 +1721,63 @@
         <v>510</v>
       </c>
       <c r="D43">
-        <v>90</v>
+        <v>245</v>
       </c>
       <c r="E43">
-        <v>489.94</v>
+        <v>1734.15</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1195.47</v>
       </c>
       <c r="H43">
         <v>90</v>
       </c>
       <c r="I43">
-        <v>489.94</v>
+        <v>538.68</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B44">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>527</v>
+      </c>
+      <c r="D44">
+        <v>90</v>
+      </c>
+      <c r="E44">
+        <v>431.22</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>90</v>
+      </c>
+      <c r="I44">
+        <v>431.22</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G528"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1894,7 +1923,7 @@
         <v>王郡江</v>
       </c>
       <c r="G6" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="7">
@@ -3504,7 +3533,7 @@
         <v>王涛</v>
       </c>
       <c r="G76" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="77">
@@ -4769,7 +4798,7 @@
         <v>王清月</v>
       </c>
       <c r="G131" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="132">
@@ -5551,7 +5580,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G165" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="166">
@@ -5988,7 +6017,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G184" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="185">
@@ -6057,7 +6086,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G187" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="188">
@@ -6586,7 +6615,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G210" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="211">
@@ -9231,7 +9260,7 @@
         <v>王清月</v>
       </c>
       <c r="G325" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="326">
@@ -9622,7 +9651,7 @@
         <v>王郡江</v>
       </c>
       <c r="G342" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="343">
@@ -9645,7 +9674,7 @@
         <v>王涛</v>
       </c>
       <c r="G343" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="344">
@@ -9668,7 +9697,7 @@
         <v>王郡江</v>
       </c>
       <c r="G344" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="345">
@@ -9691,7 +9720,7 @@
         <v>王涛</v>
       </c>
       <c r="G345" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="346">
@@ -9714,7 +9743,7 @@
         <v>王郡江</v>
       </c>
       <c r="G346" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="347">
@@ -9737,7 +9766,7 @@
         <v>王涛</v>
       </c>
       <c r="G347" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="348">
@@ -9760,7 +9789,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G348" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="349">
@@ -9783,7 +9812,7 @@
         <v>王涛</v>
       </c>
       <c r="G349" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="350">
@@ -9806,7 +9835,7 @@
         <v>王郡江</v>
       </c>
       <c r="G350" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="351">
@@ -9829,7 +9858,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G351" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="352">
@@ -9852,7 +9881,7 @@
         <v>王郡江</v>
       </c>
       <c r="G352" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="353">
@@ -9875,7 +9904,7 @@
         <v>王涛</v>
       </c>
       <c r="G353" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="354">
@@ -9898,7 +9927,7 @@
         <v>王郡江</v>
       </c>
       <c r="G354" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="355">
@@ -9921,7 +9950,7 @@
         <v>王涛</v>
       </c>
       <c r="G355" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="356">
@@ -9944,7 +9973,7 @@
         <v>王郡江</v>
       </c>
       <c r="G356" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="357">
@@ -9967,7 +9996,7 @@
         <v>王涛</v>
       </c>
       <c r="G357" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="358">
@@ -9990,7 +10019,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G358" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="359">
@@ -10473,7 +10502,7 @@
         <v>王郡江</v>
       </c>
       <c r="G379" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="380">
@@ -10496,7 +10525,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G380" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="381">
@@ -13512,9 +13541,400 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B512" t="str">
+        <v>20664462</v>
+      </c>
+      <c r="C512" t="str">
+        <v>满当当快餐</v>
+      </c>
+      <c r="D512" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E512" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F512" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G512" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B513" t="str">
+        <v>540951427</v>
+      </c>
+      <c r="C513" t="str">
+        <v>满当当快餐</v>
+      </c>
+      <c r="D513" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E513" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F513" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G513" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B514" t="str">
+        <v>542618964</v>
+      </c>
+      <c r="C514" t="str">
+        <v>石尚锅小馆</v>
+      </c>
+      <c r="D514" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E514" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F514" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G514" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B515" t="str">
+        <v>32512876</v>
+      </c>
+      <c r="C515" t="str">
+        <v>石尚锅小馆（石锅菜·拌饭）</v>
+      </c>
+      <c r="D515" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E515" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F515" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G515" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B516" t="str">
+        <v>32126547</v>
+      </c>
+      <c r="C516" t="str">
+        <v>闻香驴蹄子.菠菜面</v>
+      </c>
+      <c r="D516" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E516" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F516" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G516" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B517" t="str">
+        <v>533903842</v>
+      </c>
+      <c r="C517" t="str">
+        <v>闻香驴蹄子菠菜面(康定和园店)</v>
+      </c>
+      <c r="D517" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E517" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F517" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G517" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B518" t="str">
+        <v>32623360</v>
+      </c>
+      <c r="C518" t="str">
+        <v>炸货店</v>
+      </c>
+      <c r="D518" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E518" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F518" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G518" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B519" t="str">
+        <v>32326808</v>
+      </c>
+      <c r="C519" t="str">
+        <v>辣当家麻辣烫店</v>
+      </c>
+      <c r="D519" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E519" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F519" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G519" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B520" t="str">
+        <v>1338032041</v>
+      </c>
+      <c r="C520" t="str">
+        <v>沙县小吃</v>
+      </c>
+      <c r="D520" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E520" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F520" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G520" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B521" t="str">
+        <v>32490938</v>
+      </c>
+      <c r="C521" t="str">
+        <v>沙县小吃(滨海学院店)</v>
+      </c>
+      <c r="D521" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E521" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F521" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G521" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B522" t="str">
+        <v>542784353</v>
+      </c>
+      <c r="C522" t="str">
+        <v>陕E面馆</v>
+      </c>
+      <c r="D522" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E522" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F522" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G522" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B523" t="str">
+        <v>32394202</v>
+      </c>
+      <c r="C523" t="str">
+        <v>小辣椒.江西小炒</v>
+      </c>
+      <c r="D523" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E523" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F523" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G523" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B524" t="str">
+        <v>32430215</v>
+      </c>
+      <c r="C524" t="str">
+        <v>烤·百川烤肉·地摊文化</v>
+      </c>
+      <c r="D524" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E524" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F524" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G524" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B525" t="str">
+        <v>1338030215</v>
+      </c>
+      <c r="C525" t="str">
+        <v>烤·百川烤肉·地摊文化(百花汇店)</v>
+      </c>
+      <c r="D525" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E525" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F525" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G525" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B526" t="str">
+        <v>32491163</v>
+      </c>
+      <c r="C526" t="str">
+        <v>胡记小炒（小龙虾·烤鱼）</v>
+      </c>
+      <c r="D526" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E526" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F526" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G526" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B527" t="str">
+        <v>542863572</v>
+      </c>
+      <c r="C527" t="str">
+        <v>胡记小龙虾</v>
+      </c>
+      <c r="D527" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E527" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F527" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G527" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="B528" t="str">
+        <v>32411758</v>
+      </c>
+      <c r="C528" t="str">
+        <v>盛合烧烤（英雄山路店）</v>
+      </c>
+      <c r="D528" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E528" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F528" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G528" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G511"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G528"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13548,7 +13968,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-11 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-12 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>527</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>27830.090000000004</v>
+        <v>29754.99</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>4014</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/13 09:16:15</v>
+        <v>2026/4/14 09:34:56</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1724,7 +1724,7 @@
         <v>245</v>
       </c>
       <c r="E43">
-        <v>1734.15</v>
+        <v>1753.8</v>
       </c>
       <c r="F43">
         <v>155</v>
@@ -1736,7 +1736,7 @@
         <v>90</v>
       </c>
       <c r="I43">
-        <v>538.68</v>
+        <v>558.33</v>
       </c>
     </row>
     <row r="44">
@@ -1750,34 +1750,63 @@
         <v>527</v>
       </c>
       <c r="D44">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="E44">
-        <v>431.22</v>
+        <v>1915.79</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1449.45</v>
       </c>
       <c r="H44">
         <v>90</v>
       </c>
       <c r="I44">
-        <v>431.22</v>
+        <v>466.34</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B45">
+        <v>11</v>
+      </c>
+      <c r="C45">
+        <v>538</v>
+      </c>
+      <c r="D45">
+        <v>88</v>
+      </c>
+      <c r="E45">
+        <v>420.68</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>88</v>
+      </c>
+      <c r="I45">
+        <v>420.68</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G528"/>
+  <dimension ref="A1:G539"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3349,7 +3378,7 @@
         <v>王清月</v>
       </c>
       <c r="G68" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="69">
@@ -3648,7 +3677,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G81" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="82">
@@ -3786,7 +3815,7 @@
         <v>王清月</v>
       </c>
       <c r="G87" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="88">
@@ -3993,7 +4022,7 @@
         <v>王涛</v>
       </c>
       <c r="G96" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="97">
@@ -4729,7 +4758,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G128" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="129">
@@ -5626,7 +5655,7 @@
         <v>王涛</v>
       </c>
       <c r="G167" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="168">
@@ -5672,7 +5701,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G169" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="170">
@@ -6178,7 +6207,7 @@
         <v>王涛</v>
       </c>
       <c r="G191" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="192">
@@ -8869,7 +8898,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G308" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="309">
@@ -10042,7 +10071,7 @@
         <v>王郡江</v>
       </c>
       <c r="G359" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="360">
@@ -10065,7 +10094,7 @@
         <v>王郡江</v>
       </c>
       <c r="G360" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="361">
@@ -10502,7 +10531,7 @@
         <v>王郡江</v>
       </c>
       <c r="G379" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="380">
@@ -13932,9 +13961,262 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B529" t="str">
+        <v>32495217</v>
+      </c>
+      <c r="C529" t="str">
+        <v>7天小吃（面条·炒饭·盖码饭·滁州店）</v>
+      </c>
+      <c r="D529" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E529" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F529" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G529" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B530" t="str">
+        <v>32559943</v>
+      </c>
+      <c r="C530" t="str">
+        <v>恩施梅嬢嬢豆皮</v>
+      </c>
+      <c r="D530" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E530" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F530" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G530" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B531" t="str">
+        <v>543006424</v>
+      </c>
+      <c r="C531" t="str">
+        <v>恩施梅孃孃豆皮</v>
+      </c>
+      <c r="D531" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E531" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F531" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G531" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B532" t="str">
+        <v>1338575372</v>
+      </c>
+      <c r="C532" t="str">
+        <v>七天小吃(卤味面条炒饭浇头面卤味饭)(车城店)</v>
+      </c>
+      <c r="D532" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E532" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F532" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G532" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B533" t="str">
+        <v>24901592</v>
+      </c>
+      <c r="C533" t="str">
+        <v>大碗面（河东一店）</v>
+      </c>
+      <c r="D533" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E533" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F533" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G533" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B534" t="str">
+        <v>542975341</v>
+      </c>
+      <c r="C534" t="str">
+        <v>马辣鸡爪</v>
+      </c>
+      <c r="D534" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E534" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F534" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G534" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B535" t="str">
+        <v>32569758</v>
+      </c>
+      <c r="C535" t="str">
+        <v>马辣鸡爪</v>
+      </c>
+      <c r="D535" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E535" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F535" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G535" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B536" t="str">
+        <v>542683719</v>
+      </c>
+      <c r="C536" t="str">
+        <v>陕味御品肉夹馍</v>
+      </c>
+      <c r="D536" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E536" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F536" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G536" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B537" t="str">
+        <v>24310433</v>
+      </c>
+      <c r="C537" t="str">
+        <v>陕味御品肉夹馍（凉皮·米线）</v>
+      </c>
+      <c r="D537" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E537" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F537" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G537" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B538" t="str">
+        <v>32552738</v>
+      </c>
+      <c r="C538" t="str">
+        <v>正宗宜宾小烧烤</v>
+      </c>
+      <c r="D538" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E538" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F538" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G538" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B539" t="str">
+        <v>1337306032</v>
+      </c>
+      <c r="C539" t="str">
+        <v>小满足（火鸡面·卷饼炸串）</v>
+      </c>
+      <c r="D539" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E539" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F539" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G539" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G528"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G539"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13968,7 +14250,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-12 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-13 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>538</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>29754.99</v>
+        <v>31429.530000000002</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>4256</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/14 09:34:56</v>
+        <v>2026/4/15 09:16:27</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1779,34 +1779,63 @@
         <v>538</v>
       </c>
       <c r="D45">
-        <v>88</v>
+        <v>233</v>
       </c>
       <c r="E45">
-        <v>420.68</v>
+        <v>1630.68</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1179.13</v>
       </c>
       <c r="H45">
         <v>88</v>
       </c>
       <c r="I45">
-        <v>420.68</v>
+        <v>451.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B46">
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>559</v>
+      </c>
+      <c r="D46">
+        <v>97</v>
+      </c>
+      <c r="E46">
+        <v>464.54</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>97</v>
+      </c>
+      <c r="I46">
+        <v>464.54</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G539"/>
+  <dimension ref="A1:G560"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2918,7 +2947,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G48" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="49">
@@ -4252,7 +4281,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G106" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="107">
@@ -4390,7 +4419,7 @@
         <v>王郡江</v>
       </c>
       <c r="G112" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="113">
@@ -6092,7 +6121,7 @@
         <v>王涛</v>
       </c>
       <c r="G186" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="187">
@@ -6644,7 +6673,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G210" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="211">
@@ -6805,7 +6834,7 @@
         <v>王清月</v>
       </c>
       <c r="G217" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="218">
@@ -7081,7 +7110,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G229" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="230">
@@ -8001,7 +8030,7 @@
         <v>王郡江</v>
       </c>
       <c r="G269" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="270">
@@ -8162,7 +8191,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G276" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="277">
@@ -8967,7 +8996,7 @@
         <v>王涛</v>
       </c>
       <c r="G311" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="312">
@@ -8990,7 +9019,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G312" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="313">
@@ -9427,7 +9456,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G331" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="332">
@@ -9680,7 +9709,7 @@
         <v>王郡江</v>
       </c>
       <c r="G342" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="343">
@@ -9933,7 +9962,7 @@
         <v>王涛</v>
       </c>
       <c r="G353" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="354">
@@ -10508,7 +10537,7 @@
         <v>王清月</v>
       </c>
       <c r="G378" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="379">
@@ -12739,7 +12768,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G475" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="476">
@@ -12877,7 +12906,7 @@
         <v>王清月</v>
       </c>
       <c r="G481" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="482">
@@ -13475,7 +13504,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G507" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="508">
@@ -13843,7 +13872,7 @@
         <v>王郡江</v>
       </c>
       <c r="G523" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="524">
@@ -14214,9 +14243,492 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B540" t="str">
+        <v>32326079</v>
+      </c>
+      <c r="C540" t="str">
+        <v>嗨饺手工水饺</v>
+      </c>
+      <c r="D540" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E540" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F540" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G540" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B541" t="str">
+        <v>32365910</v>
+      </c>
+      <c r="C541" t="str">
+        <v>淮南子鲜烫牛肉汤</v>
+      </c>
+      <c r="D541" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E541" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F541" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G541" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B542" t="str">
+        <v>1334958893</v>
+      </c>
+      <c r="C542" t="str">
+        <v>查特熊(海西路店)</v>
+      </c>
+      <c r="D542" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E542" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F542" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G542" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B543" t="str">
+        <v>32469605</v>
+      </c>
+      <c r="C543" t="str">
+        <v>史记龙虾（雨顺佳园店）</v>
+      </c>
+      <c r="D543" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E543" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F543" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G543" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B544" t="str">
+        <v>32440832</v>
+      </c>
+      <c r="C544" t="str">
+        <v>满诚香饺子王</v>
+      </c>
+      <c r="D544" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E544" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F544" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G544" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B545" t="str">
+        <v>32220644</v>
+      </c>
+      <c r="C545" t="str">
+        <v>牛肉小馆（小龙虾.炒码粉）</v>
+      </c>
+      <c r="D545" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E545" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F545" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G545" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B546" t="str">
+        <v>31327148</v>
+      </c>
+      <c r="C546" t="str">
+        <v>小输胜·麺屋（义乌店）</v>
+      </c>
+      <c r="D546" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E546" t="str">
+        <v>屈维涛</v>
+      </c>
+      <c r="F546" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G546" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B547" t="str">
+        <v>1319751638</v>
+      </c>
+      <c r="C547" t="str">
+        <v>小输胜麺屋</v>
+      </c>
+      <c r="D547" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E547" t="str">
+        <v>屈维涛</v>
+      </c>
+      <c r="F547" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G547" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B548" t="str">
+        <v>542290945</v>
+      </c>
+      <c r="C548" t="str">
+        <v>马一洒河州特色包子</v>
+      </c>
+      <c r="D548" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E548" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F548" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G548" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B549" t="str">
+        <v>32618785</v>
+      </c>
+      <c r="C549" t="str">
+        <v>小萌烤肉盒子</v>
+      </c>
+      <c r="D549" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E549" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F549" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G549" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B550" t="str">
+        <v>1335812500</v>
+      </c>
+      <c r="C550" t="str">
+        <v>小萌烤肉盒子</v>
+      </c>
+      <c r="D550" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E550" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F550" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G550" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B551" t="str">
+        <v>542691306</v>
+      </c>
+      <c r="C551" t="str">
+        <v>VShow</v>
+      </c>
+      <c r="D551" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E551" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F551" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G551" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B552" t="str">
+        <v>1337819602</v>
+      </c>
+      <c r="C552" t="str">
+        <v>小曹面食</v>
+      </c>
+      <c r="D552" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E552" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F552" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G552" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B553" t="str">
+        <v>31480405</v>
+      </c>
+      <c r="C553" t="str">
+        <v>熊记·手工绿豆饼</v>
+      </c>
+      <c r="D553" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E553" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F553" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G553" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B554" t="str">
+        <v>32462394</v>
+      </c>
+      <c r="C554" t="str">
+        <v>盖食英雄盖饭（花果园店）</v>
+      </c>
+      <c r="D554" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E554" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F554" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G554" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B555" t="str">
+        <v>32452336</v>
+      </c>
+      <c r="C555" t="str">
+        <v>汕尾小吃</v>
+      </c>
+      <c r="D555" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E555" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F555" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G555" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B556" t="str">
+        <v>523311983</v>
+      </c>
+      <c r="C556" t="str">
+        <v>黔西沙窝牛肉粉(贵阳市十分店)</v>
+      </c>
+      <c r="D556" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E556" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F556" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G556" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B557" t="str">
+        <v>1338098902</v>
+      </c>
+      <c r="C557" t="str">
+        <v>東北老式麻辣烫(吾悦店)</v>
+      </c>
+      <c r="D557" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E557" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F557" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G557" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B558" t="str">
+        <v>32492387</v>
+      </c>
+      <c r="C558" t="str">
+        <v>東北麻辣烫（吾悦广场店）</v>
+      </c>
+      <c r="D558" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E558" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F558" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G558" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B559" t="str">
+        <v>32325196</v>
+      </c>
+      <c r="C559" t="str">
+        <v>小满足(火鸡面.卷饼炸串)</v>
+      </c>
+      <c r="D559" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E559" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F559" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G559" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B560" t="str">
+        <v>1334934729</v>
+      </c>
+      <c r="C560" t="str">
+        <v>宜宾燃面(邦泰五期店)</v>
+      </c>
+      <c r="D560" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E560" t="str">
+        <v>朱雯雯</v>
+      </c>
+      <c r="F560" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G560" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G539"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G560"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14250,7 +14762,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-13 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-14 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>559</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>31429.530000000002</v>
+        <v>33204</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>4498</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/15 09:16:27</v>
+        <v>2026/4/16 15:12:20</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1782,7 +1782,7 @@
         <v>233</v>
       </c>
       <c r="E45">
-        <v>1630.68</v>
+        <v>1663.65</v>
       </c>
       <c r="F45">
         <v>145</v>
@@ -1794,7 +1794,7 @@
         <v>88</v>
       </c>
       <c r="I45">
-        <v>451.55</v>
+        <v>484.52</v>
       </c>
     </row>
     <row r="46">
@@ -1808,34 +1808,63 @@
         <v>559</v>
       </c>
       <c r="D46">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="E46">
-        <v>464.54</v>
+        <v>1743.73</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1230.93</v>
       </c>
       <c r="H46">
         <v>97</v>
       </c>
       <c r="I46">
-        <v>464.54</v>
+        <v>512.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B47">
+        <v>27</v>
+      </c>
+      <c r="C47">
+        <v>586</v>
+      </c>
+      <c r="D47">
+        <v>96</v>
+      </c>
+      <c r="E47">
+        <v>462.31</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>96</v>
+      </c>
+      <c r="I47">
+        <v>462.31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G560"/>
+  <dimension ref="A1:G587"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2694,7 +2723,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G37" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="38">
@@ -2740,7 +2769,7 @@
         <v>王涛</v>
       </c>
       <c r="G39" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="40">
@@ -2809,7 +2838,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G42" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="43">
@@ -3890,7 +3919,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G89" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="90">
@@ -4718,7 +4747,7 @@
         <v>王郡江</v>
       </c>
       <c r="G125" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="126">
@@ -5339,7 +5368,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G152" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="153">
@@ -5983,7 +6012,7 @@
         <v>王清月</v>
       </c>
       <c r="G180" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="181">
@@ -6696,7 +6725,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G211" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="212">
@@ -7156,7 +7185,7 @@
         <v>王涛</v>
       </c>
       <c r="G231" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="232">
@@ -7478,7 +7507,7 @@
         <v>王清月</v>
       </c>
       <c r="G245" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="246">
@@ -9962,7 +9991,7 @@
         <v>王涛</v>
       </c>
       <c r="G353" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="354">
@@ -10146,7 +10175,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G361" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="362">
@@ -10169,7 +10198,7 @@
         <v>王清月</v>
       </c>
       <c r="G362" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="363">
@@ -10192,7 +10221,7 @@
         <v>王清月</v>
       </c>
       <c r="G363" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="364">
@@ -10215,7 +10244,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G364" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="365">
@@ -10238,7 +10267,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G365" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="366">
@@ -10261,7 +10290,7 @@
         <v>王清月</v>
       </c>
       <c r="G366" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="367">
@@ -10284,7 +10313,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G367" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="368">
@@ -10307,7 +10336,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G368" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="369">
@@ -10330,7 +10359,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G369" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="370">
@@ -10353,7 +10382,7 @@
         <v>王清月</v>
       </c>
       <c r="G370" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="371">
@@ -10422,7 +10451,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G373" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="374">
@@ -10468,7 +10497,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G375" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="376">
@@ -10491,7 +10520,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G376" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="377">
@@ -10767,7 +10796,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G388" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="389">
@@ -10928,7 +10957,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G395" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="396">
@@ -12331,7 +12360,7 @@
         <v>王清月</v>
       </c>
       <c r="G456" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="457">
@@ -12538,7 +12567,7 @@
         <v>王郡江</v>
       </c>
       <c r="G465" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="466">
@@ -12768,7 +12797,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G475" t="str">
-        <v>已解约</v>
+        <v>新店</v>
       </c>
     </row>
     <row r="476">
@@ -14148,7 +14177,7 @@
         <v>王清月</v>
       </c>
       <c r="G535" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="536">
@@ -14355,7 +14384,7 @@
         <v>王清月</v>
       </c>
       <c r="G544" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="545">
@@ -14470,7 +14499,7 @@
         <v>王清月</v>
       </c>
       <c r="G549" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="550">
@@ -14507,7 +14536,7 @@
         <v>VShow</v>
       </c>
       <c r="D551" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E551" t="str">
         <v>武力力</v>
@@ -14726,9 +14755,630 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B561" t="str">
+        <v>32344508</v>
+      </c>
+      <c r="C561" t="str">
+        <v>锦霞粉吧</v>
+      </c>
+      <c r="D561" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E561" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F561" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G561" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B562" t="str">
+        <v>1334807636</v>
+      </c>
+      <c r="C562" t="str">
+        <v>锦霞粉吧</v>
+      </c>
+      <c r="D562" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E562" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F562" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G562" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B563" t="str">
+        <v>1338055550</v>
+      </c>
+      <c r="C563" t="str">
+        <v>龚道烧烤(小溪塔店)</v>
+      </c>
+      <c r="D563" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E563" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F563" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G563" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B564" t="str">
+        <v>542873750</v>
+      </c>
+      <c r="C564" t="str">
+        <v>好旺角碳火烧烤</v>
+      </c>
+      <c r="D564" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E564" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F564" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G564" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B565" t="str">
+        <v>32530789</v>
+      </c>
+      <c r="C565" t="str">
+        <v>童记六马风味馆（安顺二分店）</v>
+      </c>
+      <c r="D565" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E565" t="str">
+        <v>贺蓓</v>
+      </c>
+      <c r="F565" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G565" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B566" t="str">
+        <v>1337305484</v>
+      </c>
+      <c r="C566" t="str">
+        <v>边边圆炸鸡汉堡</v>
+      </c>
+      <c r="D566" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E566" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F566" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G566" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B567" t="str">
+        <v>32438153</v>
+      </c>
+      <c r="C567" t="str">
+        <v>边边圆炸鸡汉堡（滨江店）</v>
+      </c>
+      <c r="D567" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E567" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F567" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G567" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B568" t="str">
+        <v>1339042989</v>
+      </c>
+      <c r="C568" t="str">
+        <v>憨妈小馆</v>
+      </c>
+      <c r="D568" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E568" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F568" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G568" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B569" t="str">
+        <v>32677481</v>
+      </c>
+      <c r="C569" t="str">
+        <v>憨妈小馆</v>
+      </c>
+      <c r="D569" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E569" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F569" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G569" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B570" t="str">
+        <v>31968694</v>
+      </c>
+      <c r="C570" t="str">
+        <v>江小排老味黑鱼排</v>
+      </c>
+      <c r="D570" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E570" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F570" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G570" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B571" t="str">
+        <v>542474360</v>
+      </c>
+      <c r="C571" t="str">
+        <v>姜姜好热卤(保利店)</v>
+      </c>
+      <c r="D571" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E571" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F571" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G571" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B572" t="str">
+        <v>32519441</v>
+      </c>
+      <c r="C572" t="str">
+        <v>老孟卤味怪（麻辣鸭货）</v>
+      </c>
+      <c r="D572" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E572" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F572" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G572" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B573" t="str">
+        <v>32549423</v>
+      </c>
+      <c r="C573" t="str">
+        <v>千禧龍虾煌•虾尾•爆汁龙虾</v>
+      </c>
+      <c r="D573" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E573" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F573" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G573" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B574" t="str">
+        <v>32200488</v>
+      </c>
+      <c r="C574" t="str">
+        <v>谢记麻辣铁板烧</v>
+      </c>
+      <c r="D574" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E574" t="str">
+        <v>汪双</v>
+      </c>
+      <c r="F574" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G574" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B575" t="str">
+        <v>1334816338</v>
+      </c>
+      <c r="C575" t="str">
+        <v>谢记麻辣铁板烧</v>
+      </c>
+      <c r="D575" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E575" t="str">
+        <v>汪双</v>
+      </c>
+      <c r="F575" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G575" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B576" t="str">
+        <v>32220682</v>
+      </c>
+      <c r="C576" t="str">
+        <v>半山小厨（热炒盖浇饭）</v>
+      </c>
+      <c r="D576" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E576" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F576" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G576" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B577" t="str">
+        <v>543095623</v>
+      </c>
+      <c r="C577" t="str">
+        <v>闽派·馄饨粉面铺</v>
+      </c>
+      <c r="D577" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E577" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F577" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G577" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B578" t="str">
+        <v>32581744</v>
+      </c>
+      <c r="C578" t="str">
+        <v>闽派馄饨粉面铺</v>
+      </c>
+      <c r="D578" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E578" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F578" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G578" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B579" t="str">
+        <v>32478245</v>
+      </c>
+      <c r="C579" t="str">
+        <v>湘聚江湖</v>
+      </c>
+      <c r="D579" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E579" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F579" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G579" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B580" t="str">
+        <v>32515884</v>
+      </c>
+      <c r="C580" t="str">
+        <v>香香炸串（炸鸡皮，鸡排）</v>
+      </c>
+      <c r="D580" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E580" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F580" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G580" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B581" t="str">
+        <v>1334033022</v>
+      </c>
+      <c r="C581" t="str">
+        <v>亚辉美蛙鱼</v>
+      </c>
+      <c r="D581" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E581" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F581" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G581" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B582" t="str">
+        <v>32424932</v>
+      </c>
+      <c r="C582" t="str">
+        <v>亚辉美蛙鱼大排档</v>
+      </c>
+      <c r="D582" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E582" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F582" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G582" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B583" t="str">
+        <v>32497363</v>
+      </c>
+      <c r="C583" t="str">
+        <v>正隆牛肉面</v>
+      </c>
+      <c r="D583" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E583" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F583" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G583" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B584" t="str">
+        <v>32176383</v>
+      </c>
+      <c r="C584" t="str">
+        <v>特色马岗豉油鹅（文昌市场店）</v>
+      </c>
+      <c r="D584" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E584" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F584" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G584" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B585" t="str">
+        <v>32590990</v>
+      </c>
+      <c r="C585" t="str">
+        <v>韩家大包（牡丹路店）</v>
+      </c>
+      <c r="D585" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E585" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F585" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G585" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B586" t="str">
+        <v>31947910</v>
+      </c>
+      <c r="C586" t="str">
+        <v>老母鸡汤面(黄焖鸡米饭）</v>
+      </c>
+      <c r="D586" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E586" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F586" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G586" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B587" t="str">
+        <v>542291482</v>
+      </c>
+      <c r="C587" t="str">
+        <v>辛营刘园老母鸡汤面黄焖鸡米饭</v>
+      </c>
+      <c r="D587" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E587" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F587" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G587" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G560"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G587"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14762,7 +15412,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-14 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-15 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>586</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>33204</v>
+        <v>35040.46000000001</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>4749</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/16 15:12:20</v>
+        <v>2026/4/17 09:26:49</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1028,7 +1028,7 @@
         <v>72</v>
       </c>
       <c r="E19">
-        <v>490.14</v>
+        <v>490.67</v>
       </c>
       <c r="F19">
         <v>57</v>
@@ -1040,7 +1040,7 @@
         <v>15</v>
       </c>
       <c r="I19">
-        <v>60.4</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="20">
@@ -1086,7 +1086,7 @@
         <v>99</v>
       </c>
       <c r="E21">
-        <v>767.18</v>
+        <v>768.32</v>
       </c>
       <c r="F21">
         <v>71</v>
@@ -1098,7 +1098,7 @@
         <v>28</v>
       </c>
       <c r="I21">
-        <v>168.57</v>
+        <v>169.71</v>
       </c>
     </row>
     <row r="22">
@@ -1144,7 +1144,7 @@
         <v>98</v>
       </c>
       <c r="E23">
-        <v>701.4</v>
+        <v>702.62</v>
       </c>
       <c r="F23">
         <v>69</v>
@@ -1156,7 +1156,7 @@
         <v>29</v>
       </c>
       <c r="I23">
-        <v>141.18</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="24">
@@ -1173,7 +1173,7 @@
         <v>107</v>
       </c>
       <c r="E24">
-        <v>774.85</v>
+        <v>776.34</v>
       </c>
       <c r="F24">
         <v>73</v>
@@ -1185,7 +1185,7 @@
         <v>34</v>
       </c>
       <c r="I24">
-        <v>219.69</v>
+        <v>221.18</v>
       </c>
     </row>
     <row r="25">
@@ -1231,7 +1231,7 @@
         <v>115</v>
       </c>
       <c r="E26">
-        <v>737.3</v>
+        <v>739.48</v>
       </c>
       <c r="F26">
         <v>77</v>
@@ -1243,7 +1243,7 @@
         <v>38</v>
       </c>
       <c r="I26">
-        <v>216.33</v>
+        <v>218.51</v>
       </c>
     </row>
     <row r="27">
@@ -1260,7 +1260,7 @@
         <v>125</v>
       </c>
       <c r="E27">
-        <v>828.27</v>
+        <v>829.61</v>
       </c>
       <c r="F27">
         <v>83</v>
@@ -1272,7 +1272,7 @@
         <v>42</v>
       </c>
       <c r="I27">
-        <v>235</v>
+        <v>236.34</v>
       </c>
     </row>
     <row r="28">
@@ -1318,7 +1318,7 @@
         <v>128</v>
       </c>
       <c r="E29">
-        <v>1034.6</v>
+        <v>1036.34</v>
       </c>
       <c r="F29">
         <v>83</v>
@@ -1330,7 +1330,7 @@
         <v>45</v>
       </c>
       <c r="I29">
-        <v>282.26</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
@@ -1376,7 +1376,7 @@
         <v>127</v>
       </c>
       <c r="E31">
-        <v>910.38</v>
+        <v>910.95</v>
       </c>
       <c r="F31">
         <v>84</v>
@@ -1388,7 +1388,7 @@
         <v>43</v>
       </c>
       <c r="I31">
-        <v>194.84</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="32">
@@ -1405,7 +1405,7 @@
         <v>150</v>
       </c>
       <c r="E32">
-        <v>971.36</v>
+        <v>975.03</v>
       </c>
       <c r="F32">
         <v>97</v>
@@ -1417,7 +1417,7 @@
         <v>53</v>
       </c>
       <c r="I32">
-        <v>260.54</v>
+        <v>264.21</v>
       </c>
     </row>
     <row r="33">
@@ -1724,7 +1724,7 @@
         <v>245</v>
       </c>
       <c r="E43">
-        <v>1753.8</v>
+        <v>1755.59</v>
       </c>
       <c r="F43">
         <v>155</v>
@@ -1736,7 +1736,7 @@
         <v>90</v>
       </c>
       <c r="I43">
-        <v>558.33</v>
+        <v>560.12</v>
       </c>
     </row>
     <row r="44">
@@ -1811,7 +1811,7 @@
         <v>252</v>
       </c>
       <c r="E46">
-        <v>1743.73</v>
+        <v>1751.89</v>
       </c>
       <c r="F46">
         <v>155</v>
@@ -1823,7 +1823,7 @@
         <v>97</v>
       </c>
       <c r="I46">
-        <v>512.8</v>
+        <v>520.96</v>
       </c>
     </row>
     <row r="47">
@@ -1837,34 +1837,63 @@
         <v>586</v>
       </c>
       <c r="D47">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="E47">
-        <v>462.31</v>
+        <v>1742.91</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1178.79</v>
       </c>
       <c r="H47">
         <v>96</v>
       </c>
       <c r="I47">
-        <v>462.31</v>
+        <v>564.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B48">
+        <v>23</v>
+      </c>
+      <c r="C48">
+        <v>609</v>
+      </c>
+      <c r="D48">
+        <v>108</v>
+      </c>
+      <c r="E48">
+        <v>532.03</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>108</v>
+      </c>
+      <c r="I48">
+        <v>532.03</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G587"/>
+  <dimension ref="A1:G610"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2217,7 +2246,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G15" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="16">
@@ -2861,7 +2890,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G43" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="44">
@@ -6633,7 +6662,7 @@
         <v>王涛</v>
       </c>
       <c r="G207" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="208">
@@ -7300,7 +7329,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G236" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="237">
@@ -7530,7 +7559,7 @@
         <v>王清月</v>
       </c>
       <c r="G246" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="247">
@@ -8381,7 +8410,7 @@
         <v>王涛</v>
       </c>
       <c r="G283" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="284">
@@ -10129,7 +10158,7 @@
         <v>王郡江</v>
       </c>
       <c r="G359" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="360">
@@ -10405,7 +10434,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G371" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="372">
@@ -10428,7 +10457,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G372" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="373">
@@ -10474,7 +10503,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G374" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="375">
@@ -10543,7 +10572,7 @@
         <v>王清月</v>
       </c>
       <c r="G377" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="378">
@@ -10635,7 +10664,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G381" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="382">
@@ -10658,7 +10687,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G382" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="383">
@@ -10681,7 +10710,7 @@
         <v>王涛</v>
       </c>
       <c r="G383" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="384">
@@ -10704,7 +10733,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G384" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="385">
@@ -10727,7 +10756,7 @@
         <v>王清月</v>
       </c>
       <c r="G385" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="386">
@@ -10750,7 +10779,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G386" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="387">
@@ -10773,7 +10802,7 @@
         <v>王涛</v>
       </c>
       <c r="G387" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="388">
@@ -10819,7 +10848,7 @@
         <v>王清月</v>
       </c>
       <c r="G389" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="390">
@@ -10842,7 +10871,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G390" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="391">
@@ -10865,7 +10894,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G391" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="392">
@@ -10888,7 +10917,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G392" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="393">
@@ -10911,7 +10940,7 @@
         <v>王郡江</v>
       </c>
       <c r="G393" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="394">
@@ -10934,7 +10963,7 @@
         <v>王清月</v>
       </c>
       <c r="G394" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="395">
@@ -10980,7 +11009,7 @@
         <v>王涛</v>
       </c>
       <c r="G396" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="397">
@@ -11187,7 +11216,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G405" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="406">
@@ -11233,7 +11262,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G407" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="408">
@@ -11256,7 +11285,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G408" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="409">
@@ -11348,7 +11377,7 @@
         <v>王郡江</v>
       </c>
       <c r="G412" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="413">
@@ -11394,7 +11423,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G414" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="415">
@@ -11417,7 +11446,7 @@
         <v>王清月</v>
       </c>
       <c r="G415" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="416">
@@ -11440,7 +11469,7 @@
         <v>王郡江</v>
       </c>
       <c r="G416" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="417">
@@ -11486,7 +11515,7 @@
         <v>王清月</v>
       </c>
       <c r="G418" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="419">
@@ -11601,7 +11630,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G423" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="424">
@@ -11647,7 +11676,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G425" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="426">
@@ -11670,7 +11699,7 @@
         <v>王清月</v>
       </c>
       <c r="G426" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="427">
@@ -12153,7 +12182,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G447" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="448">
@@ -14660,7 +14689,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G556" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="557">
@@ -14890,7 +14919,7 @@
         <v>王郡江</v>
       </c>
       <c r="G566" t="str">
-        <v>已解约</v>
+        <v>新店</v>
       </c>
     </row>
     <row r="567">
@@ -15028,7 +15057,7 @@
         <v>王郡江</v>
       </c>
       <c r="G572" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="573">
@@ -15376,9 +15405,538 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B588" t="str">
+        <v>1338087890</v>
+      </c>
+      <c r="C588" t="str">
+        <v>金豆烧烤(斗南花街店)</v>
+      </c>
+      <c r="D588" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E588" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F588" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G588" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B589" t="str">
+        <v>32616664</v>
+      </c>
+      <c r="C589" t="str">
+        <v>胖妞小锅米线</v>
+      </c>
+      <c r="D589" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E589" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F589" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G589" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B590" t="str">
+        <v>32584949</v>
+      </c>
+      <c r="C590" t="str">
+        <v>水木西门龙虾烧烤（滨湖店）</v>
+      </c>
+      <c r="D590" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E590" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F590" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G590" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B591" t="str">
+        <v>542555814</v>
+      </c>
+      <c r="C591" t="str">
+        <v>云老板·文山酸汤米线·麻辣鸡米线</v>
+      </c>
+      <c r="D591" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E591" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F591" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G591" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B592" t="str">
+        <v>542891796</v>
+      </c>
+      <c r="C592" t="str">
+        <v>童记六马风味馆</v>
+      </c>
+      <c r="D592" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E592" t="str">
+        <v>贺蓓</v>
+      </c>
+      <c r="F592" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G592" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B593" t="str">
+        <v>32542555</v>
+      </c>
+      <c r="C593" t="str">
+        <v>小高手工辣条店（林枫店）</v>
+      </c>
+      <c r="D593" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E593" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F593" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G593" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B594" t="str">
+        <v>31958065</v>
+      </c>
+      <c r="C594" t="str">
+        <v>阿朵妹·特色麻酱砂锅(未央店)</v>
+      </c>
+      <c r="D594" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E594" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F594" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G594" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B595" t="str">
+        <v>542836977</v>
+      </c>
+      <c r="C595" t="str">
+        <v>串滋滋</v>
+      </c>
+      <c r="D595" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E595" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F595" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G595" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B596" t="str">
+        <v>32340880</v>
+      </c>
+      <c r="C596" t="str">
+        <v>串滋滋炸串</v>
+      </c>
+      <c r="D596" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E596" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F596" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G596" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B597" t="str">
+        <v>32593819</v>
+      </c>
+      <c r="C597" t="str">
+        <v>豚食天地</v>
+      </c>
+      <c r="D597" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E597" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F597" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G597" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B598" t="str">
+        <v>543003721</v>
+      </c>
+      <c r="C598" t="str">
+        <v>辣么好·麻辣冷吃</v>
+      </c>
+      <c r="D598" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E598" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F598" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G598" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B599" t="str">
+        <v>32370885</v>
+      </c>
+      <c r="C599" t="str">
+        <v>厦门老八市·阿杰餐厅</v>
+      </c>
+      <c r="D599" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E599" t="str">
+        <v>屈维涛</v>
+      </c>
+      <c r="F599" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G599" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B600" t="str">
+        <v>31224528</v>
+      </c>
+      <c r="C600" t="str">
+        <v>成洋洋古蔺麻辣鸡（泸州店）</v>
+      </c>
+      <c r="D600" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E600" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F600" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G600" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B601" t="str">
+        <v>32455725</v>
+      </c>
+      <c r="C601" t="str">
+        <v>香满园麻辣拌·熏拌鸡架麻酱拌面</v>
+      </c>
+      <c r="D601" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E601" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F601" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G601" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B602" t="str">
+        <v>32377332</v>
+      </c>
+      <c r="C602" t="str">
+        <v>李记炸串卷饼·旦旦面</v>
+      </c>
+      <c r="D602" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E602" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F602" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G602" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B603" t="str">
+        <v>31630868</v>
+      </c>
+      <c r="C603" t="str">
+        <v>美滋美味家常菜</v>
+      </c>
+      <c r="D603" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E603" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F603" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G603" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B604" t="str">
+        <v>32604933</v>
+      </c>
+      <c r="C604" t="str">
+        <v>大水井•美蛙鱼•火锅</v>
+      </c>
+      <c r="D604" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E604" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F604" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G604" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B605" t="str">
+        <v>1331570298</v>
+      </c>
+      <c r="C605" t="str">
+        <v>西安剁椒面</v>
+      </c>
+      <c r="D605" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E605" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F605" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G605" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B606" t="str">
+        <v>21643286</v>
+      </c>
+      <c r="C606" t="str">
+        <v>5678肥蛤炒鸡家常菜</v>
+      </c>
+      <c r="D606" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E606" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F606" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G606" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B607" t="str">
+        <v>32262852</v>
+      </c>
+      <c r="C607" t="str">
+        <v>兰姑娘骨汤牛肉面（盖浇饭）</v>
+      </c>
+      <c r="D607" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E607" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F607" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G607" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B608" t="str">
+        <v>32439074</v>
+      </c>
+      <c r="C608" t="str">
+        <v>许村老头小吃（酒酿，酒酿馒头）</v>
+      </c>
+      <c r="D608" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E608" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F608" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G608" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B609" t="str">
+        <v>32452570</v>
+      </c>
+      <c r="C609" t="str">
+        <v>一品窝子面</v>
+      </c>
+      <c r="D609" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E609" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F609" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G609" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B610" t="str">
+        <v>1328582584</v>
+      </c>
+      <c r="C610" t="str">
+        <v>一品窝子面</v>
+      </c>
+      <c r="D610" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E610" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F610" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G610" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G587"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G610"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15412,7 +15970,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-15 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-16 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-19</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>609</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>35040.46000000001</v>
+        <v>41457.740000000005</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>5019</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/17 09:26:49</v>
+        <v>2026/4/20 10:46:51</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I51"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -883,7 +883,7 @@
         <v>48</v>
       </c>
       <c r="E14">
-        <v>345.2</v>
+        <v>346.94</v>
       </c>
       <c r="F14">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="I14">
-        <v>74.07</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="15">
@@ -912,7 +912,7 @@
         <v>60</v>
       </c>
       <c r="E15">
-        <v>488.94</v>
+        <v>489.6</v>
       </c>
       <c r="F15">
         <v>40</v>
@@ -924,7 +924,7 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>150.06</v>
+        <v>150.72</v>
       </c>
     </row>
     <row r="16">
@@ -941,7 +941,7 @@
         <v>63</v>
       </c>
       <c r="E16">
-        <v>434.16</v>
+        <v>435.09</v>
       </c>
       <c r="F16">
         <v>45</v>
@@ -953,7 +953,7 @@
         <v>18</v>
       </c>
       <c r="I16">
-        <v>93.35</v>
+        <v>94.28</v>
       </c>
     </row>
     <row r="17">
@@ -970,7 +970,7 @@
         <v>61</v>
       </c>
       <c r="E17">
-        <v>352.39</v>
+        <v>354.41</v>
       </c>
       <c r="F17">
         <v>47</v>
@@ -982,7 +982,7 @@
         <v>14</v>
       </c>
       <c r="I17">
-        <v>65.94</v>
+        <v>67.96</v>
       </c>
     </row>
     <row r="18">
@@ -1028,7 +1028,7 @@
         <v>72</v>
       </c>
       <c r="E19">
-        <v>490.67</v>
+        <v>493.32</v>
       </c>
       <c r="F19">
         <v>57</v>
@@ -1040,7 +1040,7 @@
         <v>15</v>
       </c>
       <c r="I19">
-        <v>60.93</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="20">
@@ -1057,7 +1057,7 @@
         <v>85</v>
       </c>
       <c r="E20">
-        <v>570.97</v>
+        <v>576.41</v>
       </c>
       <c r="F20">
         <v>63</v>
@@ -1069,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="I20">
-        <v>140.68</v>
+        <v>146.12</v>
       </c>
     </row>
     <row r="21">
@@ -1086,7 +1086,7 @@
         <v>99</v>
       </c>
       <c r="E21">
-        <v>768.32</v>
+        <v>770.67</v>
       </c>
       <c r="F21">
         <v>71</v>
@@ -1098,7 +1098,7 @@
         <v>28</v>
       </c>
       <c r="I21">
-        <v>169.71</v>
+        <v>172.06</v>
       </c>
     </row>
     <row r="22">
@@ -1144,7 +1144,7 @@
         <v>98</v>
       </c>
       <c r="E23">
-        <v>702.62</v>
+        <v>705.33</v>
       </c>
       <c r="F23">
         <v>69</v>
@@ -1156,7 +1156,7 @@
         <v>29</v>
       </c>
       <c r="I23">
-        <v>142.4</v>
+        <v>145.11</v>
       </c>
     </row>
     <row r="24">
@@ -1173,7 +1173,7 @@
         <v>107</v>
       </c>
       <c r="E24">
-        <v>776.34</v>
+        <v>777.71</v>
       </c>
       <c r="F24">
         <v>73</v>
@@ -1185,7 +1185,7 @@
         <v>34</v>
       </c>
       <c r="I24">
-        <v>221.18</v>
+        <v>222.55</v>
       </c>
     </row>
     <row r="25">
@@ -1231,7 +1231,7 @@
         <v>115</v>
       </c>
       <c r="E26">
-        <v>739.48</v>
+        <v>740.78</v>
       </c>
       <c r="F26">
         <v>77</v>
@@ -1243,7 +1243,7 @@
         <v>38</v>
       </c>
       <c r="I26">
-        <v>218.51</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="27">
@@ -1347,7 +1347,7 @@
         <v>133</v>
       </c>
       <c r="E30">
-        <v>1094.44</v>
+        <v>1095</v>
       </c>
       <c r="F30">
         <v>84</v>
@@ -1359,7 +1359,7 @@
         <v>49</v>
       </c>
       <c r="I30">
-        <v>302.11</v>
+        <v>302.67</v>
       </c>
     </row>
     <row r="31">
@@ -1405,7 +1405,7 @@
         <v>150</v>
       </c>
       <c r="E32">
-        <v>975.03</v>
+        <v>975.8</v>
       </c>
       <c r="F32">
         <v>97</v>
@@ -1417,7 +1417,7 @@
         <v>53</v>
       </c>
       <c r="I32">
-        <v>264.21</v>
+        <v>264.98</v>
       </c>
     </row>
     <row r="33">
@@ -1492,7 +1492,7 @@
         <v>155</v>
       </c>
       <c r="E35">
-        <v>1162.3</v>
+        <v>1163.2</v>
       </c>
       <c r="F35">
         <v>103</v>
@@ -1504,7 +1504,7 @@
         <v>52</v>
       </c>
       <c r="I35">
-        <v>306.82</v>
+        <v>307.72</v>
       </c>
     </row>
     <row r="36">
@@ -1579,7 +1579,7 @@
         <v>154</v>
       </c>
       <c r="E38">
-        <v>1144.19</v>
+        <v>1147</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -1591,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="I38">
-        <v>309.41</v>
+        <v>312.22</v>
       </c>
     </row>
     <row r="39">
@@ -1637,7 +1637,7 @@
         <v>175</v>
       </c>
       <c r="E40">
-        <v>1198.87</v>
+        <v>1200.37</v>
       </c>
       <c r="F40">
         <v>119</v>
@@ -1649,7 +1649,7 @@
         <v>56</v>
       </c>
       <c r="I40">
-        <v>286.95</v>
+        <v>288.45</v>
       </c>
     </row>
     <row r="41">
@@ -1666,7 +1666,7 @@
         <v>194</v>
       </c>
       <c r="E41">
-        <v>1285.08</v>
+        <v>1295.45</v>
       </c>
       <c r="F41">
         <v>126</v>
@@ -1678,7 +1678,7 @@
         <v>68</v>
       </c>
       <c r="I41">
-        <v>366.65</v>
+        <v>377.02</v>
       </c>
     </row>
     <row r="42">
@@ -1695,7 +1695,7 @@
         <v>211</v>
       </c>
       <c r="E42">
-        <v>1326.79</v>
+        <v>1337.57</v>
       </c>
       <c r="F42">
         <v>134</v>
@@ -1707,7 +1707,7 @@
         <v>77</v>
       </c>
       <c r="I42">
-        <v>440.21</v>
+        <v>450.99</v>
       </c>
     </row>
     <row r="43">
@@ -1724,7 +1724,7 @@
         <v>245</v>
       </c>
       <c r="E43">
-        <v>1755.59</v>
+        <v>1765.55</v>
       </c>
       <c r="F43">
         <v>155</v>
@@ -1736,7 +1736,7 @@
         <v>90</v>
       </c>
       <c r="I43">
-        <v>560.12</v>
+        <v>570.08</v>
       </c>
     </row>
     <row r="44">
@@ -1753,7 +1753,7 @@
         <v>244</v>
       </c>
       <c r="E44">
-        <v>1915.79</v>
+        <v>1919.76</v>
       </c>
       <c r="F44">
         <v>154</v>
@@ -1765,7 +1765,7 @@
         <v>90</v>
       </c>
       <c r="I44">
-        <v>466.34</v>
+        <v>470.31</v>
       </c>
     </row>
     <row r="45">
@@ -1782,7 +1782,7 @@
         <v>233</v>
       </c>
       <c r="E45">
-        <v>1663.65</v>
+        <v>1670.74</v>
       </c>
       <c r="F45">
         <v>145</v>
@@ -1794,7 +1794,7 @@
         <v>88</v>
       </c>
       <c r="I45">
-        <v>484.52</v>
+        <v>491.61</v>
       </c>
     </row>
     <row r="46">
@@ -1811,7 +1811,7 @@
         <v>252</v>
       </c>
       <c r="E46">
-        <v>1751.89</v>
+        <v>1756.64</v>
       </c>
       <c r="F46">
         <v>155</v>
@@ -1823,7 +1823,7 @@
         <v>97</v>
       </c>
       <c r="I46">
-        <v>520.96</v>
+        <v>525.71</v>
       </c>
     </row>
     <row r="47">
@@ -1840,7 +1840,7 @@
         <v>258</v>
       </c>
       <c r="E47">
-        <v>1742.91</v>
+        <v>1802.09</v>
       </c>
       <c r="F47">
         <v>162</v>
@@ -1852,7 +1852,7 @@
         <v>96</v>
       </c>
       <c r="I47">
-        <v>564.12</v>
+        <v>623.3</v>
       </c>
     </row>
     <row r="48">
@@ -1866,34 +1866,121 @@
         <v>609</v>
       </c>
       <c r="D48">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="E48">
-        <v>532.03</v>
+        <v>1926.24</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1350.48</v>
       </c>
       <c r="H48">
         <v>108</v>
       </c>
       <c r="I48">
-        <v>532.03</v>
+        <v>575.76</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B49">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <v>630</v>
+      </c>
+      <c r="D49">
+        <v>295</v>
+      </c>
+      <c r="E49">
+        <v>2128.59</v>
+      </c>
+      <c r="F49">
+        <v>182</v>
+      </c>
+      <c r="G49">
+        <v>1487.9</v>
+      </c>
+      <c r="H49">
+        <v>113</v>
+      </c>
+      <c r="I49">
+        <v>640.69</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>633</v>
+      </c>
+      <c r="D50">
+        <v>287</v>
+      </c>
+      <c r="E50">
+        <v>2135</v>
+      </c>
+      <c r="F50">
+        <v>180</v>
+      </c>
+      <c r="G50">
+        <v>1534.57</v>
+      </c>
+      <c r="H50">
+        <v>107</v>
+      </c>
+      <c r="I50">
+        <v>600.43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>637</v>
+      </c>
+      <c r="D51">
+        <v>113</v>
+      </c>
+      <c r="E51">
+        <v>625.67</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>113</v>
+      </c>
+      <c r="I51">
+        <v>625.67</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G610"/>
+  <dimension ref="A1:G638"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2890,7 +2977,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G43" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="44">
@@ -3695,7 +3782,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G78" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="79">
@@ -3718,7 +3805,7 @@
         <v>王清月</v>
       </c>
       <c r="G79" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="80">
@@ -4477,7 +4564,7 @@
         <v>王郡江</v>
       </c>
       <c r="G112" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="113">
@@ -4707,7 +4794,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G122" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="123">
@@ -4845,7 +4932,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G128" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="129">
@@ -5880,7 +5967,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G173" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="174">
@@ -6064,7 +6151,7 @@
         <v>王清月</v>
       </c>
       <c r="G181" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="182">
@@ -6202,7 +6289,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G187" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="188">
@@ -6340,7 +6427,7 @@
         <v>王清月</v>
       </c>
       <c r="G193" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="194">
@@ -6501,7 +6588,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G200" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="201">
@@ -6662,7 +6749,7 @@
         <v>王涛</v>
       </c>
       <c r="G207" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="208">
@@ -6731,7 +6818,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G210" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="211">
@@ -6961,7 +7048,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G220" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="221">
@@ -7053,7 +7140,7 @@
         <v>王郡江</v>
       </c>
       <c r="G224" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="225">
@@ -7099,7 +7186,7 @@
         <v>王清月</v>
       </c>
       <c r="G226" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="227">
@@ -7559,7 +7646,7 @@
         <v>王清月</v>
       </c>
       <c r="G246" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="247">
@@ -7743,7 +7830,7 @@
         <v>王清月</v>
       </c>
       <c r="G254" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="255">
@@ -7881,7 +7968,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G260" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="261">
@@ -8065,7 +8152,7 @@
         <v>王郡江</v>
       </c>
       <c r="G268" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="269">
@@ -8249,7 +8336,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G276" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="277">
@@ -8295,7 +8382,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G278" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="279">
@@ -8341,7 +8428,7 @@
         <v>王郡江</v>
       </c>
       <c r="G280" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="281">
@@ -8502,7 +8589,7 @@
         <v>王清月</v>
       </c>
       <c r="G287" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="288">
@@ -8778,7 +8865,7 @@
         <v>王涛</v>
       </c>
       <c r="G299" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="300">
@@ -9077,7 +9164,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G312" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="313">
@@ -9721,7 +9808,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G340" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="341">
@@ -9836,7 +9923,7 @@
         <v>王涛</v>
       </c>
       <c r="G345" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="346">
@@ -10503,7 +10590,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G374" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="375">
@@ -11032,7 +11119,7 @@
         <v>王涛</v>
       </c>
       <c r="G397" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="398">
@@ -11055,7 +11142,7 @@
         <v>王清月</v>
       </c>
       <c r="G398" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="399">
@@ -11078,7 +11165,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G399" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="400">
@@ -11101,7 +11188,7 @@
         <v>王涛</v>
       </c>
       <c r="G400" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="401">
@@ -11147,7 +11234,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G402" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="403">
@@ -11170,7 +11257,7 @@
         <v>王清月</v>
       </c>
       <c r="G403" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="404">
@@ -11193,7 +11280,7 @@
         <v>王涛</v>
       </c>
       <c r="G404" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="405">
@@ -11239,7 +11326,7 @@
         <v>王郡江</v>
       </c>
       <c r="G406" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="407">
@@ -11308,7 +11395,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G409" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="410">
@@ -11331,7 +11418,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G410" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="411">
@@ -11354,7 +11441,7 @@
         <v>王清月</v>
       </c>
       <c r="G411" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="412">
@@ -11400,7 +11487,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G413" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="414">
@@ -11423,7 +11510,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G414" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="415">
@@ -11446,7 +11533,7 @@
         <v>王清月</v>
       </c>
       <c r="G415" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="416">
@@ -11492,7 +11579,7 @@
         <v>王涛</v>
       </c>
       <c r="G417" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="418">
@@ -11538,7 +11625,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G419" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="420">
@@ -11561,7 +11648,7 @@
         <v>王郡江</v>
       </c>
       <c r="G420" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="421">
@@ -11584,7 +11671,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G421" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="422">
@@ -11607,7 +11694,7 @@
         <v>王涛</v>
       </c>
       <c r="G422" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="423">
@@ -11653,7 +11740,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G424" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="425">
@@ -11722,7 +11809,7 @@
         <v>王郡江</v>
       </c>
       <c r="G427" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="428">
@@ -11745,7 +11832,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G428" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="429">
@@ -11768,7 +11855,7 @@
         <v>王涛</v>
       </c>
       <c r="G429" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="430">
@@ -11791,7 +11878,7 @@
         <v>王清月</v>
       </c>
       <c r="G430" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="431">
@@ -11814,7 +11901,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G431" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="432">
@@ -11837,7 +11924,7 @@
         <v>王涛</v>
       </c>
       <c r="G432" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="433">
@@ -11860,7 +11947,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G433" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="434">
@@ -11883,7 +11970,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G434" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="435">
@@ -11906,7 +11993,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G435" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="436">
@@ -11929,7 +12016,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G436" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="437">
@@ -11952,7 +12039,7 @@
         <v>王清月</v>
       </c>
       <c r="G437" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="438">
@@ -11975,7 +12062,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G438" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="439">
@@ -11998,7 +12085,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G439" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="440">
@@ -12021,7 +12108,7 @@
         <v>王清月</v>
       </c>
       <c r="G440" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="441">
@@ -12044,7 +12131,7 @@
         <v>王郡江</v>
       </c>
       <c r="G441" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="442">
@@ -12067,7 +12154,7 @@
         <v>王清月</v>
       </c>
       <c r="G442" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="443">
@@ -12090,7 +12177,7 @@
         <v>王清月</v>
       </c>
       <c r="G443" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="444">
@@ -12113,7 +12200,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G444" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="445">
@@ -12136,7 +12223,7 @@
         <v>王郡江</v>
       </c>
       <c r="G445" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="446">
@@ -12159,7 +12246,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G446" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="447">
@@ -12205,7 +12292,7 @@
         <v>王清月</v>
       </c>
       <c r="G448" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="449">
@@ -12228,7 +12315,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G449" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="450">
@@ -12251,7 +12338,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G450" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="451">
@@ -12274,7 +12361,7 @@
         <v>王涛</v>
       </c>
       <c r="G451" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="452">
@@ -12297,7 +12384,7 @@
         <v>王涛</v>
       </c>
       <c r="G452" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="453">
@@ -12320,7 +12407,7 @@
         <v>王清月</v>
       </c>
       <c r="G453" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="454">
@@ -12343,7 +12430,7 @@
         <v>王郡江</v>
       </c>
       <c r="G454" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="455">
@@ -12366,7 +12453,7 @@
         <v>王涛</v>
       </c>
       <c r="G455" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="456">
@@ -12412,7 +12499,7 @@
         <v>王清月</v>
       </c>
       <c r="G457" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="458">
@@ -12435,7 +12522,7 @@
         <v>王清月</v>
       </c>
       <c r="G458" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="459">
@@ -12458,7 +12545,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G459" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="460">
@@ -12481,7 +12568,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G460" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="461">
@@ -12504,7 +12591,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G461" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="462">
@@ -12527,7 +12614,7 @@
         <v>王涛</v>
       </c>
       <c r="G462" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="463">
@@ -12550,7 +12637,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G463" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="464">
@@ -12573,7 +12660,7 @@
         <v>王涛</v>
       </c>
       <c r="G464" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="465">
@@ -12619,7 +12706,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G466" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="467">
@@ -12642,7 +12729,7 @@
         <v>王涛</v>
       </c>
       <c r="G467" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="468">
@@ -12665,7 +12752,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G468" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="469">
@@ -12688,7 +12775,7 @@
         <v>王清月</v>
       </c>
       <c r="G469" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="470">
@@ -12711,7 +12798,7 @@
         <v>王郡江</v>
       </c>
       <c r="G470" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="471">
@@ -12734,7 +12821,7 @@
         <v>王涛</v>
       </c>
       <c r="G471" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="472">
@@ -12757,7 +12844,7 @@
         <v>王涛</v>
       </c>
       <c r="G472" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="473">
@@ -12780,7 +12867,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G473" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="474">
@@ -12803,7 +12890,7 @@
         <v>王清月</v>
       </c>
       <c r="G474" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="475">
@@ -12826,7 +12913,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G475" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="476">
@@ -12849,7 +12936,7 @@
         <v>王涛</v>
       </c>
       <c r="G476" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="477">
@@ -12872,7 +12959,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G477" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="478">
@@ -12895,7 +12982,7 @@
         <v>王清月</v>
       </c>
       <c r="G478" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="479">
@@ -12918,7 +13005,7 @@
         <v>王涛</v>
       </c>
       <c r="G479" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="480">
@@ -12941,7 +13028,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G480" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="481">
@@ -12987,7 +13074,7 @@
         <v>王涛</v>
       </c>
       <c r="G482" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="483">
@@ -13010,7 +13097,7 @@
         <v>王郡江</v>
       </c>
       <c r="G483" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="484">
@@ -13033,7 +13120,7 @@
         <v>王清月</v>
       </c>
       <c r="G484" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="485">
@@ -13056,7 +13143,7 @@
         <v>王清月</v>
       </c>
       <c r="G485" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="486">
@@ -13079,7 +13166,7 @@
         <v>王清月</v>
       </c>
       <c r="G486" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="487">
@@ -13102,7 +13189,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G487" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="488">
@@ -13125,7 +13212,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G488" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="489">
@@ -13148,7 +13235,7 @@
         <v>王郡江</v>
       </c>
       <c r="G489" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="490">
@@ -13171,7 +13258,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G490" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="491">
@@ -13194,7 +13281,7 @@
         <v>王郡江</v>
       </c>
       <c r="G491" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="492">
@@ -13332,7 +13419,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G497" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="498">
@@ -13470,7 +13557,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G503" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="504">
@@ -13654,7 +13741,7 @@
         <v>王清月</v>
       </c>
       <c r="G511" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="512">
@@ -15310,7 +15397,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G583" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="584">
@@ -15333,7 +15420,7 @@
         <v>王涛</v>
       </c>
       <c r="G584" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="585">
@@ -15934,9 +16021,653 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B611" t="str">
+        <v>1338051300</v>
+      </c>
+      <c r="C611" t="str">
+        <v>半山小厨</v>
+      </c>
+      <c r="D611" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E611" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F611" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G611" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B612" t="str">
+        <v>32196835</v>
+      </c>
+      <c r="C612" t="str">
+        <v>文山酸汤米线·麻辣鸡米线</v>
+      </c>
+      <c r="D612" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E612" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F612" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G612" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B613" t="str">
+        <v>32394317</v>
+      </c>
+      <c r="C613" t="str">
+        <v>鑫福轩麻辣烫</v>
+      </c>
+      <c r="D613" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E613" t="str">
+        <v>贺蓓</v>
+      </c>
+      <c r="F613" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G613" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B614" t="str">
+        <v>1335764038</v>
+      </c>
+      <c r="C614" t="str">
+        <v>鑫福轩炸串·麻辣烫</v>
+      </c>
+      <c r="D614" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E614" t="str">
+        <v>贺蓓</v>
+      </c>
+      <c r="F614" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G614" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B615" t="str">
+        <v>32300334</v>
+      </c>
+      <c r="C615" t="str">
+        <v>小胖水煎包胡辣汤</v>
+      </c>
+      <c r="D615" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E615" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F615" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G615" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B616" t="str">
+        <v>32544905</v>
+      </c>
+      <c r="C616" t="str">
+        <v>大红头龙虾馆</v>
+      </c>
+      <c r="D616" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E616" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F616" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G616" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B617" t="str">
+        <v>32575964</v>
+      </c>
+      <c r="C617" t="str">
+        <v>少野家锅锅米线</v>
+      </c>
+      <c r="D617" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E617" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F617" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G617" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B618" t="str">
+        <v>542864109</v>
+      </c>
+      <c r="C618" t="str">
+        <v>放牛纪·奶皮子手工酸奶</v>
+      </c>
+      <c r="D618" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E618" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F618" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G618" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B619" t="str">
+        <v>32370610</v>
+      </c>
+      <c r="C619" t="str">
+        <v>天津小笼包(小笼包，盖饭)</v>
+      </c>
+      <c r="D619" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E619" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F619" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G619" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B620" t="str">
+        <v>1338943709</v>
+      </c>
+      <c r="C620" t="str">
+        <v>王记鲜包牛肉面</v>
+      </c>
+      <c r="D620" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E620" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F620" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G620" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B621" t="str">
+        <v>32389217</v>
+      </c>
+      <c r="C621" t="str">
+        <v>王记鲜包牛肉面（太子桥店）</v>
+      </c>
+      <c r="D621" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E621" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F621" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G621" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B622" t="str">
+        <v>32649079</v>
+      </c>
+      <c r="C622" t="str">
+        <v>手工水饺（陵西店）</v>
+      </c>
+      <c r="D622" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E622" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F622" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G622" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B623" t="str">
+        <v>542613457</v>
+      </c>
+      <c r="C623" t="str">
+        <v>烤梨馄饨烤冷面·东北菜(东悦荟店)</v>
+      </c>
+      <c r="D623" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E623" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F623" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G623" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B624" t="str">
+        <v>32611494</v>
+      </c>
+      <c r="C624" t="str">
+        <v>湘味小馆</v>
+      </c>
+      <c r="D624" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E624" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F624" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G624" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B625" t="str">
+        <v>1339001222</v>
+      </c>
+      <c r="C625" t="str">
+        <v>湘味小馆</v>
+      </c>
+      <c r="D625" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E625" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F625" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G625" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B626" t="str">
+        <v>32675737</v>
+      </c>
+      <c r="C626" t="str">
+        <v>皓轩烤炉鸡蛋灌饼</v>
+      </c>
+      <c r="D626" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E626" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F626" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G626" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B627" t="str">
+        <v>1340336041</v>
+      </c>
+      <c r="C627" t="str">
+        <v>皓轩烤炉鸡蛋灌饼(威海总店)</v>
+      </c>
+      <c r="D627" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E627" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F627" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G627" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B628" t="str">
+        <v>32312404</v>
+      </c>
+      <c r="C628" t="str">
+        <v>柳州螺蛳粉桂林米粉</v>
+      </c>
+      <c r="D628" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E628" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F628" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G628" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B629" t="str">
+        <v>32474229</v>
+      </c>
+      <c r="C629" t="str">
+        <v>楼下（咖啡·小吃）</v>
+      </c>
+      <c r="D629" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E629" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F629" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G629" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B630" t="str">
+        <v>32369679</v>
+      </c>
+      <c r="C630" t="str">
+        <v>老厦门砂锅套餐</v>
+      </c>
+      <c r="D630" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E630" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F630" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G630" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="B631" t="str">
+        <v>542696349</v>
+      </c>
+      <c r="C631" t="str">
+        <v>老厦门砂锅套餐</v>
+      </c>
+      <c r="D631" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E631" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F631" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G631" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="B632" t="str">
+        <v>32701509</v>
+      </c>
+      <c r="C632" t="str">
+        <v>地摊串串小火锅</v>
+      </c>
+      <c r="D632" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E632" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F632" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G632" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="B633" t="str">
+        <v>32532785</v>
+      </c>
+      <c r="C633" t="str">
+        <v>螺蛳粉界的黑马（元谷mall店）</v>
+      </c>
+      <c r="D633" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E633" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F633" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G633" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="B634" t="str">
+        <v>1332435651</v>
+      </c>
+      <c r="C634" t="str">
+        <v>孙小昌中国炸鸡(湖北襄阳三十一中店)</v>
+      </c>
+      <c r="D634" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E634" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F634" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G634" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B635" t="str">
+        <v>32672788</v>
+      </c>
+      <c r="C635" t="str">
+        <v>搞一碗七（早点·汤面·炒面）</v>
+      </c>
+      <c r="D635" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E635" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F635" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G635" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B636" t="str">
+        <v>1335763420</v>
+      </c>
+      <c r="C636" t="str">
+        <v>鲜货炒鸡·临沂特色(四望亭店)</v>
+      </c>
+      <c r="D636" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E636" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F636" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G636" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B637" t="str">
+        <v>32425959</v>
+      </c>
+      <c r="C637" t="str">
+        <v>鲜货炒鸡·临沂特色（四望亭路店）</v>
+      </c>
+      <c r="D637" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E637" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F637" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G637" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="B638" t="str">
+        <v>32457223</v>
+      </c>
+      <c r="C638" t="str">
+        <v>荷包洋芋（泸州一中店）</v>
+      </c>
+      <c r="D638" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E638" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F638" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G638" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G610"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G638"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15970,7 +16701,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-16 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-19 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-22</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>637</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>41457.740000000005</v>
+        <v>47891.70000000001</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>5877</v>
+        <v>6717</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/20 10:46:51</v>
+        <v>2026/4/23 09:45:32</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1898,7 +1898,7 @@
         <v>295</v>
       </c>
       <c r="E49">
-        <v>2128.59</v>
+        <v>2129.12</v>
       </c>
       <c r="F49">
         <v>182</v>
@@ -1910,7 +1910,7 @@
         <v>113</v>
       </c>
       <c r="I49">
-        <v>640.69</v>
+        <v>641.22</v>
       </c>
     </row>
     <row r="50">
@@ -1953,34 +1953,121 @@
         <v>637</v>
       </c>
       <c r="D51">
-        <v>113</v>
+        <v>284</v>
       </c>
       <c r="E51">
-        <v>625.67</v>
+        <v>2295.76</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1599.01</v>
       </c>
       <c r="H51">
         <v>113</v>
       </c>
       <c r="I51">
-        <v>625.67</v>
+        <v>696.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B52">
+        <v>13</v>
+      </c>
+      <c r="C52">
+        <v>650</v>
+      </c>
+      <c r="D52">
+        <v>267</v>
+      </c>
+      <c r="E52">
+        <v>1953.94</v>
+      </c>
+      <c r="F52">
+        <v>167</v>
+      </c>
+      <c r="G52">
+        <v>1287.08</v>
+      </c>
+      <c r="H52">
+        <v>100</v>
+      </c>
+      <c r="I52">
+        <v>666.86</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B53">
+        <v>29</v>
+      </c>
+      <c r="C53">
+        <v>679</v>
+      </c>
+      <c r="D53">
+        <v>288</v>
+      </c>
+      <c r="E53">
+        <v>2192.25</v>
+      </c>
+      <c r="F53">
+        <v>176</v>
+      </c>
+      <c r="G53">
+        <v>1482.57</v>
+      </c>
+      <c r="H53">
+        <v>112</v>
+      </c>
+      <c r="I53">
+        <v>709.68</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
+      <c r="C54">
+        <v>694</v>
+      </c>
+      <c r="D54">
+        <v>114</v>
+      </c>
+      <c r="E54">
+        <v>617.15</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>114</v>
+      </c>
+      <c r="I54">
+        <v>617.15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G638"/>
+  <dimension ref="A1:G695"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2333,7 +2420,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G15" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="16">
@@ -2425,7 +2512,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G19" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="20">
@@ -2839,7 +2926,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G37" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="38">
@@ -2954,7 +3041,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G42" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="43">
@@ -3230,7 +3317,7 @@
         <v>王清月</v>
       </c>
       <c r="G54" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="55">
@@ -3460,7 +3547,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G64" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="65">
@@ -3782,7 +3869,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G78" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="79">
@@ -3805,7 +3892,7 @@
         <v>王清月</v>
       </c>
       <c r="G79" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="80">
@@ -4357,7 +4444,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G103" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="104">
@@ -4449,7 +4536,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G107" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="108">
@@ -4495,7 +4582,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G109" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="110">
@@ -4656,7 +4743,7 @@
         <v>王涛</v>
       </c>
       <c r="G116" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="117">
@@ -4679,7 +4766,7 @@
         <v>王清月</v>
       </c>
       <c r="G117" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="118">
@@ -5001,7 +5088,7 @@
         <v>王清月</v>
       </c>
       <c r="G131" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="132">
@@ -5369,7 +5456,7 @@
         <v>王涛</v>
       </c>
       <c r="G147" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="148">
@@ -5967,7 +6054,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G173" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="174">
@@ -6105,7 +6192,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G179" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="180">
@@ -6565,7 +6652,7 @@
         <v>王郡江</v>
       </c>
       <c r="G199" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="200">
@@ -7048,7 +7135,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G220" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="221">
@@ -7163,7 +7250,7 @@
         <v>王涛</v>
       </c>
       <c r="G225" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="226">
@@ -7232,7 +7319,7 @@
         <v>王清月</v>
       </c>
       <c r="G228" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="229">
@@ -7301,7 +7388,7 @@
         <v>王涛</v>
       </c>
       <c r="G231" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="232">
@@ -7416,7 +7503,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G236" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="237">
@@ -7623,7 +7710,7 @@
         <v>王清月</v>
       </c>
       <c r="G245" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="246">
@@ -7853,7 +7940,7 @@
         <v>王郡江</v>
       </c>
       <c r="G255" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="256">
@@ -7991,7 +8078,7 @@
         <v>王涛</v>
       </c>
       <c r="G261" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="262">
@@ -8382,7 +8469,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G278" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="279">
@@ -8589,7 +8676,7 @@
         <v>王清月</v>
       </c>
       <c r="G287" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="288">
@@ -9670,7 +9757,7 @@
         <v>王郡江</v>
       </c>
       <c r="G334" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="335">
@@ -9900,7 +9987,7 @@
         <v>王郡江</v>
       </c>
       <c r="G344" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="345">
@@ -10314,7 +10401,7 @@
         <v>王清月</v>
       </c>
       <c r="G362" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="363">
@@ -10613,7 +10700,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G375" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="376">
@@ -10820,7 +10907,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G384" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="385">
@@ -11165,7 +11252,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G399" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="400">
@@ -11441,7 +11528,7 @@
         <v>王清月</v>
       </c>
       <c r="G411" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="412">
@@ -11487,7 +11574,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G413" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="414">
@@ -11579,7 +11666,7 @@
         <v>王涛</v>
       </c>
       <c r="G417" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="418">
@@ -11625,7 +11712,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G419" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="420">
@@ -11694,7 +11781,7 @@
         <v>王涛</v>
       </c>
       <c r="G422" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="423">
@@ -11740,7 +11827,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G424" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="425">
@@ -12223,7 +12310,7 @@
         <v>王郡江</v>
       </c>
       <c r="G445" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="446">
@@ -12683,7 +12770,7 @@
         <v>王郡江</v>
       </c>
       <c r="G465" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="466">
@@ -12706,7 +12793,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G466" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="467">
@@ -12959,7 +13046,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G477" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="478">
@@ -13327,7 +13414,7 @@
         <v>王涛</v>
       </c>
       <c r="G493" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="494">
@@ -13350,7 +13437,7 @@
         <v>王清月</v>
       </c>
       <c r="G494" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="495">
@@ -13373,7 +13460,7 @@
         <v>王涛</v>
       </c>
       <c r="G495" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="496">
@@ -13396,7 +13483,7 @@
         <v>王清月</v>
       </c>
       <c r="G496" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="497">
@@ -13442,7 +13529,7 @@
         <v>王清月</v>
       </c>
       <c r="G498" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="499">
@@ -13465,7 +13552,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G499" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="500">
@@ -13488,7 +13575,7 @@
         <v>王清月</v>
       </c>
       <c r="G500" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="501">
@@ -13511,7 +13598,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G501" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="502">
@@ -13534,7 +13621,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G502" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="503">
@@ -13580,7 +13667,7 @@
         <v>王涛</v>
       </c>
       <c r="G504" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="505">
@@ -13603,7 +13690,7 @@
         <v>王清月</v>
       </c>
       <c r="G505" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="506">
@@ -13626,7 +13713,7 @@
         <v>王涛</v>
       </c>
       <c r="G506" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="507">
@@ -13672,7 +13759,7 @@
         <v>王清月</v>
       </c>
       <c r="G508" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="509">
@@ -13695,7 +13782,7 @@
         <v>王涛</v>
       </c>
       <c r="G509" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="510">
@@ -13718,7 +13805,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G510" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="511">
@@ -13741,7 +13828,7 @@
         <v>王清月</v>
       </c>
       <c r="G511" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="512">
@@ -13764,7 +13851,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G512" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="513">
@@ -13787,7 +13874,7 @@
         <v>王郡江</v>
       </c>
       <c r="G513" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="514">
@@ -13810,7 +13897,7 @@
         <v>王郡江</v>
       </c>
       <c r="G514" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="515">
@@ -13833,7 +13920,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G515" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="516">
@@ -13856,7 +13943,7 @@
         <v>王郡江</v>
       </c>
       <c r="G516" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="517">
@@ -13879,7 +13966,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G517" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="518">
@@ -13902,7 +13989,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G518" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="519">
@@ -13925,7 +14012,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G519" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="520">
@@ -13948,7 +14035,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G520" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="521">
@@ -13971,7 +14058,7 @@
         <v>王郡江</v>
       </c>
       <c r="G521" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="522">
@@ -13994,7 +14081,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G522" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="523">
@@ -14040,7 +14127,7 @@
         <v>王郡江</v>
       </c>
       <c r="G524" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="525">
@@ -14063,7 +14150,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G525" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="526">
@@ -14132,7 +14219,7 @@
         <v>王郡江</v>
       </c>
       <c r="G528" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="529">
@@ -14155,7 +14242,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G529" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="530">
@@ -14178,7 +14265,7 @@
         <v>王郡江</v>
       </c>
       <c r="G530" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="531">
@@ -14201,7 +14288,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G531" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="532">
@@ -14224,7 +14311,7 @@
         <v>王郡江</v>
       </c>
       <c r="G532" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="533">
@@ -14247,7 +14334,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G533" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="534">
@@ -14270,7 +14357,7 @@
         <v>王涛</v>
       </c>
       <c r="G534" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="535">
@@ -14316,7 +14403,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G536" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="537">
@@ -14339,7 +14426,7 @@
         <v>王郡江</v>
       </c>
       <c r="G537" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="538">
@@ -14362,7 +14449,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G538" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="539">
@@ -14385,7 +14472,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G539" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="540">
@@ -14454,7 +14541,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G542" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="543">
@@ -14477,7 +14564,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G543" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="544">
@@ -14523,7 +14610,7 @@
         <v>王清月</v>
       </c>
       <c r="G545" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="546">
@@ -14707,7 +14794,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G553" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="554">
@@ -14799,7 +14886,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G557" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="558">
@@ -14983,7 +15070,7 @@
         <v>王清月</v>
       </c>
       <c r="G565" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="566">
@@ -15098,7 +15185,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G570" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="571">
@@ -16432,7 +16519,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G628" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="629">
@@ -16665,9 +16752,1320 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B639" t="str">
+        <v>32210632</v>
+      </c>
+      <c r="C639" t="str">
+        <v>8点8优品刀切拌面</v>
+      </c>
+      <c r="D639" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E639" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F639" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G639" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B640" t="str">
+        <v>523319142</v>
+      </c>
+      <c r="C640" t="str">
+        <v>瑶妹石磨手工肠粉店</v>
+      </c>
+      <c r="D640" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E640" t="str">
+        <v>郭文</v>
+      </c>
+      <c r="F640" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G640" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B641" t="str">
+        <v>1328583428</v>
+      </c>
+      <c r="C641" t="str">
+        <v>曹小韩米线</v>
+      </c>
+      <c r="D641" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E641" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F641" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G641" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B642" t="str">
+        <v>541801754</v>
+      </c>
+      <c r="C642" t="str">
+        <v>史记龙虾(雨顺店)</v>
+      </c>
+      <c r="D642" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E642" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F642" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G642" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B643" t="str">
+        <v>32551574</v>
+      </c>
+      <c r="C643" t="str">
+        <v>盱眙小龙虾</v>
+      </c>
+      <c r="D643" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E643" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F643" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G643" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B644" t="str">
+        <v>1338614817</v>
+      </c>
+      <c r="C644" t="str">
+        <v>庞氏淄味鲜肉大烧饼</v>
+      </c>
+      <c r="D644" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E644" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F644" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G644" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B645" t="str">
+        <v>32377042</v>
+      </c>
+      <c r="C645" t="str">
+        <v>庞氏淄味鲜肉大烧饼</v>
+      </c>
+      <c r="D645" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E645" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F645" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G645" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B646" t="str">
+        <v>32717928</v>
+      </c>
+      <c r="C646" t="str">
+        <v>千禧龍虾煌•虾尾•爆汁龙虾</v>
+      </c>
+      <c r="D646" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E646" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F646" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G646" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B647" t="str">
+        <v>1340322563</v>
+      </c>
+      <c r="C647" t="str">
+        <v>以勒肉饼</v>
+      </c>
+      <c r="D647" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E647" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F647" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G647" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B648" t="str">
+        <v>1338063921</v>
+      </c>
+      <c r="C648" t="str">
+        <v>即食自选快餐厅·快餐盒饭</v>
+      </c>
+      <c r="D648" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E648" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F648" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G648" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B649" t="str">
+        <v>1335809545</v>
+      </c>
+      <c r="C649" t="str">
+        <v>李记·炸串卷饼·担担面(龙园店)</v>
+      </c>
+      <c r="D649" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E649" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F649" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G649" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B650" t="str">
+        <v>32371800</v>
+      </c>
+      <c r="C650" t="str">
+        <v>尚鲜拇指生煎包</v>
+      </c>
+      <c r="D650" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E650" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F650" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G650" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B651" t="str">
+        <v>32379788</v>
+      </c>
+      <c r="C651" t="str">
+        <v>奇鑫小吃店（高坪店）</v>
+      </c>
+      <c r="D651" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E651" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F651" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G651" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B652" t="str">
+        <v>32511375</v>
+      </c>
+      <c r="C652" t="str">
+        <v>新疆阿达西烧烤</v>
+      </c>
+      <c r="D652" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E652" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F652" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G652" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B653" t="str">
+        <v>32641421</v>
+      </c>
+      <c r="C653" t="str">
+        <v>老面高桩馒头(蒸包·窝头·闵子骞路店)</v>
+      </c>
+      <c r="D653" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E653" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F653" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G653" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B654" t="str">
+        <v>541817411</v>
+      </c>
+      <c r="C654" t="str">
+        <v>手工老面馒头·煎包·蒸包·窝窝头</v>
+      </c>
+      <c r="D654" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E654" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F654" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G654" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B655" t="str">
+        <v>32549122</v>
+      </c>
+      <c r="C655" t="str">
+        <v>聚福源</v>
+      </c>
+      <c r="D655" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E655" t="str">
+        <v>贺蓓</v>
+      </c>
+      <c r="F655" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G655" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B656" t="str">
+        <v>543118469</v>
+      </c>
+      <c r="C656" t="str">
+        <v>重庆小面(厚施路店)</v>
+      </c>
+      <c r="D656" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E656" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F656" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G656" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B657" t="str">
+        <v>32729690</v>
+      </c>
+      <c r="C657" t="str">
+        <v>玥熹重庆小面(厚施路店)</v>
+      </c>
+      <c r="D657" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E657" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F657" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G657" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B658" t="str">
+        <v>31953265</v>
+      </c>
+      <c r="C658" t="str">
+        <v>阿献骨汤川味面</v>
+      </c>
+      <c r="D658" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E658" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F658" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G658" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B659" t="str">
+        <v>32674384</v>
+      </c>
+      <c r="C659" t="str">
+        <v>爆叔炸串</v>
+      </c>
+      <c r="D659" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E659" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F659" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G659" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B660" t="str">
+        <v>543040878</v>
+      </c>
+      <c r="C660" t="str">
+        <v>爆叔炸串</v>
+      </c>
+      <c r="D660" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E660" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F660" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G660" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B661" t="str">
+        <v>32635858</v>
+      </c>
+      <c r="C661" t="str">
+        <v>潮汕汤粉王</v>
+      </c>
+      <c r="D661" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E661" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F661" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G661" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B662" t="str">
+        <v>1338968476</v>
+      </c>
+      <c r="C662" t="str">
+        <v>潮汕汤粉王(新会机电店)</v>
+      </c>
+      <c r="D662" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E662" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F662" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G662" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B663" t="str">
+        <v>32564918</v>
+      </c>
+      <c r="C663" t="str">
+        <v>醴陵炒粉（涉外店）</v>
+      </c>
+      <c r="D663" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E663" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F663" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G663" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B664" t="str">
+        <v>32684432</v>
+      </c>
+      <c r="C664" t="str">
+        <v>马老二自助餐</v>
+      </c>
+      <c r="D664" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E664" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F664" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G664" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B665" t="str">
+        <v>1334991014</v>
+      </c>
+      <c r="C665" t="str">
+        <v>马老二自助餐</v>
+      </c>
+      <c r="D665" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E665" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F665" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G665" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B666" t="str">
+        <v>542547831</v>
+      </c>
+      <c r="C666" t="str">
+        <v>锦州烧烤</v>
+      </c>
+      <c r="D666" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E666" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F666" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G666" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B667" t="str">
+        <v>32330811</v>
+      </c>
+      <c r="C667" t="str">
+        <v>锦州烧烤（瑞园小区店）</v>
+      </c>
+      <c r="D667" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E667" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F667" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G667" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B668" t="str">
+        <v>542841840</v>
+      </c>
+      <c r="C668" t="str">
+        <v>乐山钵钵鸡(平和堂店)</v>
+      </c>
+      <c r="D668" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E668" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F668" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G668" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B669" t="str">
+        <v>32637238</v>
+      </c>
+      <c r="C669" t="str">
+        <v>龙江小四川水煮鱼</v>
+      </c>
+      <c r="D669" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E669" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F669" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G669" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B670" t="str">
+        <v>542646570</v>
+      </c>
+      <c r="C670" t="str">
+        <v>三小只炖品</v>
+      </c>
+      <c r="D670" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E670" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F670" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G670" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B671" t="str">
+        <v>32372740</v>
+      </c>
+      <c r="C671" t="str">
+        <v>三小只炖品店</v>
+      </c>
+      <c r="D671" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E671" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F671" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G671" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B672" t="str">
+        <v>32365678</v>
+      </c>
+      <c r="C672" t="str">
+        <v>沙县小吃（盖浇饭.扁食.炖汤龙江富城店）</v>
+      </c>
+      <c r="D672" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E672" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F672" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G672" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B673" t="str">
+        <v>542468566</v>
+      </c>
+      <c r="C673" t="str">
+        <v>魏姐早餐店</v>
+      </c>
+      <c r="D673" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E673" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F673" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G673" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B674" t="str">
+        <v>1236850952</v>
+      </c>
+      <c r="C674" t="str">
+        <v>萧记花生汤·早餐·盖浇饭</v>
+      </c>
+      <c r="D674" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E674" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F674" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G674" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B675" t="str">
+        <v>32509360</v>
+      </c>
+      <c r="C675" t="str">
+        <v>二洋煎饼果子</v>
+      </c>
+      <c r="D675" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E675" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F675" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G675" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B676" t="str">
+        <v>1335008295</v>
+      </c>
+      <c r="C676" t="str">
+        <v>状元郎私房菜·手擀面馆(恒大店)</v>
+      </c>
+      <c r="D676" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E676" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F676" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G676" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B677" t="str">
+        <v>32569266</v>
+      </c>
+      <c r="C677" t="str">
+        <v>Karu Italian Lounge</v>
+      </c>
+      <c r="D677" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E677" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F677" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G677" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B678" t="str">
+        <v>32151614</v>
+      </c>
+      <c r="C678" t="str">
+        <v>二师兄猪脚饭</v>
+      </c>
+      <c r="D678" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E678" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F678" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G678" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B679" t="str">
+        <v>1333693931</v>
+      </c>
+      <c r="C679" t="str">
+        <v>二师兄猪脚饭(南外店)</v>
+      </c>
+      <c r="D679" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E679" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F679" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G679" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="B680" t="str">
+        <v>1338849505</v>
+      </c>
+      <c r="C680" t="str">
+        <v>荣昌德烧麦(手工包子馒头云梦店)</v>
+      </c>
+      <c r="D680" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E680" t="str">
+        <v>叶文静</v>
+      </c>
+      <c r="F680" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G680" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B681" t="str">
+        <v>32619094</v>
+      </c>
+      <c r="C681" t="str">
+        <v>香襄湘煲仔饭</v>
+      </c>
+      <c r="D681" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E681" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F681" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G681" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B682" t="str">
+        <v>541595955</v>
+      </c>
+      <c r="C682" t="str">
+        <v>盱眙眼镜龙虾(梁清路店)</v>
+      </c>
+      <c r="D682" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E682" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F682" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G682" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B683" t="str">
+        <v>1337824418</v>
+      </c>
+      <c r="C683" t="str">
+        <v>网红手撕烤鸭(高塘店)</v>
+      </c>
+      <c r="D683" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E683" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F683" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G683" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B684" t="str">
+        <v>32605565</v>
+      </c>
+      <c r="C684" t="str">
+        <v>脆皮烧鸡·小龙虾</v>
+      </c>
+      <c r="D684" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E684" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F684" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G684" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B685" t="str">
+        <v>1339113264</v>
+      </c>
+      <c r="C685" t="str">
+        <v>二东家现炒烤肉(港务区店)</v>
+      </c>
+      <c r="D685" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E685" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F685" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G685" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B686" t="str">
+        <v>32524879</v>
+      </c>
+      <c r="C686" t="str">
+        <v>鸿鑫肉业（卤肉·鸭货）</v>
+      </c>
+      <c r="D686" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E686" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F686" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G686" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B687" t="str">
+        <v>531651965</v>
+      </c>
+      <c r="C687" t="str">
+        <v>赛百特·脆皮烧鸡·小龙虾</v>
+      </c>
+      <c r="D687" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E687" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F687" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G687" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B688" t="str">
+        <v>542674479</v>
+      </c>
+      <c r="C688" t="str">
+        <v>三品源包子铺</v>
+      </c>
+      <c r="D688" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E688" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F688" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G688" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B689" t="str">
+        <v>1239687456</v>
+      </c>
+      <c r="C689" t="str">
+        <v>青年邵阳牛肉米粉</v>
+      </c>
+      <c r="D689" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E689" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F689" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G689" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B690" t="str">
+        <v>32414837</v>
+      </c>
+      <c r="C690" t="str">
+        <v>疆晓晓•新疆炒米粉（高新店）</v>
+      </c>
+      <c r="D690" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E690" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F690" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G690" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B691" t="str">
+        <v>32361443</v>
+      </c>
+      <c r="C691" t="str">
+        <v>神湖御肘猪脚饭</v>
+      </c>
+      <c r="D691" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E691" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F691" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G691" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B692" t="str">
+        <v>541035462</v>
+      </c>
+      <c r="C692" t="str">
+        <v>云南蒸汽石锅鱼·炒菜(鸿宇广场店)</v>
+      </c>
+      <c r="D692" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E692" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F692" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G692" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B693" t="str">
+        <v>31856698</v>
+      </c>
+      <c r="C693" t="str">
+        <v>雲南蒸汽石锅鱼</v>
+      </c>
+      <c r="D693" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E693" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F693" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G693" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B694" t="str">
+        <v>32243562</v>
+      </c>
+      <c r="C694" t="str">
+        <v>陈大勺鲜炒码粉面馆</v>
+      </c>
+      <c r="D694" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E694" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F694" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G694" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="B695" t="str">
+        <v>542620092</v>
+      </c>
+      <c r="C695" t="str">
+        <v>煎个煎饼(大众街店)</v>
+      </c>
+      <c r="D695" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E695" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F695" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G695" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G638"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G695"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16701,7 +18099,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-19 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-22 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-26</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>694</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>47891.70000000001</v>
+        <v>56895.82000000001</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>6717</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/23 09:45:32</v>
+        <v>2026/4/27 10:19:00</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I58"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1521,7 +1521,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>1038.36</v>
+        <v>1047.89</v>
       </c>
       <c r="F36">
         <v>101</v>
@@ -1533,7 +1533,7 @@
         <v>57</v>
       </c>
       <c r="I36">
-        <v>295.72</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="37">
@@ -1550,7 +1550,7 @@
         <v>145</v>
       </c>
       <c r="E37">
-        <v>1177.42</v>
+        <v>1183.39</v>
       </c>
       <c r="F37">
         <v>95</v>
@@ -1562,7 +1562,7 @@
         <v>50</v>
       </c>
       <c r="I37">
-        <v>333.26</v>
+        <v>339.23</v>
       </c>
     </row>
     <row r="38">
@@ -1579,7 +1579,7 @@
         <v>154</v>
       </c>
       <c r="E38">
-        <v>1147</v>
+        <v>1149.63</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -1591,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="I38">
-        <v>312.22</v>
+        <v>314.85</v>
       </c>
     </row>
     <row r="39">
@@ -1608,7 +1608,7 @@
         <v>151</v>
       </c>
       <c r="E39">
-        <v>841.9</v>
+        <v>844.02</v>
       </c>
       <c r="F39">
         <v>102</v>
@@ -1620,7 +1620,7 @@
         <v>49</v>
       </c>
       <c r="I39">
-        <v>218.15</v>
+        <v>220.27</v>
       </c>
     </row>
     <row r="40">
@@ -1898,7 +1898,7 @@
         <v>295</v>
       </c>
       <c r="E49">
-        <v>2129.12</v>
+        <v>2129.51</v>
       </c>
       <c r="F49">
         <v>182</v>
@@ -1910,7 +1910,7 @@
         <v>113</v>
       </c>
       <c r="I49">
-        <v>641.22</v>
+        <v>641.61</v>
       </c>
     </row>
     <row r="50">
@@ -1927,7 +1927,7 @@
         <v>287</v>
       </c>
       <c r="E50">
-        <v>2135</v>
+        <v>2138.37</v>
       </c>
       <c r="F50">
         <v>180</v>
@@ -1939,7 +1939,7 @@
         <v>107</v>
       </c>
       <c r="I50">
-        <v>600.43</v>
+        <v>603.8</v>
       </c>
     </row>
     <row r="51">
@@ -1956,7 +1956,7 @@
         <v>284</v>
       </c>
       <c r="E51">
-        <v>2295.76</v>
+        <v>2297.39</v>
       </c>
       <c r="F51">
         <v>171</v>
@@ -1968,7 +1968,7 @@
         <v>113</v>
       </c>
       <c r="I51">
-        <v>696.75</v>
+        <v>698.38</v>
       </c>
     </row>
     <row r="52">
@@ -1985,7 +1985,7 @@
         <v>267</v>
       </c>
       <c r="E52">
-        <v>1953.94</v>
+        <v>1956.98</v>
       </c>
       <c r="F52">
         <v>167</v>
@@ -1997,7 +1997,7 @@
         <v>100</v>
       </c>
       <c r="I52">
-        <v>666.86</v>
+        <v>669.9</v>
       </c>
     </row>
     <row r="53">
@@ -2014,7 +2014,7 @@
         <v>288</v>
       </c>
       <c r="E53">
-        <v>2192.25</v>
+        <v>2192.79</v>
       </c>
       <c r="F53">
         <v>176</v>
@@ -2026,7 +2026,7 @@
         <v>112</v>
       </c>
       <c r="I53">
-        <v>709.68</v>
+        <v>710.22</v>
       </c>
     </row>
     <row r="54">
@@ -2040,34 +2040,150 @@
         <v>694</v>
       </c>
       <c r="D54">
-        <v>114</v>
+        <v>299</v>
       </c>
       <c r="E54">
-        <v>617.15</v>
+        <v>2096.49</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1441.58</v>
       </c>
       <c r="H54">
         <v>114</v>
       </c>
       <c r="I54">
-        <v>617.15</v>
+        <v>654.91</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <v>709</v>
+      </c>
+      <c r="D55">
+        <v>303</v>
+      </c>
+      <c r="E55">
+        <v>2158.96</v>
+      </c>
+      <c r="F55">
+        <v>177</v>
+      </c>
+      <c r="G55">
+        <v>1370.68</v>
+      </c>
+      <c r="H55">
+        <v>126</v>
+      </c>
+      <c r="I55">
+        <v>788.28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B56">
+        <v>27</v>
+      </c>
+      <c r="C56">
+        <v>736</v>
+      </c>
+      <c r="D56">
+        <v>313</v>
+      </c>
+      <c r="E56">
+        <v>2116.23</v>
+      </c>
+      <c r="F56">
+        <v>188</v>
+      </c>
+      <c r="G56">
+        <v>1379.78</v>
+      </c>
+      <c r="H56">
+        <v>125</v>
+      </c>
+      <c r="I56">
+        <v>736.45</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B57">
+        <v>22</v>
+      </c>
+      <c r="C57">
+        <v>758</v>
+      </c>
+      <c r="D57">
+        <v>321</v>
+      </c>
+      <c r="E57">
+        <v>2403.32</v>
+      </c>
+      <c r="F57">
+        <v>191</v>
+      </c>
+      <c r="G57">
+        <v>1655.65</v>
+      </c>
+      <c r="H57">
+        <v>130</v>
+      </c>
+      <c r="I57">
+        <v>747.67</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>770</v>
+      </c>
+      <c r="D58">
+        <v>141</v>
+      </c>
+      <c r="E58">
+        <v>817.05</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>141</v>
+      </c>
+      <c r="I58">
+        <v>817.05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I58"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G695"/>
+  <dimension ref="A1:G771"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2121,7 +2237,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G2" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="3">
@@ -2512,7 +2628,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G19" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="20">
@@ -2788,7 +2904,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G31" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="32">
@@ -3064,7 +3180,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G43" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="44">
@@ -3432,7 +3548,7 @@
         <v>王郡江</v>
       </c>
       <c r="G59" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="60">
@@ -3547,7 +3663,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G64" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="65">
@@ -3892,7 +4008,7 @@
         <v>王清月</v>
       </c>
       <c r="G79" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="80">
@@ -4122,7 +4238,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G89" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="90">
@@ -4513,7 +4629,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G106" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="107">
@@ -4674,7 +4790,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G113" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="114">
@@ -4697,7 +4813,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G114" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="115">
@@ -4743,7 +4859,7 @@
         <v>王涛</v>
       </c>
       <c r="G116" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="117">
@@ -4973,7 +5089,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G126" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="127">
@@ -5180,7 +5296,7 @@
         <v>王清月</v>
       </c>
       <c r="G135" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="136">
@@ -5479,7 +5595,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G148" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="149">
@@ -5709,7 +5825,7 @@
         <v>王郡江</v>
       </c>
       <c r="G158" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="159">
@@ -6077,7 +6193,7 @@
         <v>王清月</v>
       </c>
       <c r="G174" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="175">
@@ -6100,7 +6216,7 @@
         <v>王清月</v>
       </c>
       <c r="G175" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="176">
@@ -6238,7 +6354,7 @@
         <v>王清月</v>
       </c>
       <c r="G181" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="182">
@@ -6445,7 +6561,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G190" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="191">
@@ -6675,7 +6791,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G200" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="201">
@@ -7020,7 +7136,7 @@
         <v>王清月</v>
       </c>
       <c r="G215" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="216">
@@ -7135,7 +7251,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G220" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="221">
@@ -7181,7 +7297,7 @@
         <v>王涛</v>
       </c>
       <c r="G222" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="223">
@@ -7227,7 +7343,7 @@
         <v>王郡江</v>
       </c>
       <c r="G224" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="225">
@@ -7549,7 +7665,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G238" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="239">
@@ -7710,7 +7826,7 @@
         <v>王清月</v>
       </c>
       <c r="G245" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="246">
@@ -7802,7 +7918,7 @@
         <v>王涛</v>
       </c>
       <c r="G249" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="250">
@@ -8147,7 +8263,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G264" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="265">
@@ -8446,7 +8562,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G277" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="278">
@@ -8469,7 +8585,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G278" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="279">
@@ -8814,7 +8930,7 @@
         <v>王郡江</v>
       </c>
       <c r="G293" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="294">
@@ -8952,7 +9068,7 @@
         <v>王涛</v>
       </c>
       <c r="G299" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="300">
@@ -8975,7 +9091,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G300" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="301">
@@ -9320,7 +9436,7 @@
         <v>王清月</v>
       </c>
       <c r="G315" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="316">
@@ -9343,7 +9459,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G316" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="317">
@@ -9412,7 +9528,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G319" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="320">
@@ -9757,7 +9873,7 @@
         <v>王郡江</v>
       </c>
       <c r="G334" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="335">
@@ -9803,7 +9919,7 @@
         <v>王涛</v>
       </c>
       <c r="G336" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="337">
@@ -10102,7 +10218,7 @@
         <v>王涛</v>
       </c>
       <c r="G349" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="350">
@@ -10424,7 +10540,7 @@
         <v>王清月</v>
       </c>
       <c r="G363" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="364">
@@ -10953,7 +11069,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G386" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="387">
@@ -11068,7 +11184,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G391" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="392">
@@ -11091,7 +11207,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G392" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="393">
@@ -11206,7 +11322,7 @@
         <v>王涛</v>
       </c>
       <c r="G397" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="398">
@@ -11459,7 +11575,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G408" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="409">
@@ -11505,7 +11621,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G410" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="411">
@@ -11781,7 +11897,7 @@
         <v>王涛</v>
       </c>
       <c r="G422" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="423">
@@ -11896,7 +12012,7 @@
         <v>王郡江</v>
       </c>
       <c r="G427" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="428">
@@ -11988,7 +12104,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G431" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="432">
@@ -12264,7 +12380,7 @@
         <v>王清月</v>
       </c>
       <c r="G443" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="444">
@@ -12977,7 +13093,7 @@
         <v>王清月</v>
       </c>
       <c r="G474" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="475">
@@ -13069,7 +13185,7 @@
         <v>王清月</v>
       </c>
       <c r="G478" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="479">
@@ -13092,7 +13208,7 @@
         <v>王涛</v>
       </c>
       <c r="G479" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="480">
@@ -13253,7 +13369,7 @@
         <v>王清月</v>
       </c>
       <c r="G486" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="487">
@@ -13414,7 +13530,7 @@
         <v>王涛</v>
       </c>
       <c r="G493" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="494">
@@ -13460,7 +13576,7 @@
         <v>王涛</v>
       </c>
       <c r="G495" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="496">
@@ -13713,7 +13829,7 @@
         <v>王涛</v>
       </c>
       <c r="G506" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="507">
@@ -13874,7 +13990,7 @@
         <v>王郡江</v>
       </c>
       <c r="G513" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="514">
@@ -14150,7 +14266,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G525" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="526">
@@ -14322,7 +14438,7 @@
         <v>24901592</v>
       </c>
       <c r="C533" t="str">
-        <v>大碗面（河东一店）</v>
+        <v>左撇子·扛霸子面</v>
       </c>
       <c r="D533" t="str">
         <v>美团</v>
@@ -14357,7 +14473,7 @@
         <v>王涛</v>
       </c>
       <c r="G534" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="535">
@@ -14495,7 +14611,7 @@
         <v>王涛</v>
       </c>
       <c r="G540" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="541">
@@ -14518,7 +14634,7 @@
         <v>王涛</v>
       </c>
       <c r="G541" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="542">
@@ -14564,7 +14680,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G543" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="544">
@@ -14633,7 +14749,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G546" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="547">
@@ -14656,7 +14772,7 @@
         <v>王清月</v>
       </c>
       <c r="G547" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="548">
@@ -14679,7 +14795,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G548" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="549">
@@ -14725,7 +14841,7 @@
         <v>王郡江</v>
       </c>
       <c r="G550" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="551">
@@ -14748,7 +14864,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G551" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="552">
@@ -14771,7 +14887,7 @@
         <v>王郡江</v>
       </c>
       <c r="G552" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="553">
@@ -14817,7 +14933,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G554" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="555">
@@ -14840,7 +14956,7 @@
         <v>王郡江</v>
       </c>
       <c r="G555" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="556">
@@ -14909,7 +15025,7 @@
         <v>王涛</v>
       </c>
       <c r="G558" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="559">
@@ -14932,7 +15048,7 @@
         <v>王涛</v>
       </c>
       <c r="G559" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="560">
@@ -14955,7 +15071,7 @@
         <v>王郡江</v>
       </c>
       <c r="G560" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="561">
@@ -14978,7 +15094,7 @@
         <v>王涛</v>
       </c>
       <c r="G561" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="562">
@@ -15001,7 +15117,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G562" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="563">
@@ -15024,7 +15140,7 @@
         <v>王涛</v>
       </c>
       <c r="G563" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="564">
@@ -15047,7 +15163,7 @@
         <v>王郡江</v>
       </c>
       <c r="G564" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="565">
@@ -15093,7 +15209,7 @@
         <v>王郡江</v>
       </c>
       <c r="G566" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="567">
@@ -15116,7 +15232,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G567" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="568">
@@ -15139,7 +15255,7 @@
         <v>王郡江</v>
       </c>
       <c r="G568" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="569">
@@ -15162,7 +15278,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G569" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="570">
@@ -15208,7 +15324,7 @@
         <v>王清月</v>
       </c>
       <c r="G571" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="572">
@@ -15254,7 +15370,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G573" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="574">
@@ -15277,7 +15393,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G574" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="575">
@@ -15300,7 +15416,7 @@
         <v>王清月</v>
       </c>
       <c r="G575" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="576">
@@ -15323,7 +15439,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G576" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="577">
@@ -15346,7 +15462,7 @@
         <v>王清月</v>
       </c>
       <c r="G577" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="578">
@@ -15369,7 +15485,7 @@
         <v>王涛</v>
       </c>
       <c r="G578" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="579">
@@ -15392,7 +15508,7 @@
         <v>王郡江</v>
       </c>
       <c r="G579" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="580">
@@ -15415,7 +15531,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G580" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="581">
@@ -15438,7 +15554,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G581" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="582">
@@ -15461,7 +15577,7 @@
         <v>王涛</v>
       </c>
       <c r="G582" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="583">
@@ -15530,7 +15646,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G585" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="586">
@@ -15553,7 +15669,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G586" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="587">
@@ -15576,7 +15692,7 @@
         <v>王清月</v>
       </c>
       <c r="G587" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="588">
@@ -15599,7 +15715,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G588" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="589">
@@ -15622,7 +15738,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G589" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="590">
@@ -15645,7 +15761,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G590" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="591">
@@ -15668,7 +15784,7 @@
         <v>王清月</v>
       </c>
       <c r="G591" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="592">
@@ -15691,7 +15807,7 @@
         <v>王涛</v>
       </c>
       <c r="G592" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="593">
@@ -15714,7 +15830,7 @@
         <v>王清月</v>
       </c>
       <c r="G593" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="594">
@@ -15737,7 +15853,7 @@
         <v>王郡江</v>
       </c>
       <c r="G594" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="595">
@@ -15760,7 +15876,7 @@
         <v>王清月</v>
       </c>
       <c r="G595" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="596">
@@ -15783,7 +15899,7 @@
         <v>王涛</v>
       </c>
       <c r="G596" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="597">
@@ -15806,7 +15922,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G597" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="598">
@@ -15829,7 +15945,7 @@
         <v>王郡江</v>
       </c>
       <c r="G598" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="599">
@@ -15852,7 +15968,7 @@
         <v>王清月</v>
       </c>
       <c r="G599" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="600">
@@ -15875,7 +15991,7 @@
         <v>王涛</v>
       </c>
       <c r="G600" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="601">
@@ -15898,7 +16014,7 @@
         <v>王清月</v>
       </c>
       <c r="G601" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="602">
@@ -15921,7 +16037,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G602" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="603">
@@ -15944,7 +16060,7 @@
         <v>王郡江</v>
       </c>
       <c r="G603" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="604">
@@ -15967,7 +16083,7 @@
         <v>王涛</v>
       </c>
       <c r="G604" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="605">
@@ -15990,7 +16106,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G605" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="606">
@@ -16013,7 +16129,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G606" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="607">
@@ -16036,7 +16152,7 @@
         <v>王郡江</v>
       </c>
       <c r="G607" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="608">
@@ -16059,7 +16175,7 @@
         <v>王涛</v>
       </c>
       <c r="G608" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="609">
@@ -16082,7 +16198,7 @@
         <v>王涛</v>
       </c>
       <c r="G609" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="610">
@@ -16105,7 +16221,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G610" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="611">
@@ -16128,7 +16244,7 @@
         <v>王郡江</v>
       </c>
       <c r="G611" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="612">
@@ -16151,7 +16267,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G612" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="613">
@@ -16174,7 +16290,7 @@
         <v>王清月</v>
       </c>
       <c r="G613" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="614">
@@ -16197,7 +16313,7 @@
         <v>王涛</v>
       </c>
       <c r="G614" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="615">
@@ -16220,7 +16336,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G615" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="616">
@@ -16243,7 +16359,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G616" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="617">
@@ -16289,7 +16405,7 @@
         <v>王清月</v>
       </c>
       <c r="G618" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="619">
@@ -16312,7 +16428,7 @@
         <v>王涛</v>
       </c>
       <c r="G619" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="620">
@@ -16335,7 +16451,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G620" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="621">
@@ -16358,7 +16474,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G621" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="622">
@@ -16404,7 +16520,7 @@
         <v>王郡江</v>
       </c>
       <c r="G623" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="624">
@@ -16427,7 +16543,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G624" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="625">
@@ -16450,7 +16566,7 @@
         <v>王清月</v>
       </c>
       <c r="G625" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="626">
@@ -16473,7 +16589,7 @@
         <v>王涛</v>
       </c>
       <c r="G626" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="627">
@@ -16496,7 +16612,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G627" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="628">
@@ -16542,7 +16658,7 @@
         <v>王郡江</v>
       </c>
       <c r="G629" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="630">
@@ -16565,7 +16681,7 @@
         <v>王涛</v>
       </c>
       <c r="G630" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="631">
@@ -16588,7 +16704,7 @@
         <v>王清月</v>
       </c>
       <c r="G631" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="632">
@@ -16634,7 +16750,7 @@
         <v>王清月</v>
       </c>
       <c r="G633" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="634">
@@ -16657,7 +16773,7 @@
         <v>王清月</v>
       </c>
       <c r="G634" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="635">
@@ -16680,7 +16796,7 @@
         <v>王清月</v>
       </c>
       <c r="G635" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="636">
@@ -16933,7 +17049,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G646" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="647">
@@ -17140,7 +17256,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G655" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="656">
@@ -17324,7 +17440,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G663" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="664">
@@ -17427,7 +17543,7 @@
         <v>542841840</v>
       </c>
       <c r="C668" t="str">
-        <v>乐山钵钵鸡(平和堂店)</v>
+        <v>乐山钵钵鸡(手工冰粉）(平和堂店)</v>
       </c>
       <c r="D668" t="str">
         <v>饿了么</v>
@@ -18063,9 +18179,1757 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B696" t="str">
+        <v>541582377</v>
+      </c>
+      <c r="C696" t="str">
+        <v>遇稻手作饭团(思北店)</v>
+      </c>
+      <c r="D696" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E696" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F696" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G696" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B697" t="str">
+        <v>32670098</v>
+      </c>
+      <c r="C697" t="str">
+        <v>遇稻手作饭团(思北店)</v>
+      </c>
+      <c r="D697" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E697" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F697" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G697" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B698" t="str">
+        <v>1338049914</v>
+      </c>
+      <c r="C698" t="str">
+        <v>马明旺·麻辣冷吃</v>
+      </c>
+      <c r="D698" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E698" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F698" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G698" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B699" t="str">
+        <v>32653580</v>
+      </c>
+      <c r="C699" t="str">
+        <v>马明旺麻辣冷吃</v>
+      </c>
+      <c r="D699" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E699" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F699" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G699" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B700" t="str">
+        <v>1340365797</v>
+      </c>
+      <c r="C700" t="str">
+        <v>寻香记炸串集(四中店)</v>
+      </c>
+      <c r="D700" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E700" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F700" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G700" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B701" t="str">
+        <v>542557010</v>
+      </c>
+      <c r="C701" t="str">
+        <v>暮夜烧烤</v>
+      </c>
+      <c r="D701" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E701" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F701" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G701" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B702" t="str">
+        <v>32513971</v>
+      </c>
+      <c r="C702" t="str">
+        <v>老面手工大包</v>
+      </c>
+      <c r="D702" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E702" t="str">
+        <v>汪双</v>
+      </c>
+      <c r="F702" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G702" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B703" t="str">
+        <v>543117469</v>
+      </c>
+      <c r="C703" t="str">
+        <v>彭姐炸串铁板烧(高新店)</v>
+      </c>
+      <c r="D703" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E703" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F703" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G703" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B704" t="str">
+        <v>543403891</v>
+      </c>
+      <c r="C704" t="str">
+        <v>状元卷饼(前山店)</v>
+      </c>
+      <c r="D704" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E704" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F704" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G704" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B705" t="str">
+        <v>32729555</v>
+      </c>
+      <c r="C705" t="str">
+        <v>食惠小厨馆</v>
+      </c>
+      <c r="D705" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E705" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F705" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G705" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B706" t="str">
+        <v>32583229</v>
+      </c>
+      <c r="C706" t="str">
+        <v>王家碗拌炮仗烤肉</v>
+      </c>
+      <c r="D706" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E706" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F706" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G706" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B707" t="str">
+        <v>31660905</v>
+      </c>
+      <c r="C707" t="str">
+        <v>暮云间</v>
+      </c>
+      <c r="D707" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E707" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F707" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G707" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B708" t="str">
+        <v>30099195</v>
+      </c>
+      <c r="C708" t="str">
+        <v>王宝强黄焖鸡米饭</v>
+      </c>
+      <c r="D708" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E708" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F708" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G708" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B709" t="str">
+        <v>1334026003</v>
+      </c>
+      <c r="C709" t="str">
+        <v>王宝强黄焖鸡米饭(华池山水国际店)</v>
+      </c>
+      <c r="D709" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E709" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F709" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G709" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B710" t="str">
+        <v>32306711</v>
+      </c>
+      <c r="C710" t="str">
+        <v>三哥烤面筋</v>
+      </c>
+      <c r="D710" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E710" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F710" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G710" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B711" t="str">
+        <v>542780899</v>
+      </c>
+      <c r="C711" t="str">
+        <v>喜古·现烧鸡公煲</v>
+      </c>
+      <c r="D711" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E711" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F711" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G711" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B712" t="str">
+        <v>1338905099</v>
+      </c>
+      <c r="C712" t="str">
+        <v>搞一碗七（早餐·面食）</v>
+      </c>
+      <c r="D712" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E712" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F712" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G712" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B713" t="str">
+        <v>543058201</v>
+      </c>
+      <c r="C713" t="str">
+        <v>韩大叔炸鸡·拌饭</v>
+      </c>
+      <c r="D713" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E713" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F713" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G713" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B714" t="str">
+        <v>32733531</v>
+      </c>
+      <c r="C714" t="str">
+        <v>禾肴饭堂自选餐</v>
+      </c>
+      <c r="D714" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E714" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F714" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G714" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B715" t="str">
+        <v>1328572858</v>
+      </c>
+      <c r="C715" t="str">
+        <v>隆江猪脚饭</v>
+      </c>
+      <c r="D715" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E715" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F715" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G715" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B716" t="str">
+        <v>32552966</v>
+      </c>
+      <c r="C716" t="str">
+        <v>隆江猪脚饭（金联村店）</v>
+      </c>
+      <c r="D716" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E716" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F716" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G716" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B717" t="str">
+        <v>1337842220</v>
+      </c>
+      <c r="C717" t="str">
+        <v>文潮苑·潮汕砂锅粥(恩施店)</v>
+      </c>
+      <c r="D717" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E717" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F717" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G717" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B718" t="str">
+        <v>32482028</v>
+      </c>
+      <c r="C718" t="str">
+        <v>文潮苑·潮汕砂锅粥（恩施店）</v>
+      </c>
+      <c r="D718" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E718" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F718" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G718" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B719" t="str">
+        <v>32430145</v>
+      </c>
+      <c r="C719" t="str">
+        <v>嗨野热卤</v>
+      </c>
+      <c r="D719" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E719" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F719" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G719" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B720" t="str">
+        <v>32792632</v>
+      </c>
+      <c r="C720" t="str">
+        <v>黄三爷炒饭•炒粉</v>
+      </c>
+      <c r="D720" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E720" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F720" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G720" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B721" t="str">
+        <v>32713552</v>
+      </c>
+      <c r="C721" t="str">
+        <v>君来顺面馆</v>
+      </c>
+      <c r="D721" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E721" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F721" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G721" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B722" t="str">
+        <v>1338890636</v>
+      </c>
+      <c r="C722" t="str">
+        <v>贵州砂锅粉·炒饭·盖浇饭</v>
+      </c>
+      <c r="D722" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E722" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F722" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G722" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B723" t="str">
+        <v>32530876</v>
+      </c>
+      <c r="C723" t="str">
+        <v>方家淮南牛肉汤（梁园区店）</v>
+      </c>
+      <c r="D723" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E723" t="str">
+        <v>屈维涛</v>
+      </c>
+      <c r="F723" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G723" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B724" t="str">
+        <v>1338077637</v>
+      </c>
+      <c r="C724" t="str">
+        <v>明厨煲仔饭</v>
+      </c>
+      <c r="D724" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E724" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F724" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G724" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B725" t="str">
+        <v>1340386537</v>
+      </c>
+      <c r="C725" t="str">
+        <v>牛牛站酸辣粉</v>
+      </c>
+      <c r="D725" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E725" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F725" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G725" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B726" t="str">
+        <v>542775317</v>
+      </c>
+      <c r="C726" t="str">
+        <v>御扇窑鸡(安居店)</v>
+      </c>
+      <c r="D726" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E726" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F726" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G726" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B727" t="str">
+        <v>32568928</v>
+      </c>
+      <c r="C727" t="str">
+        <v>御扇窑鸡（安居店）</v>
+      </c>
+      <c r="D727" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E727" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F727" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G727" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B728" t="str">
+        <v>32614555</v>
+      </c>
+      <c r="C728" t="str">
+        <v>贵州羊肉粉（大烟囱店）</v>
+      </c>
+      <c r="D728" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E728" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F728" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G728" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B729" t="str">
+        <v>32457055</v>
+      </c>
+      <c r="C729" t="str">
+        <v>爱尚榴莲芝士饼烤榴莲</v>
+      </c>
+      <c r="D729" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E729" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F729" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G729" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B730" t="str">
+        <v>1337288798</v>
+      </c>
+      <c r="C730" t="str">
+        <v>爱尚榴莲芝士饼烤榴莲</v>
+      </c>
+      <c r="D730" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E730" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F730" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G730" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B731" t="str">
+        <v>32626779</v>
+      </c>
+      <c r="C731" t="str">
+        <v>饺饺者</v>
+      </c>
+      <c r="D731" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E731" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F731" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G731" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B732" t="str">
+        <v>1338980454</v>
+      </c>
+      <c r="C732" t="str">
+        <v>饺饺者</v>
+      </c>
+      <c r="D732" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E732" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F732" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G732" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B733" t="str">
+        <v>32694984</v>
+      </c>
+      <c r="C733" t="str">
+        <v>美缘美食</v>
+      </c>
+      <c r="D733" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E733" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F733" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G733" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B734" t="str">
+        <v>542620297</v>
+      </c>
+      <c r="C734" t="str">
+        <v>方家淮南牛肉汤</v>
+      </c>
+      <c r="D734" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E734" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F734" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G734" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B735" t="str">
+        <v>1340153586</v>
+      </c>
+      <c r="C735" t="str">
+        <v>园园包子</v>
+      </c>
+      <c r="D735" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E735" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F735" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G735" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B736" t="str">
+        <v>32341192</v>
+      </c>
+      <c r="C736" t="str">
+        <v>园园大包（阿尔勒店）</v>
+      </c>
+      <c r="D736" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E736" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F736" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G736" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B737" t="str">
+        <v>32409452</v>
+      </c>
+      <c r="C737" t="str">
+        <v>巷子披萨（漯河店）</v>
+      </c>
+      <c r="D737" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E737" t="str">
+        <v>朱雯雯</v>
+      </c>
+      <c r="F737" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G737" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B738" t="str">
+        <v>31244842</v>
+      </c>
+      <c r="C738" t="str">
+        <v>川香婆麻辣烫米线（学院店）</v>
+      </c>
+      <c r="D738" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E738" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F738" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G738" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B739" t="str">
+        <v>32396611</v>
+      </c>
+      <c r="C739" t="str">
+        <v>欧丽披萨</v>
+      </c>
+      <c r="D739" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E739" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F739" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G739" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B740" t="str">
+        <v>542525847</v>
+      </c>
+      <c r="C740" t="str">
+        <v>屉屉鲜·正宗杭州小笼包</v>
+      </c>
+      <c r="D740" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E740" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F740" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G740" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B741" t="str">
+        <v>32148554</v>
+      </c>
+      <c r="C741" t="str">
+        <v>屉屉鲜·正宗杭州小笼包</v>
+      </c>
+      <c r="D741" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E741" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F741" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G741" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B742" t="str">
+        <v>31843999</v>
+      </c>
+      <c r="C742" t="str">
+        <v>幸·烩融会餐厅</v>
+      </c>
+      <c r="D742" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E742" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F742" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G742" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B743" t="str">
+        <v>542782561</v>
+      </c>
+      <c r="C743" t="str">
+        <v>瑶妹子·湘菜小炒(宜昌店)</v>
+      </c>
+      <c r="D743" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E743" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F743" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G743" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B744" t="str">
+        <v>32151730</v>
+      </c>
+      <c r="C744" t="str">
+        <v>骨汤皇猪杂粉</v>
+      </c>
+      <c r="D744" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E744" t="str">
+        <v>李嘉辉</v>
+      </c>
+      <c r="F744" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G744" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B745" t="str">
+        <v>542608571</v>
+      </c>
+      <c r="C745" t="str">
+        <v>龙氏骨汤皇猪杂粉</v>
+      </c>
+      <c r="D745" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E745" t="str">
+        <v>李嘉辉</v>
+      </c>
+      <c r="F745" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G745" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B746" t="str">
+        <v>32411461</v>
+      </c>
+      <c r="C746" t="str">
+        <v>潮汕老牌手工面</v>
+      </c>
+      <c r="D746" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E746" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F746" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G746" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B747" t="str">
+        <v>31176092</v>
+      </c>
+      <c r="C747" t="str">
+        <v>炊烟袅袅一惹味馆</v>
+      </c>
+      <c r="D747" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E747" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F747" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G747" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B748" t="str">
+        <v>32662119</v>
+      </c>
+      <c r="C748" t="str">
+        <v>炭烤先生</v>
+      </c>
+      <c r="D748" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E748" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F748" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G748" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B749" t="str">
+        <v>32770587</v>
+      </c>
+      <c r="C749" t="str">
+        <v>新疆艾力烧烤（固戍店）</v>
+      </c>
+      <c r="D749" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E749" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F749" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G749" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B750" t="str">
+        <v>32696748</v>
+      </c>
+      <c r="C750" t="str">
+        <v>以勒肉饼</v>
+      </c>
+      <c r="D750" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E750" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F750" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G750" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B751" t="str">
+        <v>32785404</v>
+      </c>
+      <c r="C751" t="str">
+        <v>不误整夜</v>
+      </c>
+      <c r="D751" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E751" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F751" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G751" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B752" t="str">
+        <v>1340386537</v>
+      </c>
+      <c r="C752" t="str">
+        <v>牛牛站酸辣粉</v>
+      </c>
+      <c r="D752" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E752" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F752" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G752" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B753" t="str">
+        <v>541333838</v>
+      </c>
+      <c r="C753" t="str">
+        <v>幸烩融合餐厅</v>
+      </c>
+      <c r="D753" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E753" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F753" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G753" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B754" t="str">
+        <v>32430267</v>
+      </c>
+      <c r="C754" t="str">
+        <v>烤吧</v>
+      </c>
+      <c r="D754" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E754" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F754" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G754" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B755" t="str">
+        <v>1334030543</v>
+      </c>
+      <c r="C755" t="str">
+        <v>可以烤吧</v>
+      </c>
+      <c r="D755" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E755" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F755" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G755" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B756" t="str">
+        <v>32550136</v>
+      </c>
+      <c r="C756" t="str">
+        <v>艳霞大排粉面馆</v>
+      </c>
+      <c r="D756" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E756" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F756" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G756" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B757" t="str">
+        <v>542640786</v>
+      </c>
+      <c r="C757" t="str">
+        <v>清真·黄焖鸡·拌面·炒面·米饭·椒麻鸡</v>
+      </c>
+      <c r="D757" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E757" t="str">
+        <v>肖锐</v>
+      </c>
+      <c r="F757" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G757" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B758" t="str">
+        <v>32484261</v>
+      </c>
+      <c r="C758" t="str">
+        <v>遵义羊肉粉快餐店</v>
+      </c>
+      <c r="D758" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E758" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F758" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G758" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="B759" t="str">
+        <v>1331457097</v>
+      </c>
+      <c r="C759" t="str">
+        <v>贵州特产·黔川风味铺</v>
+      </c>
+      <c r="D759" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E759" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F759" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G759" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B760" t="str">
+        <v>26323356</v>
+      </c>
+      <c r="C760" t="str">
+        <v>贾记甏肉干饭</v>
+      </c>
+      <c r="D760" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E760" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F760" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G760" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B761" t="str">
+        <v>32703173</v>
+      </c>
+      <c r="C761" t="str">
+        <v>黄果树破酥包</v>
+      </c>
+      <c r="D761" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E761" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F761" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G761" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B762" t="str">
+        <v>32420233</v>
+      </c>
+      <c r="C762" t="str">
+        <v>瑶妹子·湘菜小炒</v>
+      </c>
+      <c r="D762" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E762" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F762" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G762" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B763" t="str">
+        <v>543398294</v>
+      </c>
+      <c r="C763" t="str">
+        <v>北京片皮烤鸭(龙岗店)</v>
+      </c>
+      <c r="D763" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E763" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F763" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G763" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B764" t="str">
+        <v>32405423</v>
+      </c>
+      <c r="C764" t="str">
+        <v>牛马弟兄盖饭（花果园店）</v>
+      </c>
+      <c r="D764" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E764" t="str">
+        <v>李嘉辉</v>
+      </c>
+      <c r="F764" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G764" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B765" t="str">
+        <v>31407283</v>
+      </c>
+      <c r="C765" t="str">
+        <v>天津老味烧烤</v>
+      </c>
+      <c r="D765" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E765" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F765" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G765" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B766" t="str">
+        <v>32591661</v>
+      </c>
+      <c r="C766" t="str">
+        <v>OTTO轻食简餐</v>
+      </c>
+      <c r="D766" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E766" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F766" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G766" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B767" t="str">
+        <v>32531192</v>
+      </c>
+      <c r="C767" t="str">
+        <v>润记一口汤包•小笼包•水煎包（春柳店）</v>
+      </c>
+      <c r="D767" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E767" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F767" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G767" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B768" t="str">
+        <v>1339068229</v>
+      </c>
+      <c r="C768" t="str">
+        <v>麻辣鲜生·三文鱼·生腌捞汁小海鲜</v>
+      </c>
+      <c r="D768" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E768" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F768" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G768" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B769" t="str">
+        <v>1341990965</v>
+      </c>
+      <c r="C769" t="str">
+        <v>艳霞大排粉面馆</v>
+      </c>
+      <c r="D769" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E769" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F769" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G769" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B770" t="str">
+        <v>32473259</v>
+      </c>
+      <c r="C770" t="str">
+        <v>虾忙小龙虾</v>
+      </c>
+      <c r="D770" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E770" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F770" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G770" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="B771" t="str">
+        <v>542286326</v>
+      </c>
+      <c r="C771" t="str">
+        <v>炸锅幸会·砂锅土豆粉·酥香炸货(平等小区店)</v>
+      </c>
+      <c r="D771" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E771" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F771" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G771" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G695"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G771"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18099,7 +19963,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-22 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-26 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-30</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>770</v>
+        <v>866</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>56895.82000000001</v>
+        <v>66881.19000000002</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>7980</v>
+        <v>9348</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/4/27 10:19:00</v>
+        <v>2026/5/1 10:15:51</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I62"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1376,7 +1376,7 @@
         <v>127</v>
       </c>
       <c r="E31">
-        <v>910.95</v>
+        <v>912.3</v>
       </c>
       <c r="F31">
         <v>84</v>
@@ -1388,7 +1388,7 @@
         <v>43</v>
       </c>
       <c r="I31">
-        <v>195.41</v>
+        <v>196.76</v>
       </c>
     </row>
     <row r="32">
@@ -1434,7 +1434,7 @@
         <v>154</v>
       </c>
       <c r="E33">
-        <v>1052.6</v>
+        <v>1053.88</v>
       </c>
       <c r="F33">
         <v>107</v>
@@ -1446,7 +1446,7 @@
         <v>47</v>
       </c>
       <c r="I33">
-        <v>273.5</v>
+        <v>274.78</v>
       </c>
     </row>
     <row r="34">
@@ -1521,7 +1521,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>1047.89</v>
+        <v>1049.28</v>
       </c>
       <c r="F36">
         <v>101</v>
@@ -1533,7 +1533,7 @@
         <v>57</v>
       </c>
       <c r="I36">
-        <v>305.25</v>
+        <v>306.64</v>
       </c>
     </row>
     <row r="37">
@@ -1550,7 +1550,7 @@
         <v>145</v>
       </c>
       <c r="E37">
-        <v>1183.39</v>
+        <v>1192.62</v>
       </c>
       <c r="F37">
         <v>95</v>
@@ -1562,7 +1562,7 @@
         <v>50</v>
       </c>
       <c r="I37">
-        <v>339.23</v>
+        <v>348.46</v>
       </c>
     </row>
     <row r="38">
@@ -1579,7 +1579,7 @@
         <v>154</v>
       </c>
       <c r="E38">
-        <v>1149.63</v>
+        <v>1153.11</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -1591,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="I38">
-        <v>314.85</v>
+        <v>318.33</v>
       </c>
     </row>
     <row r="39">
@@ -1637,7 +1637,7 @@
         <v>175</v>
       </c>
       <c r="E40">
-        <v>1200.37</v>
+        <v>1201.86</v>
       </c>
       <c r="F40">
         <v>119</v>
@@ -1649,7 +1649,7 @@
         <v>56</v>
       </c>
       <c r="I40">
-        <v>288.45</v>
+        <v>289.94</v>
       </c>
     </row>
     <row r="41">
@@ -1666,7 +1666,7 @@
         <v>194</v>
       </c>
       <c r="E41">
-        <v>1295.45</v>
+        <v>1299.68</v>
       </c>
       <c r="F41">
         <v>126</v>
@@ -1678,7 +1678,7 @@
         <v>68</v>
       </c>
       <c r="I41">
-        <v>377.02</v>
+        <v>381.25</v>
       </c>
     </row>
     <row r="42">
@@ -1753,7 +1753,7 @@
         <v>244</v>
       </c>
       <c r="E44">
-        <v>1919.76</v>
+        <v>1920.89</v>
       </c>
       <c r="F44">
         <v>154</v>
@@ -1765,7 +1765,7 @@
         <v>90</v>
       </c>
       <c r="I44">
-        <v>470.31</v>
+        <v>471.44</v>
       </c>
     </row>
     <row r="45">
@@ -1811,7 +1811,7 @@
         <v>252</v>
       </c>
       <c r="E46">
-        <v>1756.64</v>
+        <v>1767.83</v>
       </c>
       <c r="F46">
         <v>155</v>
@@ -1823,7 +1823,7 @@
         <v>97</v>
       </c>
       <c r="I46">
-        <v>525.71</v>
+        <v>536.9</v>
       </c>
     </row>
     <row r="47">
@@ -1840,7 +1840,7 @@
         <v>258</v>
       </c>
       <c r="E47">
-        <v>1802.09</v>
+        <v>1805.14</v>
       </c>
       <c r="F47">
         <v>162</v>
@@ -1852,7 +1852,7 @@
         <v>96</v>
       </c>
       <c r="I47">
-        <v>623.3</v>
+        <v>626.35</v>
       </c>
     </row>
     <row r="48">
@@ -1869,7 +1869,7 @@
         <v>271</v>
       </c>
       <c r="E48">
-        <v>1926.24</v>
+        <v>1927.69</v>
       </c>
       <c r="F48">
         <v>163</v>
@@ -1881,7 +1881,7 @@
         <v>108</v>
       </c>
       <c r="I48">
-        <v>575.76</v>
+        <v>577.21</v>
       </c>
     </row>
     <row r="49">
@@ -1898,7 +1898,7 @@
         <v>295</v>
       </c>
       <c r="E49">
-        <v>2129.51</v>
+        <v>2132.08</v>
       </c>
       <c r="F49">
         <v>182</v>
@@ -1910,7 +1910,7 @@
         <v>113</v>
       </c>
       <c r="I49">
-        <v>641.61</v>
+        <v>644.18</v>
       </c>
     </row>
     <row r="50">
@@ -1927,7 +1927,7 @@
         <v>287</v>
       </c>
       <c r="E50">
-        <v>2138.37</v>
+        <v>2139.91</v>
       </c>
       <c r="F50">
         <v>180</v>
@@ -1939,7 +1939,7 @@
         <v>107</v>
       </c>
       <c r="I50">
-        <v>603.8</v>
+        <v>605.34</v>
       </c>
     </row>
     <row r="51">
@@ -1956,7 +1956,7 @@
         <v>284</v>
       </c>
       <c r="E51">
-        <v>2297.39</v>
+        <v>2302.29</v>
       </c>
       <c r="F51">
         <v>171</v>
@@ -1968,7 +1968,7 @@
         <v>113</v>
       </c>
       <c r="I51">
-        <v>698.38</v>
+        <v>703.28</v>
       </c>
     </row>
     <row r="52">
@@ -1985,7 +1985,7 @@
         <v>267</v>
       </c>
       <c r="E52">
-        <v>1956.98</v>
+        <v>1959.93</v>
       </c>
       <c r="F52">
         <v>167</v>
@@ -1997,7 +1997,7 @@
         <v>100</v>
       </c>
       <c r="I52">
-        <v>669.9</v>
+        <v>672.85</v>
       </c>
     </row>
     <row r="53">
@@ -2014,7 +2014,7 @@
         <v>288</v>
       </c>
       <c r="E53">
-        <v>2192.79</v>
+        <v>2195.16</v>
       </c>
       <c r="F53">
         <v>176</v>
@@ -2026,7 +2026,7 @@
         <v>112</v>
       </c>
       <c r="I53">
-        <v>710.22</v>
+        <v>712.59</v>
       </c>
     </row>
     <row r="54">
@@ -2043,7 +2043,7 @@
         <v>299</v>
       </c>
       <c r="E54">
-        <v>2096.49</v>
+        <v>2106.09</v>
       </c>
       <c r="F54">
         <v>185</v>
@@ -2055,7 +2055,7 @@
         <v>114</v>
       </c>
       <c r="I54">
-        <v>654.91</v>
+        <v>664.51</v>
       </c>
     </row>
     <row r="55">
@@ -2072,7 +2072,7 @@
         <v>303</v>
       </c>
       <c r="E55">
-        <v>2158.96</v>
+        <v>2164.04</v>
       </c>
       <c r="F55">
         <v>177</v>
@@ -2084,7 +2084,7 @@
         <v>126</v>
       </c>
       <c r="I55">
-        <v>788.28</v>
+        <v>793.36</v>
       </c>
     </row>
     <row r="56">
@@ -2101,7 +2101,7 @@
         <v>313</v>
       </c>
       <c r="E56">
-        <v>2116.23</v>
+        <v>2124.73</v>
       </c>
       <c r="F56">
         <v>188</v>
@@ -2113,7 +2113,7 @@
         <v>125</v>
       </c>
       <c r="I56">
-        <v>736.45</v>
+        <v>744.95</v>
       </c>
     </row>
     <row r="57">
@@ -2130,7 +2130,7 @@
         <v>321</v>
       </c>
       <c r="E57">
-        <v>2403.32</v>
+        <v>2415.75</v>
       </c>
       <c r="F57">
         <v>191</v>
@@ -2142,7 +2142,7 @@
         <v>130</v>
       </c>
       <c r="I57">
-        <v>747.67</v>
+        <v>760.1</v>
       </c>
     </row>
     <row r="58">
@@ -2156,34 +2156,150 @@
         <v>770</v>
       </c>
       <c r="D58">
-        <v>141</v>
+        <v>337</v>
       </c>
       <c r="E58">
-        <v>817.05</v>
+        <v>2716.57</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1786.74</v>
       </c>
       <c r="H58">
         <v>141</v>
       </c>
       <c r="I58">
-        <v>817.05</v>
+        <v>929.83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B59">
+        <v>17</v>
+      </c>
+      <c r="C59">
+        <v>787</v>
+      </c>
+      <c r="D59">
+        <v>327</v>
+      </c>
+      <c r="E59">
+        <v>2307.54</v>
+      </c>
+      <c r="F59">
+        <v>189</v>
+      </c>
+      <c r="G59">
+        <v>1427.65</v>
+      </c>
+      <c r="H59">
+        <v>138</v>
+      </c>
+      <c r="I59">
+        <v>879.89</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B60">
+        <v>25</v>
+      </c>
+      <c r="C60">
+        <v>812</v>
+      </c>
+      <c r="D60">
+        <v>355</v>
+      </c>
+      <c r="E60">
+        <v>2481.8</v>
+      </c>
+      <c r="F60">
+        <v>207</v>
+      </c>
+      <c r="G60">
+        <v>1541.04</v>
+      </c>
+      <c r="H60">
+        <v>148</v>
+      </c>
+      <c r="I60">
+        <v>940.76</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B61">
+        <v>28</v>
+      </c>
+      <c r="C61">
+        <v>840</v>
+      </c>
+      <c r="D61">
+        <v>346</v>
+      </c>
+      <c r="E61">
+        <v>2459.3</v>
+      </c>
+      <c r="F61">
+        <v>207</v>
+      </c>
+      <c r="G61">
+        <v>1580.44</v>
+      </c>
+      <c r="H61">
+        <v>139</v>
+      </c>
+      <c r="I61">
+        <v>878.86</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B62">
+        <v>26</v>
+      </c>
+      <c r="C62">
+        <v>866</v>
+      </c>
+      <c r="D62">
+        <v>144</v>
+      </c>
+      <c r="E62">
+        <v>748</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>144</v>
+      </c>
+      <c r="I62">
+        <v>748</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I62"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G771"/>
+  <dimension ref="A1:G867"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3548,7 +3664,7 @@
         <v>王郡江</v>
       </c>
       <c r="G59" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="60">
@@ -3663,7 +3779,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G64" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="65">
@@ -3686,7 +3802,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G65" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="66">
@@ -3709,7 +3825,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G66" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="67">
@@ -3732,7 +3848,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G67" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="68">
@@ -3824,7 +3940,7 @@
         <v>王涛</v>
       </c>
       <c r="G71" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="72">
@@ -3985,7 +4101,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G78" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="79">
@@ -4238,7 +4354,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G89" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="90">
@@ -4364,7 +4480,7 @@
         <v>32107973</v>
       </c>
       <c r="C95" t="str">
-        <v>土家鲜肉饼（穆堂路店）</v>
+        <v>土家鲜肉饼</v>
       </c>
       <c r="D95" t="str">
         <v>美团</v>
@@ -4376,7 +4492,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G95" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="96">
@@ -4560,7 +4676,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G103" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="104">
@@ -4652,7 +4768,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G107" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="108">
@@ -4882,7 +4998,7 @@
         <v>王清月</v>
       </c>
       <c r="G117" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="118">
@@ -5595,7 +5711,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G148" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="149">
@@ -5618,7 +5734,7 @@
         <v>王郡江</v>
       </c>
       <c r="G149" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="150">
@@ -5687,7 +5803,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G152" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="153">
@@ -5894,7 +6010,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G161" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="162">
@@ -6170,7 +6286,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G173" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="174">
@@ -6193,7 +6309,7 @@
         <v>王清月</v>
       </c>
       <c r="G174" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="175">
@@ -6354,7 +6470,7 @@
         <v>王清月</v>
       </c>
       <c r="G181" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="182">
@@ -6607,7 +6723,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G192" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="193">
@@ -6630,7 +6746,7 @@
         <v>王清月</v>
       </c>
       <c r="G193" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="194">
@@ -6768,7 +6884,7 @@
         <v>王郡江</v>
       </c>
       <c r="G199" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="200">
@@ -7044,7 +7160,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G211" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="212">
@@ -7366,7 +7482,7 @@
         <v>王涛</v>
       </c>
       <c r="G225" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="226">
@@ -7619,7 +7735,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G236" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="237">
@@ -7757,7 +7873,7 @@
         <v>王郡江</v>
       </c>
       <c r="G242" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="243">
@@ -7780,7 +7896,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G243" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="244">
@@ -7826,7 +7942,7 @@
         <v>王清月</v>
       </c>
       <c r="G245" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="246">
@@ -8079,7 +8195,7 @@
         <v>王涛</v>
       </c>
       <c r="G256" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="257">
@@ -8263,7 +8379,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G264" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="265">
@@ -8332,7 +8448,7 @@
         <v>王郡江</v>
       </c>
       <c r="G267" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="268">
@@ -8355,7 +8471,7 @@
         <v>王郡江</v>
       </c>
       <c r="G268" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="269">
@@ -8539,7 +8655,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G276" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="277">
@@ -8562,7 +8678,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G277" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="278">
@@ -8585,7 +8701,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G278" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="279">
@@ -8700,7 +8816,7 @@
         <v>王涛</v>
       </c>
       <c r="G283" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="284">
@@ -8953,7 +9069,7 @@
         <v>王涛</v>
       </c>
       <c r="G294" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="295">
@@ -9022,7 +9138,7 @@
         <v>王清月</v>
       </c>
       <c r="G297" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="298">
@@ -9091,7 +9207,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G300" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="301">
@@ -9827,7 +9943,7 @@
         <v>王清月</v>
       </c>
       <c r="G332" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="333">
@@ -9919,7 +10035,7 @@
         <v>王涛</v>
       </c>
       <c r="G336" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="337">
@@ -10218,7 +10334,7 @@
         <v>王涛</v>
       </c>
       <c r="G349" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="350">
@@ -10333,7 +10449,7 @@
         <v>王郡江</v>
       </c>
       <c r="G354" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="355">
@@ -10540,7 +10656,7 @@
         <v>王清月</v>
       </c>
       <c r="G363" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="364">
@@ -11215,7 +11331,7 @@
         <v>2026-04-07</v>
       </c>
       <c r="B393" t="str">
-        <v>32448291</v>
+        <v>1337300909</v>
       </c>
       <c r="C393" t="str">
         <v>东北大叔麻辣烫</v>
@@ -11230,7 +11346,7 @@
         <v>王郡江</v>
       </c>
       <c r="G393" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="394">
@@ -11253,7 +11369,7 @@
         <v>王清月</v>
       </c>
       <c r="G394" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="395">
@@ -11322,7 +11438,7 @@
         <v>王涛</v>
       </c>
       <c r="G397" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="398">
@@ -12012,7 +12128,7 @@
         <v>王郡江</v>
       </c>
       <c r="G427" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="428">
@@ -12035,7 +12151,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G428" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="429">
@@ -12058,7 +12174,7 @@
         <v>王涛</v>
       </c>
       <c r="G429" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="430">
@@ -12104,7 +12220,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G431" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="432">
@@ -12173,7 +12289,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G434" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="435">
@@ -12357,7 +12473,7 @@
         <v>王清月</v>
       </c>
       <c r="G442" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="443">
@@ -12403,7 +12519,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G444" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="445">
@@ -12702,7 +12818,7 @@
         <v>王清月</v>
       </c>
       <c r="G457" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="458">
@@ -12725,7 +12841,7 @@
         <v>王清月</v>
       </c>
       <c r="G458" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="459">
@@ -13093,7 +13209,7 @@
         <v>王清月</v>
       </c>
       <c r="G474" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="475">
@@ -13530,7 +13646,7 @@
         <v>王涛</v>
       </c>
       <c r="G493" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="494">
@@ -14013,7 +14129,7 @@
         <v>王郡江</v>
       </c>
       <c r="G514" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="515">
@@ -14059,7 +14175,7 @@
         <v>王郡江</v>
       </c>
       <c r="G516" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="517">
@@ -14174,7 +14290,7 @@
         <v>王郡江</v>
       </c>
       <c r="G521" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="522">
@@ -14243,7 +14359,7 @@
         <v>王郡江</v>
       </c>
       <c r="G524" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="525">
@@ -14565,7 +14681,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G538" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="539">
@@ -14956,7 +15072,7 @@
         <v>王郡江</v>
       </c>
       <c r="G555" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="556">
@@ -15002,7 +15118,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G557" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="558">
@@ -15186,7 +15302,7 @@
         <v>王清月</v>
       </c>
       <c r="G565" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="566">
@@ -15209,7 +15325,7 @@
         <v>王郡江</v>
       </c>
       <c r="G566" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="567">
@@ -15232,7 +15348,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G567" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="568">
@@ -15646,7 +15762,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G585" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="586">
@@ -15991,7 +16107,7 @@
         <v>王涛</v>
       </c>
       <c r="G600" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="601">
@@ -16244,7 +16360,7 @@
         <v>王郡江</v>
       </c>
       <c r="G611" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="612">
@@ -16359,7 +16475,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G616" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="617">
@@ -16635,7 +16751,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G628" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="629">
@@ -16658,7 +16774,7 @@
         <v>王郡江</v>
       </c>
       <c r="G629" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="630">
@@ -16727,7 +16843,7 @@
         <v>王涛</v>
       </c>
       <c r="G632" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="633">
@@ -16796,7 +16912,7 @@
         <v>王清月</v>
       </c>
       <c r="G635" t="str">
-        <v>已解约</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="636">
@@ -16819,7 +16935,7 @@
         <v>王涛</v>
       </c>
       <c r="G636" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="637">
@@ -16842,7 +16958,7 @@
         <v>王涛</v>
       </c>
       <c r="G637" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="638">
@@ -16865,7 +16981,7 @@
         <v>王涛</v>
       </c>
       <c r="G638" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="639">
@@ -16888,7 +17004,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G639" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="640">
@@ -16911,7 +17027,7 @@
         <v>王郡江</v>
       </c>
       <c r="G640" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="641">
@@ -16934,7 +17050,7 @@
         <v>王涛</v>
       </c>
       <c r="G641" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="642">
@@ -16957,7 +17073,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G642" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="643">
@@ -16980,7 +17096,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G643" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="644">
@@ -17003,7 +17119,7 @@
         <v>王涛</v>
       </c>
       <c r="G644" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="645">
@@ -17026,7 +17142,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G645" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="646">
@@ -17049,7 +17165,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G646" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="647">
@@ -17072,7 +17188,7 @@
         <v>王郡江</v>
       </c>
       <c r="G647" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="648">
@@ -17095,7 +17211,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G648" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="649">
@@ -17118,7 +17234,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G649" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="650">
@@ -17141,7 +17257,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G650" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="651">
@@ -17164,7 +17280,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G651" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="652">
@@ -17187,7 +17303,7 @@
         <v>王涛</v>
       </c>
       <c r="G652" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="653">
@@ -17210,7 +17326,7 @@
         <v>王涛</v>
       </c>
       <c r="G653" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="654">
@@ -17233,7 +17349,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G654" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="655">
@@ -17279,7 +17395,7 @@
         <v>王清月</v>
       </c>
       <c r="G656" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="657">
@@ -17302,7 +17418,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G657" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="658">
@@ -17325,7 +17441,7 @@
         <v>王涛</v>
       </c>
       <c r="G658" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="659">
@@ -17348,7 +17464,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G659" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="660">
@@ -17371,7 +17487,7 @@
         <v>王清月</v>
       </c>
       <c r="G660" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="661">
@@ -17394,7 +17510,7 @@
         <v>王涛</v>
       </c>
       <c r="G661" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="662">
@@ -17417,7 +17533,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G662" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="663">
@@ -17463,7 +17579,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G664" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="665">
@@ -17486,7 +17602,7 @@
         <v>王清月</v>
       </c>
       <c r="G665" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="666">
@@ -17509,7 +17625,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G666" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="667">
@@ -17532,7 +17648,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G667" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="668">
@@ -17555,7 +17671,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G668" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="669">
@@ -17578,7 +17694,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G669" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="670">
@@ -17601,7 +17717,7 @@
         <v>王清月</v>
       </c>
       <c r="G670" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="671">
@@ -17624,7 +17740,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G671" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="672">
@@ -17647,7 +17763,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G672" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="673">
@@ -17693,7 +17809,7 @@
         <v>王涛</v>
       </c>
       <c r="G674" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="675">
@@ -17716,7 +17832,7 @@
         <v>王清月</v>
       </c>
       <c r="G675" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="676">
@@ -17739,7 +17855,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G676" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="677">
@@ -17785,7 +17901,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G678" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="679">
@@ -17808,7 +17924,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G679" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="680">
@@ -17831,7 +17947,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G680" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="681">
@@ -17877,7 +17993,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G682" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="683">
@@ -17923,7 +18039,7 @@
         <v>王清月</v>
       </c>
       <c r="G684" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="685">
@@ -18015,7 +18131,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G688" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="689">
@@ -18084,7 +18200,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G691" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="692">
@@ -18337,7 +18453,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G702" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="703">
@@ -18544,7 +18660,7 @@
         <v>王涛</v>
       </c>
       <c r="G711" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="712">
@@ -18575,22 +18691,22 @@
         <v>2026-04-24</v>
       </c>
       <c r="B713" t="str">
-        <v>543058201</v>
+        <v>32733531</v>
       </c>
       <c r="C713" t="str">
-        <v>韩大叔炸鸡·拌饭</v>
+        <v>禾肴饭堂自选餐</v>
       </c>
       <c r="D713" t="str">
-        <v>饿了么</v>
+        <v>美团</v>
       </c>
       <c r="E713" t="str">
         <v>韩大武</v>
       </c>
       <c r="F713" t="str">
-        <v>张玉莲</v>
+        <v>杨有淇</v>
       </c>
       <c r="G713" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="714">
@@ -18598,19 +18714,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B714" t="str">
-        <v>32733531</v>
+        <v>543058201</v>
       </c>
       <c r="C714" t="str">
-        <v>禾肴饭堂自选餐</v>
+        <v>韩大叔炸鸡·拌饭</v>
       </c>
       <c r="D714" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E714" t="str">
-        <v>韩大武</v>
+        <v>柯松</v>
       </c>
       <c r="F714" t="str">
-        <v>杨有淇</v>
+        <v>张玉莲</v>
       </c>
       <c r="G714" t="str">
         <v>新店</v>
@@ -18774,7 +18890,7 @@
         <v>王清月</v>
       </c>
       <c r="G721" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="722">
@@ -18805,16 +18921,16 @@
         <v>2026-04-24</v>
       </c>
       <c r="B723" t="str">
-        <v>32530876</v>
+        <v>1338077637</v>
       </c>
       <c r="C723" t="str">
-        <v>方家淮南牛肉汤（梁园区店）</v>
+        <v>明厨煲仔饭</v>
       </c>
       <c r="D723" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E723" t="str">
-        <v>屈维涛</v>
+        <v>吴销</v>
       </c>
       <c r="F723" t="str">
         <v>王涛</v>
@@ -18828,10 +18944,10 @@
         <v>2026-04-24</v>
       </c>
       <c r="B724" t="str">
-        <v>1338077637</v>
+        <v>1340386537</v>
       </c>
       <c r="C724" t="str">
-        <v>明厨煲仔饭</v>
+        <v>牛牛站酸辣粉</v>
       </c>
       <c r="D724" t="str">
         <v>饿了么</v>
@@ -18840,10 +18956,10 @@
         <v>吴销</v>
       </c>
       <c r="F724" t="str">
-        <v>王涛</v>
+        <v>杨有淇</v>
       </c>
       <c r="G724" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="725">
@@ -18851,10 +18967,10 @@
         <v>2026-04-24</v>
       </c>
       <c r="B725" t="str">
-        <v>1340386537</v>
+        <v>542775317</v>
       </c>
       <c r="C725" t="str">
-        <v>牛牛站酸辣粉</v>
+        <v>御扇窑鸡(安居店)</v>
       </c>
       <c r="D725" t="str">
         <v>饿了么</v>
@@ -18866,7 +18982,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G725" t="str">
-        <v>已解约</v>
+        <v>新店</v>
       </c>
     </row>
     <row r="726">
@@ -18874,19 +18990,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B726" t="str">
-        <v>542775317</v>
+        <v>32568928</v>
       </c>
       <c r="C726" t="str">
-        <v>御扇窑鸡(安居店)</v>
+        <v>御扇窑鸡（安居店）</v>
       </c>
       <c r="D726" t="str">
-        <v>饿了么</v>
+        <v>美团</v>
       </c>
       <c r="E726" t="str">
         <v>吴销</v>
       </c>
       <c r="F726" t="str">
-        <v>杨有淇</v>
+        <v>王涛</v>
       </c>
       <c r="G726" t="str">
         <v>新店</v>
@@ -18897,19 +19013,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B727" t="str">
-        <v>32568928</v>
+        <v>32614555</v>
       </c>
       <c r="C727" t="str">
-        <v>御扇窑鸡（安居店）</v>
+        <v>贵州羊肉粉（大烟囱店）</v>
       </c>
       <c r="D727" t="str">
         <v>美团</v>
       </c>
       <c r="E727" t="str">
-        <v>吴销</v>
+        <v>武力力</v>
       </c>
       <c r="F727" t="str">
-        <v>王涛</v>
+        <v>张玉莲</v>
       </c>
       <c r="G727" t="str">
         <v>新店</v>
@@ -18920,16 +19036,16 @@
         <v>2026-04-24</v>
       </c>
       <c r="B728" t="str">
-        <v>32614555</v>
+        <v>32457055</v>
       </c>
       <c r="C728" t="str">
-        <v>贵州羊肉粉（大烟囱店）</v>
+        <v>爱尚榴莲芝士饼烤榴莲</v>
       </c>
       <c r="D728" t="str">
         <v>美团</v>
       </c>
       <c r="E728" t="str">
-        <v>武力力</v>
+        <v>杨译博</v>
       </c>
       <c r="F728" t="str">
         <v>张玉莲</v>
@@ -18943,19 +19059,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B729" t="str">
-        <v>32457055</v>
+        <v>1337288798</v>
       </c>
       <c r="C729" t="str">
         <v>爱尚榴莲芝士饼烤榴莲</v>
       </c>
       <c r="D729" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E729" t="str">
         <v>杨译博</v>
       </c>
       <c r="F729" t="str">
-        <v>张玉莲</v>
+        <v>袁丽妮</v>
       </c>
       <c r="G729" t="str">
         <v>新店</v>
@@ -18966,19 +19082,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B730" t="str">
-        <v>1337288798</v>
+        <v>32626779</v>
       </c>
       <c r="C730" t="str">
-        <v>爱尚榴莲芝士饼烤榴莲</v>
+        <v>饺饺者</v>
       </c>
       <c r="D730" t="str">
-        <v>饿了么</v>
+        <v>美团</v>
       </c>
       <c r="E730" t="str">
         <v>杨译博</v>
       </c>
       <c r="F730" t="str">
-        <v>袁丽妮</v>
+        <v>王涛</v>
       </c>
       <c r="G730" t="str">
         <v>新店</v>
@@ -18989,19 +19105,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B731" t="str">
-        <v>32626779</v>
+        <v>1338980454</v>
       </c>
       <c r="C731" t="str">
         <v>饺饺者</v>
       </c>
       <c r="D731" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E731" t="str">
         <v>杨译博</v>
       </c>
       <c r="F731" t="str">
-        <v>王涛</v>
+        <v>杨有淇</v>
       </c>
       <c r="G731" t="str">
         <v>新店</v>
@@ -19012,19 +19128,19 @@
         <v>2026-04-24</v>
       </c>
       <c r="B732" t="str">
-        <v>1338980454</v>
+        <v>32694984</v>
       </c>
       <c r="C732" t="str">
-        <v>饺饺者</v>
+        <v>美缘美食</v>
       </c>
       <c r="D732" t="str">
-        <v>饿了么</v>
+        <v>美团</v>
       </c>
       <c r="E732" t="str">
         <v>杨译博</v>
       </c>
       <c r="F732" t="str">
-        <v>杨有淇</v>
+        <v>张玉莲</v>
       </c>
       <c r="G732" t="str">
         <v>新店</v>
@@ -19035,22 +19151,22 @@
         <v>2026-04-24</v>
       </c>
       <c r="B733" t="str">
-        <v>32694984</v>
+        <v>542620297</v>
       </c>
       <c r="C733" t="str">
-        <v>美缘美食</v>
+        <v>方家淮南牛肉汤</v>
       </c>
       <c r="D733" t="str">
-        <v>美团</v>
+        <v>饿了么</v>
       </c>
       <c r="E733" t="str">
-        <v>杨译博</v>
+        <v>张兴岚</v>
       </c>
       <c r="F733" t="str">
         <v>张玉莲</v>
       </c>
       <c r="G733" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="734">
@@ -19058,22 +19174,22 @@
         <v>2026-04-24</v>
       </c>
       <c r="B734" t="str">
-        <v>542620297</v>
+        <v>32530876</v>
       </c>
       <c r="C734" t="str">
-        <v>方家淮南牛肉汤</v>
+        <v>方家淮南牛肉汤（梁园区店）</v>
       </c>
       <c r="D734" t="str">
-        <v>饿了么</v>
+        <v>美团</v>
       </c>
       <c r="E734" t="str">
         <v>张兴岚</v>
       </c>
       <c r="F734" t="str">
-        <v>张玉莲</v>
+        <v>王涛</v>
       </c>
       <c r="G734" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="735">
@@ -19418,7 +19534,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G749" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="750">
@@ -19472,7 +19588,7 @@
         <v>2026-04-25</v>
       </c>
       <c r="B752" t="str">
-        <v>1340386537</v>
+        <v>32712677</v>
       </c>
       <c r="C752" t="str">
         <v>牛牛站酸辣粉</v>
@@ -19625,7 +19741,7 @@
         <v>张玉莲</v>
       </c>
       <c r="G758" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="759">
@@ -19740,7 +19856,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G763" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="764">
@@ -19901,7 +20017,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G770" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="771">
@@ -19927,9 +20043,2217 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B772" t="str">
+        <v>543027067</v>
+      </c>
+      <c r="C772" t="str">
+        <v>饿了么26/4.27虾掌门·龙虾馆 8%</v>
+      </c>
+      <c r="D772" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E772" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F772" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G772" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B773" t="str">
+        <v>32620114</v>
+      </c>
+      <c r="C773" t="str">
+        <v>虾掌门龙虾馆</v>
+      </c>
+      <c r="D773" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E773" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F773" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G773" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B774" t="str">
+        <v>32423023</v>
+      </c>
+      <c r="C774" t="str">
+        <v>小俩口麻酱麻辣烫</v>
+      </c>
+      <c r="D774" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E774" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F774" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G774" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B775" t="str">
+        <v>1338069984</v>
+      </c>
+      <c r="C775" t="str">
+        <v>赣小坤·江西小炒(定海店)</v>
+      </c>
+      <c r="D775" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E775" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F775" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G775" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B776" t="str">
+        <v>536471478</v>
+      </c>
+      <c r="C776" t="str">
+        <v>陈记破包子(碧桂园店）</v>
+      </c>
+      <c r="D776" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E776" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F776" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G776" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B777" t="str">
+        <v>542696711</v>
+      </c>
+      <c r="C777" t="str">
+        <v>正阳剁椒烤面筋</v>
+      </c>
+      <c r="D777" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E777" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F777" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G777" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B778" t="str">
+        <v>32589215</v>
+      </c>
+      <c r="C778" t="str">
+        <v>正阳剁椒烤面筋</v>
+      </c>
+      <c r="D778" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E778" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F778" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G778" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B779" t="str">
+        <v>32684360</v>
+      </c>
+      <c r="C779" t="str">
+        <v>阿东兄弟龙虾</v>
+      </c>
+      <c r="D779" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E779" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F779" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G779" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B780" t="str">
+        <v>1340304771</v>
+      </c>
+      <c r="C780" t="str">
+        <v>阿东兄弟龙虾(灯塔工业区店)</v>
+      </c>
+      <c r="D780" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E780" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F780" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G780" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B781" t="str">
+        <v>1340331112</v>
+      </c>
+      <c r="C781" t="str">
+        <v>巷口咖喱·煲仔饭(新理工大店)</v>
+      </c>
+      <c r="D781" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E781" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F781" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G781" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B782" t="str">
+        <v>32597950</v>
+      </c>
+      <c r="C782" t="str">
+        <v>巷口咖喱煲仔饭</v>
+      </c>
+      <c r="D782" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E782" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F782" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G782" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B783" t="str">
+        <v>32546499</v>
+      </c>
+      <c r="C783" t="str">
+        <v>新疆阿大西羊肉串烧烤</v>
+      </c>
+      <c r="D783" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E783" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F783" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G783" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B784" t="str">
+        <v>2076465685</v>
+      </c>
+      <c r="C784" t="str">
+        <v>重庆川味园(大营村店)</v>
+      </c>
+      <c r="D784" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E784" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F784" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G784" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B785" t="str">
+        <v>32529291</v>
+      </c>
+      <c r="C785" t="str">
+        <v>兰州拉面（巢湖路店）</v>
+      </c>
+      <c r="D785" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E785" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F785" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G785" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B786" t="str">
+        <v>32702990</v>
+      </c>
+      <c r="C786" t="str">
+        <v>和州小笼包（四方路店）</v>
+      </c>
+      <c r="D786" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E786" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F786" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G786" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B787" t="str">
+        <v>32802387</v>
+      </c>
+      <c r="C787" t="str">
+        <v>乐山二妹油炸串串</v>
+      </c>
+      <c r="D787" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E787" t="str">
+        <v>朱雯雯</v>
+      </c>
+      <c r="F787" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G787" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="B788" t="str">
+        <v>1341979615</v>
+      </c>
+      <c r="C788" t="str">
+        <v>乐山二妹油炸串串</v>
+      </c>
+      <c r="D788" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E788" t="str">
+        <v>朱雯雯</v>
+      </c>
+      <c r="F788" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G788" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B789" t="str">
+        <v>542301673</v>
+      </c>
+      <c r="C789" t="str">
+        <v>田记口福饼</v>
+      </c>
+      <c r="D789" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E789" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F789" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G789" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B790" t="str">
+        <v>1315317237</v>
+      </c>
+      <c r="C790" t="str">
+        <v>香襄湘煲仔饭</v>
+      </c>
+      <c r="D790" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E790" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F790" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G790" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B791" t="str">
+        <v>1327932092</v>
+      </c>
+      <c r="C791" t="str">
+        <v>藏书龙虾(世家万达店)</v>
+      </c>
+      <c r="D791" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E791" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F791" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G791" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B792" t="str">
+        <v>32449028</v>
+      </c>
+      <c r="C792" t="str">
+        <v>炭火江湖音乐烤吧</v>
+      </c>
+      <c r="D792" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E792" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F792" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G792" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B793" t="str">
+        <v>543028187</v>
+      </c>
+      <c r="C793" t="str">
+        <v>御龙蟹盱眙小龙虾(领秀城店)</v>
+      </c>
+      <c r="D793" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E793" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F793" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G793" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B794" t="str">
+        <v>1337282471</v>
+      </c>
+      <c r="C794" t="str">
+        <v>万缘手工水饺</v>
+      </c>
+      <c r="D794" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E794" t="str">
+        <v>柯松</v>
+      </c>
+      <c r="F794" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G794" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B795" t="str">
+        <v>32425624</v>
+      </c>
+      <c r="C795" t="str">
+        <v>四季乳鸽</v>
+      </c>
+      <c r="D795" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E795" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F795" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G795" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B796" t="str">
+        <v>542992094</v>
+      </c>
+      <c r="C796" t="str">
+        <v>芝士火鸡烤冷面</v>
+      </c>
+      <c r="D796" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E796" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F796" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G796" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B797" t="str">
+        <v>32203637</v>
+      </c>
+      <c r="C797" t="str">
+        <v>牛魔王超大牛肉串</v>
+      </c>
+      <c r="D797" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E797" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F797" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G797" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B798" t="str">
+        <v>1337285267</v>
+      </c>
+      <c r="C798" t="str">
+        <v>润记·一口汤包·小笼包·水煎包</v>
+      </c>
+      <c r="D798" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E798" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F798" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G798" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B799" t="str">
+        <v>1340957899</v>
+      </c>
+      <c r="C799" t="str">
+        <v>食惠小厨馆</v>
+      </c>
+      <c r="D799" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E799" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F799" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G799" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B800" t="str">
+        <v>1340335911</v>
+      </c>
+      <c r="C800" t="str">
+        <v>宋先生风味炸肉</v>
+      </c>
+      <c r="D800" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E800" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F800" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G800" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B801" t="str">
+        <v>32623773</v>
+      </c>
+      <c r="C801" t="str">
+        <v>宋先生风味炸肉（炸串）</v>
+      </c>
+      <c r="D801" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E801" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F801" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G801" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B802" t="str">
+        <v>1337309214</v>
+      </c>
+      <c r="C802" t="str">
+        <v>仙尝·桂林米粉</v>
+      </c>
+      <c r="D802" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E802" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F802" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G802" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B803" t="str">
+        <v>32750697</v>
+      </c>
+      <c r="C803" t="str">
+        <v>手撕大排骨(大排骨)</v>
+      </c>
+      <c r="D803" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E803" t="str">
+        <v>肖锐</v>
+      </c>
+      <c r="F803" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G803" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B804" t="str">
+        <v>32808149</v>
+      </c>
+      <c r="C804" t="str">
+        <v>潮汕鲜牛肉粿条</v>
+      </c>
+      <c r="D804" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E804" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F804" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G804" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B805" t="str">
+        <v>543515369</v>
+      </c>
+      <c r="C805" t="str">
+        <v>忱哥玩味(金融港店)</v>
+      </c>
+      <c r="D805" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E805" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F805" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G805" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B806" t="str">
+        <v>32773745</v>
+      </c>
+      <c r="C806" t="str">
+        <v>忱哥玩味（烧肉饭，小龙虾）</v>
+      </c>
+      <c r="D806" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E806" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F806" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G806" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B807" t="str">
+        <v>32688355</v>
+      </c>
+      <c r="C807" t="str">
+        <v>酱板卤菜（光谷店）</v>
+      </c>
+      <c r="D807" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E807" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F807" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G807" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B808" t="str">
+        <v>32741575</v>
+      </c>
+      <c r="C808" t="str">
+        <v>柳螺源（新生街店）</v>
+      </c>
+      <c r="D808" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E808" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F808" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G808" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B809" t="str">
+        <v>32785768</v>
+      </c>
+      <c r="C809" t="str">
+        <v>王记三鲜豆皮</v>
+      </c>
+      <c r="D809" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E809" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F809" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G809" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B810" t="str">
+        <v>543236718</v>
+      </c>
+      <c r="C810" t="str">
+        <v>王记三鲜豆皮(武大广八路店)</v>
+      </c>
+      <c r="D810" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E810" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F810" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G810" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B811" t="str">
+        <v>517765155</v>
+      </c>
+      <c r="C811" t="str">
+        <v>衢州鸭头·现卤现卖领先一步(宜陵店)</v>
+      </c>
+      <c r="D811" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E811" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F811" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G811" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B812" t="str">
+        <v>32568178</v>
+      </c>
+      <c r="C812" t="str">
+        <v>湖南芷江鸭子粉</v>
+      </c>
+      <c r="D812" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E812" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F812" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G812" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="B813" t="str">
+        <v>32553166</v>
+      </c>
+      <c r="C813" t="str">
+        <v>小黄记盖饭</v>
+      </c>
+      <c r="D813" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E813" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F813" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G813" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B814" t="str">
+        <v>1335756022</v>
+      </c>
+      <c r="C814" t="str">
+        <v>东北老式麻辣烫炸串</v>
+      </c>
+      <c r="D814" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E814" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F814" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G814" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B815" t="str">
+        <v>530018962</v>
+      </c>
+      <c r="C815" t="str">
+        <v>老上海馄饨铺(江南御花园店)</v>
+      </c>
+      <c r="D815" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E815" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F815" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G815" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B816" t="str">
+        <v>32365326</v>
+      </c>
+      <c r="C816" t="str">
+        <v>老上海馄饨铺（江南御花园店）</v>
+      </c>
+      <c r="D816" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E816" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F816" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G816" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B817" t="str">
+        <v>32540605</v>
+      </c>
+      <c r="C817" t="str">
+        <v>元蒸香正宗潜江小龙虾</v>
+      </c>
+      <c r="D817" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E817" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F817" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G817" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B818" t="str">
+        <v>26030515</v>
+      </c>
+      <c r="C818" t="str">
+        <v>大飞烧烤</v>
+      </c>
+      <c r="D818" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E818" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F818" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G818" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B819" t="str">
+        <v>31950551</v>
+      </c>
+      <c r="C819" t="str">
+        <v>井屿串烧</v>
+      </c>
+      <c r="D819" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E819" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F819" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G819" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B820" t="str">
+        <v>515015530</v>
+      </c>
+      <c r="C820" t="str">
+        <v>兰州牛肉面(万达店)</v>
+      </c>
+      <c r="D820" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E820" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F820" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G820" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B821" t="str">
+        <v>20371236</v>
+      </c>
+      <c r="C821" t="str">
+        <v>兰州牛肉面（万达店）</v>
+      </c>
+      <c r="D821" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E821" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F821" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G821" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B822" t="str">
+        <v>32838176</v>
+      </c>
+      <c r="C822" t="str">
+        <v>巷口砂锅粉</v>
+      </c>
+      <c r="D822" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E822" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F822" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G822" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B823" t="str">
+        <v>32593712</v>
+      </c>
+      <c r="C823" t="str">
+        <v>东北菜铁锅炖饺子馆（炒菜.盖饭）</v>
+      </c>
+      <c r="D823" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E823" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F823" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G823" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B824" t="str">
+        <v>543061227</v>
+      </c>
+      <c r="C824" t="str">
+        <v>给你画个饼·的唔昂(台头店)</v>
+      </c>
+      <c r="D824" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E824" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F824" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G824" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B825" t="str">
+        <v>32601564</v>
+      </c>
+      <c r="C825" t="str">
+        <v>给你画个饼（的唔昂台头店）</v>
+      </c>
+      <c r="D825" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E825" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F825" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G825" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B826" t="str">
+        <v>32272057</v>
+      </c>
+      <c r="C826" t="str">
+        <v>三时便当</v>
+      </c>
+      <c r="D826" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E826" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F826" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G826" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B827" t="str">
+        <v>1337299788</v>
+      </c>
+      <c r="C827" t="str">
+        <v>树下烧烤大排档</v>
+      </c>
+      <c r="D827" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E827" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F827" t="str">
+        <v>张玉莲</v>
+      </c>
+      <c r="G827" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B828" t="str">
+        <v>32494969</v>
+      </c>
+      <c r="C828" t="str">
+        <v>树下烧烤大排档</v>
+      </c>
+      <c r="D828" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E828" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F828" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G828" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B829" t="str">
+        <v>32798440</v>
+      </c>
+      <c r="C829" t="str">
+        <v>温卤知香</v>
+      </c>
+      <c r="D829" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E829" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F829" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G829" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B830" t="str">
+        <v>32717086</v>
+      </c>
+      <c r="C830" t="str">
+        <v>熊氏龙虾王(兴华路店)</v>
+      </c>
+      <c r="D830" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E830" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F830" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G830" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B831" t="str">
+        <v>32698550</v>
+      </c>
+      <c r="C831" t="str">
+        <v>杨家军卤味</v>
+      </c>
+      <c r="D831" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E831" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F831" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G831" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B832" t="str">
+        <v>32316650</v>
+      </c>
+      <c r="C832" t="str">
+        <v>御品小龙虾</v>
+      </c>
+      <c r="D832" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E832" t="str">
+        <v>屈维涛</v>
+      </c>
+      <c r="F832" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G832" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B833" t="str">
+        <v>32662518</v>
+      </c>
+      <c r="C833" t="str">
+        <v>桃姐餐饮（炒菜·蒸菜）</v>
+      </c>
+      <c r="D833" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E833" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F833" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G833" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B834" t="str">
+        <v>31584584</v>
+      </c>
+      <c r="C834" t="str">
+        <v>华毅粉店</v>
+      </c>
+      <c r="D834" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E834" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F834" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G834" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B835" t="str">
+        <v>542460090</v>
+      </c>
+      <c r="C835" t="str">
+        <v>华毅粉店</v>
+      </c>
+      <c r="D835" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E835" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F835" t="str">
+        <v>袁丽妮</v>
+      </c>
+      <c r="G835" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B836" t="str">
+        <v>32730484</v>
+      </c>
+      <c r="C836" t="str">
+        <v>阿许汤包（鸣阳路店）</v>
+      </c>
+      <c r="D836" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E836" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F836" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G836" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B837" t="str">
+        <v>543495484</v>
+      </c>
+      <c r="C837" t="str">
+        <v>台湾盐酥鸡炭烤鸡排</v>
+      </c>
+      <c r="D837" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E837" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F837" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G837" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B838" t="str">
+        <v>32791800</v>
+      </c>
+      <c r="C838" t="str">
+        <v>盐酥鸡碳烤大鸡排</v>
+      </c>
+      <c r="D838" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E838" t="str">
+        <v>杨译博</v>
+      </c>
+      <c r="F838" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G838" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B839" t="str">
+        <v>29599271</v>
+      </c>
+      <c r="C839" t="str">
+        <v>一品香烤鸭(宿舍店)</v>
+      </c>
+      <c r="D839" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E839" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F839" t="str">
+        <v>王清月</v>
+      </c>
+      <c r="G839" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B840" t="str">
+        <v>1329553747</v>
+      </c>
+      <c r="C840" t="str">
+        <v>螺味鲜·螺蛳粉</v>
+      </c>
+      <c r="D840" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E840" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F840" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G840" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="B841" t="str">
+        <v>19212950</v>
+      </c>
+      <c r="C841" t="str">
+        <v>衢州鸭头（公道店）</v>
+      </c>
+      <c r="D841" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E841" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F841" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G841" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B842" t="str">
+        <v>32365326</v>
+      </c>
+      <c r="C842" t="str">
+        <v>老上海馄饨铺（江南御花园店）</v>
+      </c>
+      <c r="D842" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E842" t="str">
+        <v>陈冉</v>
+      </c>
+      <c r="F842" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G842" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B843" t="str">
+        <v>32752792</v>
+      </c>
+      <c r="C843" t="str">
+        <v>鼠大厨炸货铺</v>
+      </c>
+      <c r="D843" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E843" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F843" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G843" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B844" t="str">
+        <v>1341012771</v>
+      </c>
+      <c r="C844" t="str">
+        <v>鼠大厨炸货铺(红旗路店)</v>
+      </c>
+      <c r="D844" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E844" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F844" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G844" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B845" t="str">
+        <v>32652587</v>
+      </c>
+      <c r="C845" t="str">
+        <v>土家鲜肉饼</v>
+      </c>
+      <c r="D845" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E845" t="str">
+        <v>韩大武</v>
+      </c>
+      <c r="F845" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G845" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B846" t="str">
+        <v>32768954</v>
+      </c>
+      <c r="C846" t="str">
+        <v>不蒸馒头蒸口气</v>
+      </c>
+      <c r="D846" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E846" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F846" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G846" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B847" t="str">
+        <v>30905935</v>
+      </c>
+      <c r="C847" t="str">
+        <v>假日碳火烧烤</v>
+      </c>
+      <c r="D847" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E847" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F847" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G847" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B848" t="str">
+        <v>32784991</v>
+      </c>
+      <c r="C848" t="str">
+        <v>虾享美味小龙虾</v>
+      </c>
+      <c r="D848" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E848" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F848" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G848" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B849" t="str">
+        <v>1340386821</v>
+      </c>
+      <c r="C849" t="str">
+        <v>川香味老盒饭</v>
+      </c>
+      <c r="D849" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E849" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F849" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G849" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B850" t="str">
+        <v>32739610</v>
+      </c>
+      <c r="C850" t="str">
+        <v>川香味老盒饭</v>
+      </c>
+      <c r="D850" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E850" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F850" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G850" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B851" t="str">
+        <v>32503567</v>
+      </c>
+      <c r="C851" t="str">
+        <v>赣小坤江西小炒</v>
+      </c>
+      <c r="D851" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E851" t="str">
+        <v>秦金城</v>
+      </c>
+      <c r="F851" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G851" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B852" t="str">
+        <v>510929032</v>
+      </c>
+      <c r="C852" t="str">
+        <v>就晓得吃(边城店)</v>
+      </c>
+      <c r="D852" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E852" t="str">
+        <v>吴销</v>
+      </c>
+      <c r="F852" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G852" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B853" t="str">
+        <v>542288280</v>
+      </c>
+      <c r="C853" t="str">
+        <v>重庆面馆(南职店)</v>
+      </c>
+      <c r="D853" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E853" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F853" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G853" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B854" t="str">
+        <v>32594849</v>
+      </c>
+      <c r="C854" t="str">
+        <v>奇缘麻辣烫米线</v>
+      </c>
+      <c r="D854" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E854" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F854" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G854" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B855" t="str">
+        <v>32672215</v>
+      </c>
+      <c r="C855" t="str">
+        <v>鸭天下·卤菜鸭货</v>
+      </c>
+      <c r="D855" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E855" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F855" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G855" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B856" t="str">
+        <v>542838026</v>
+      </c>
+      <c r="C856" t="str">
+        <v>鸭天下·卤菜鸭货</v>
+      </c>
+      <c r="D856" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E856" t="str">
+        <v>武力力</v>
+      </c>
+      <c r="F856" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G856" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B857" t="str">
+        <v>542834695</v>
+      </c>
+      <c r="C857" t="str">
+        <v>重庆瘦肉丸子包(临钢店)</v>
+      </c>
+      <c r="D857" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E857" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F857" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G857" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B858" t="str">
+        <v>32640632</v>
+      </c>
+      <c r="C858" t="str">
+        <v>袁麟记小吃</v>
+      </c>
+      <c r="D858" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E858" t="str">
+        <v>向文强</v>
+      </c>
+      <c r="F858" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G858" t="str">
+        <v>已解约</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B859" t="str">
+        <v>32623466</v>
+      </c>
+      <c r="C859" t="str">
+        <v>土家族咔咔饼</v>
+      </c>
+      <c r="D859" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E859" t="str">
+        <v>肖锐</v>
+      </c>
+      <c r="F859" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G859" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B860" t="str">
+        <v>1338935338</v>
+      </c>
+      <c r="C860" t="str">
+        <v>土家族咔咔饼.蛋黄南瓜麻花</v>
+      </c>
+      <c r="D860" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E860" t="str">
+        <v>肖锐</v>
+      </c>
+      <c r="F860" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G860" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B861" t="str">
+        <v>542617733</v>
+      </c>
+      <c r="C861" t="str">
+        <v>金贝炸鸡</v>
+      </c>
+      <c r="D861" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E861" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F861" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G861" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B862" t="str">
+        <v>32827439</v>
+      </c>
+      <c r="C862" t="str">
+        <v>一品香烤鸭</v>
+      </c>
+      <c r="D862" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E862" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F862" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G862" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B863" t="str">
+        <v>20387399</v>
+      </c>
+      <c r="C863" t="str">
+        <v>有粉有面（洞口店）</v>
+      </c>
+      <c r="D863" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E863" t="str">
+        <v>张兴岚</v>
+      </c>
+      <c r="F863" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G863" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B864" t="str">
+        <v>32469486</v>
+      </c>
+      <c r="C864" t="str">
+        <v>船旗海鲜（东市店）</v>
+      </c>
+      <c r="D864" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E864" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F864" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G864" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B865" t="str">
+        <v>1341442986</v>
+      </c>
+      <c r="C865" t="str">
+        <v>味三鲜麻辣烫</v>
+      </c>
+      <c r="D865" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E865" t="str">
+        <v>赵春燕</v>
+      </c>
+      <c r="F865" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G865" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B866" t="str">
+        <v>543444984</v>
+      </c>
+      <c r="C866" t="str">
+        <v>叫啥龙虾</v>
+      </c>
+      <c r="D866" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E866" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F866" t="str">
+        <v>王涛</v>
+      </c>
+      <c r="G866" t="str">
+        <v>新店</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B867" t="str">
+        <v>32868243</v>
+      </c>
+      <c r="C867" t="str">
+        <v>叫啥龙虾</v>
+      </c>
+      <c r="D867" t="str">
+        <v>美团</v>
+      </c>
+      <c r="E867" t="str">
+        <v>周广鑫</v>
+      </c>
+      <c r="F867" t="str">
+        <v>王郡江</v>
+      </c>
+      <c r="G867" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G771"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G867"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -19963,7 +22287,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-26 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-04-30 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">

--- a/2026年3月开单店铺每日抽点与回款累计统计.xlsx
+++ b/2026年3月开单店铺每日抽点与回款累计统计.xlsx
@@ -427,7 +427,7 @@
         <v>统计截止日期</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-30</v>
+        <v>2026-05-03</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>起始日期后开单店铺总数</v>
       </c>
       <c r="B4">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>累计日报天数</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -451,7 +451,7 @@
         <v>累计回款总额</v>
       </c>
       <c r="B6">
-        <v>66881.19000000002</v>
+        <v>75265.95000000003</v>
       </c>
     </row>
     <row r="7">
@@ -459,7 +459,7 @@
         <v>累计抽点店铺次数</v>
       </c>
       <c r="B7">
-        <v>9348</v>
+        <v>10363</v>
       </c>
     </row>
     <row r="8">
@@ -467,7 +467,7 @@
         <v>导出时间</v>
       </c>
       <c r="B8" t="str">
-        <v>2026/5/1 10:15:51</v>
+        <v>2026/5/4 10:01:03</v>
       </c>
     </row>
   </sheetData>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -2272,34 +2272,121 @@
         <v>866</v>
       </c>
       <c r="D62">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E62">
-        <v>748</v>
+        <v>2582.2</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1598.74</v>
       </c>
       <c r="H62">
         <v>144</v>
       </c>
       <c r="I62">
-        <v>748</v>
+        <v>983.46</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>867</v>
+      </c>
+      <c r="D63">
+        <v>338</v>
+      </c>
+      <c r="E63">
+        <v>2844.14</v>
+      </c>
+      <c r="F63">
+        <v>206</v>
+      </c>
+      <c r="G63">
+        <v>1834.16</v>
+      </c>
+      <c r="H63">
+        <v>132</v>
+      </c>
+      <c r="I63">
+        <v>1009.98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>867</v>
+      </c>
+      <c r="D64">
+        <v>346</v>
+      </c>
+      <c r="E64">
+        <v>2987.21</v>
+      </c>
+      <c r="F64">
+        <v>200</v>
+      </c>
+      <c r="G64">
+        <v>1990.07</v>
+      </c>
+      <c r="H64">
+        <v>146</v>
+      </c>
+      <c r="I64">
+        <v>997.14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>867</v>
+      </c>
+      <c r="D65">
+        <v>130</v>
+      </c>
+      <c r="E65">
+        <v>719.21</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>130</v>
+      </c>
+      <c r="I65">
+        <v>719.21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I65"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G867"/>
+  <dimension ref="A1:G868"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2649,7 +2736,7 @@
         <v>韩大武</v>
       </c>
       <c r="F15" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G15" t="str">
         <v>正常</v>
@@ -2672,7 +2759,7 @@
         <v>韩大武</v>
       </c>
       <c r="F16" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G16" t="str">
         <v>正常</v>
@@ -2810,7 +2897,7 @@
         <v>梁智</v>
       </c>
       <c r="F22" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G22" t="str">
         <v>正常</v>
@@ -2902,7 +2989,7 @@
         <v>梁智</v>
       </c>
       <c r="F26" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G26" t="str">
         <v>正常</v>
@@ -3109,7 +3196,7 @@
         <v>向文强</v>
       </c>
       <c r="F35" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G35" t="str">
         <v>正常</v>
@@ -3155,7 +3242,7 @@
         <v>向文强</v>
       </c>
       <c r="F37" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G37" t="str">
         <v>无效店铺</v>
@@ -3181,7 +3268,7 @@
         <v>王清月</v>
       </c>
       <c r="G38" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="39">
@@ -3362,7 +3449,7 @@
         <v>朱雯雯</v>
       </c>
       <c r="F46" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G46" t="str">
         <v>正常</v>
@@ -3753,7 +3840,7 @@
         <v>屈维涛</v>
       </c>
       <c r="F63" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G63" t="str">
         <v>正常</v>
@@ -3802,7 +3889,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G65" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="66">
@@ -3822,7 +3909,7 @@
         <v>向文强</v>
       </c>
       <c r="F66" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G66" t="str">
         <v>已解约</v>
@@ -3986,7 +4073,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G73" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="74">
@@ -4101,7 +4188,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G78" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="79">
@@ -4167,7 +4254,7 @@
         <v>梁智</v>
       </c>
       <c r="F81" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G81" t="str">
         <v>无效店铺</v>
@@ -4469,7 +4556,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G94" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="95">
@@ -4742,7 +4829,7 @@
         <v>韩大武</v>
       </c>
       <c r="F106" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G106" t="str">
         <v>无效店铺</v>
@@ -4765,7 +4852,7 @@
         <v>梁智</v>
       </c>
       <c r="F107" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G107" t="str">
         <v>正常</v>
@@ -5110,7 +5197,7 @@
         <v>杨蓉</v>
       </c>
       <c r="F122" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G122" t="str">
         <v>无效店铺</v>
@@ -5432,7 +5519,7 @@
         <v>向文强</v>
       </c>
       <c r="F136" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G136" t="str">
         <v>已解约</v>
@@ -5570,7 +5657,7 @@
         <v>韩大武</v>
       </c>
       <c r="F142" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G142" t="str">
         <v>正常</v>
@@ -5961,7 +6048,7 @@
         <v>梁智</v>
       </c>
       <c r="F159" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G159" t="str">
         <v>已解约</v>
@@ -6007,7 +6094,7 @@
         <v>梁智</v>
       </c>
       <c r="F161" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G161" t="str">
         <v>已解约</v>
@@ -6191,7 +6278,7 @@
         <v>韩大武</v>
       </c>
       <c r="F169" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G169" t="str">
         <v>已解约</v>
@@ -6332,7 +6419,7 @@
         <v>王清月</v>
       </c>
       <c r="G175" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="176">
@@ -6375,7 +6462,7 @@
         <v>向文强</v>
       </c>
       <c r="F177" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G177" t="str">
         <v>正常</v>
@@ -6421,7 +6508,7 @@
         <v>韩大武</v>
       </c>
       <c r="F179" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G179" t="str">
         <v>无效店铺</v>
@@ -6858,7 +6945,7 @@
         <v>梁智</v>
       </c>
       <c r="F198" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G198" t="str">
         <v>无效店铺</v>
@@ -7042,7 +7129,7 @@
         <v>韩大武</v>
       </c>
       <c r="F206" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G206" t="str">
         <v>正常</v>
@@ -7068,7 +7155,7 @@
         <v>王涛</v>
       </c>
       <c r="G207" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="208">
@@ -7137,7 +7224,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G210" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="211">
@@ -7160,7 +7247,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G211" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="212">
@@ -7643,7 +7730,7 @@
         <v>王涛</v>
       </c>
       <c r="G232" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="233">
@@ -7709,7 +7796,7 @@
         <v>韩大武</v>
       </c>
       <c r="F235" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G235" t="str">
         <v>正常</v>
@@ -7778,10 +7865,10 @@
         <v>梁智</v>
       </c>
       <c r="F238" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G238" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="239">
@@ -8008,7 +8095,7 @@
         <v>韩大武</v>
       </c>
       <c r="F248" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G248" t="str">
         <v>正常</v>
@@ -8261,7 +8348,7 @@
         <v>李帅</v>
       </c>
       <c r="F259" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G259" t="str">
         <v>正常</v>
@@ -8284,7 +8371,7 @@
         <v>李帅</v>
       </c>
       <c r="F260" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G260" t="str">
         <v>已解约</v>
@@ -8330,10 +8417,10 @@
         <v>梁智</v>
       </c>
       <c r="F262" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G262" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="263">
@@ -8376,7 +8463,7 @@
         <v>梁智</v>
       </c>
       <c r="F264" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G264" t="str">
         <v>正常</v>
@@ -8540,7 +8627,7 @@
         <v>王清月</v>
       </c>
       <c r="G271" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="272">
@@ -8652,7 +8739,7 @@
         <v>韩大武</v>
       </c>
       <c r="F276" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G276" t="str">
         <v>无效店铺</v>
@@ -8678,7 +8765,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G277" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="278">
@@ -8954,7 +9041,7 @@
         <v>王郡江</v>
       </c>
       <c r="G289" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="290">
@@ -9138,7 +9225,7 @@
         <v>王清月</v>
       </c>
       <c r="G297" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="298">
@@ -9296,7 +9383,7 @@
         <v>梁智</v>
       </c>
       <c r="F304" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G304" t="str">
         <v>正常</v>
@@ -9480,7 +9567,7 @@
         <v>韩大武</v>
       </c>
       <c r="F312" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G312" t="str">
         <v>无效店铺</v>
@@ -9848,7 +9935,7 @@
         <v>梁智</v>
       </c>
       <c r="F328" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G328" t="str">
         <v>正常</v>
@@ -10101,7 +10188,7 @@
         <v>周广鑫</v>
       </c>
       <c r="F339" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G339" t="str">
         <v>正常</v>
@@ -10308,7 +10395,7 @@
         <v>梁智</v>
       </c>
       <c r="F348" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G348" t="str">
         <v>正常</v>
@@ -10377,7 +10464,7 @@
         <v>杨译博</v>
       </c>
       <c r="F351" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G351" t="str">
         <v>正常</v>
@@ -10472,7 +10559,7 @@
         <v>王涛</v>
       </c>
       <c r="G355" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="356">
@@ -10538,7 +10625,7 @@
         <v>赵春燕</v>
       </c>
       <c r="F358" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G358" t="str">
         <v>正常</v>
@@ -10610,7 +10697,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G361" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="362">
@@ -10725,7 +10812,7 @@
         <v>王清月</v>
       </c>
       <c r="G366" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="367">
@@ -11044,7 +11131,7 @@
         <v>梁智</v>
       </c>
       <c r="F380" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G380" t="str">
         <v>正常</v>
@@ -11067,7 +11154,7 @@
         <v>梁智</v>
       </c>
       <c r="F381" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G381" t="str">
         <v>正常</v>
@@ -11139,7 +11226,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G384" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="385">
@@ -11162,7 +11249,7 @@
         <v>王清月</v>
       </c>
       <c r="G385" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="386">
@@ -11987,7 +12074,7 @@
         <v>向文强</v>
       </c>
       <c r="F421" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G421" t="str">
         <v>正常</v>
@@ -12220,7 +12307,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G431" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="432">
@@ -12309,7 +12396,7 @@
         <v>梁智</v>
       </c>
       <c r="F435" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G435" t="str">
         <v>正常</v>
@@ -12519,7 +12606,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G444" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="445">
@@ -12680,7 +12767,7 @@
         <v>王涛</v>
       </c>
       <c r="G451" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="452">
@@ -12884,7 +12971,7 @@
         <v>韩大武</v>
       </c>
       <c r="F460" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G460" t="str">
         <v>正常</v>
@@ -13117,7 +13204,7 @@
         <v>王郡江</v>
       </c>
       <c r="G470" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="471">
@@ -13439,7 +13526,7 @@
         <v>王清月</v>
       </c>
       <c r="G484" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="485">
@@ -13692,7 +13779,7 @@
         <v>王涛</v>
       </c>
       <c r="G495" t="str">
-        <v>无效店铺</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="496">
@@ -13781,7 +13868,7 @@
         <v>梁智</v>
       </c>
       <c r="F499" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G499" t="str">
         <v>正常</v>
@@ -13853,7 +13940,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G502" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="503">
@@ -13945,7 +14032,7 @@
         <v>王涛</v>
       </c>
       <c r="G506" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="507">
@@ -14129,7 +14216,7 @@
         <v>王郡江</v>
       </c>
       <c r="G514" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="515">
@@ -14152,7 +14239,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G515" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="516">
@@ -14244,7 +14331,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G519" t="str">
-        <v>正常</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="520">
@@ -14359,7 +14446,7 @@
         <v>王郡江</v>
       </c>
       <c r="G524" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="525">
@@ -14471,7 +14558,7 @@
         <v>韩大武</v>
       </c>
       <c r="F529" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G529" t="str">
         <v>正常</v>
@@ -14750,7 +14837,7 @@
         <v>王涛</v>
       </c>
       <c r="G541" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="542">
@@ -14796,7 +14883,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G543" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="544">
@@ -15046,7 +15133,7 @@
         <v>叶文静</v>
       </c>
       <c r="F554" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G554" t="str">
         <v>正常</v>
@@ -15693,7 +15780,7 @@
         <v>王涛</v>
       </c>
       <c r="G582" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="583">
@@ -15759,7 +15846,7 @@
         <v>张兴岚</v>
       </c>
       <c r="F585" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G585" t="str">
         <v>已解约</v>
@@ -15900,7 +15987,7 @@
         <v>王清月</v>
       </c>
       <c r="G591" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="592">
@@ -16150,7 +16237,7 @@
         <v>向文强</v>
       </c>
       <c r="F602" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G602" t="str">
         <v>正常</v>
@@ -16337,7 +16424,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G610" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="611">
@@ -16587,7 +16674,7 @@
         <v>武力力</v>
       </c>
       <c r="F621" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G621" t="str">
         <v>正常</v>
@@ -16774,7 +16861,7 @@
         <v>王郡江</v>
       </c>
       <c r="G629" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="630">
@@ -17073,7 +17160,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G642" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="643">
@@ -17231,7 +17318,7 @@
         <v>向文强</v>
       </c>
       <c r="F649" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G649" t="str">
         <v>正常</v>
@@ -17602,7 +17689,7 @@
         <v>王清月</v>
       </c>
       <c r="G665" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="666">
@@ -17671,7 +17758,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G668" t="str">
-        <v>正常</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="669">
@@ -17737,7 +17824,7 @@
         <v>向文强</v>
       </c>
       <c r="F671" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G671" t="str">
         <v>正常</v>
@@ -17832,7 +17919,7 @@
         <v>王清月</v>
       </c>
       <c r="G675" t="str">
-        <v>无效店铺</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="676">
@@ -17875,7 +17962,7 @@
         <v>杨译博</v>
       </c>
       <c r="F677" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G677" t="str">
         <v>已解约</v>
@@ -17944,7 +18031,7 @@
         <v>叶文静</v>
       </c>
       <c r="F680" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G680" t="str">
         <v>已解约</v>
@@ -17970,7 +18057,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G681" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="682">
@@ -18062,7 +18149,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G685" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="686">
@@ -18085,7 +18172,7 @@
         <v>王涛</v>
       </c>
       <c r="G686" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="687">
@@ -18108,7 +18195,7 @@
         <v>王涛</v>
       </c>
       <c r="G687" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="688">
@@ -18154,7 +18241,7 @@
         <v>王清月</v>
       </c>
       <c r="G689" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="690">
@@ -18177,7 +18264,7 @@
         <v>王涛</v>
       </c>
       <c r="G690" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="691">
@@ -18197,7 +18284,7 @@
         <v>张兴岚</v>
       </c>
       <c r="F691" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G691" t="str">
         <v>正常</v>
@@ -18223,7 +18310,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G692" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="693">
@@ -18243,10 +18330,10 @@
         <v>赵春燕</v>
       </c>
       <c r="F693" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G693" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="694">
@@ -18269,7 +18356,7 @@
         <v>王清月</v>
       </c>
       <c r="G694" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="695">
@@ -18292,7 +18379,7 @@
         <v>王涛</v>
       </c>
       <c r="G695" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="696">
@@ -18315,7 +18402,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G696" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="697">
@@ -18338,7 +18425,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G697" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="698">
@@ -18361,7 +18448,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G698" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="699">
@@ -18384,7 +18471,7 @@
         <v>王涛</v>
       </c>
       <c r="G699" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="700">
@@ -18407,7 +18494,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G700" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="701">
@@ -18430,7 +18517,7 @@
         <v>王清月</v>
       </c>
       <c r="G701" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="702">
@@ -18473,10 +18560,10 @@
         <v>吴销</v>
       </c>
       <c r="F703" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G703" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="704">
@@ -18499,7 +18586,7 @@
         <v>王清月</v>
       </c>
       <c r="G704" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="705">
@@ -18522,7 +18609,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G705" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="706">
@@ -18545,7 +18632,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G706" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="707">
@@ -18568,7 +18655,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G707" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="708">
@@ -18588,10 +18675,10 @@
         <v>张兴岚</v>
       </c>
       <c r="F708" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G708" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="709">
@@ -18614,7 +18701,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G709" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="710">
@@ -18637,7 +18724,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G710" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="711">
@@ -18680,10 +18767,10 @@
         <v>韩大武</v>
       </c>
       <c r="F712" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G712" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="713">
@@ -18726,10 +18813,10 @@
         <v>柯松</v>
       </c>
       <c r="F714" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G714" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="715">
@@ -18752,7 +18839,7 @@
         <v>王清月</v>
       </c>
       <c r="G715" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="716">
@@ -18775,7 +18862,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G716" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="717">
@@ -18798,7 +18885,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G717" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="718">
@@ -18821,7 +18908,7 @@
         <v>王涛</v>
       </c>
       <c r="G718" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="719">
@@ -18841,10 +18928,10 @@
         <v>梁智</v>
       </c>
       <c r="F719" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G719" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="720">
@@ -18867,7 +18954,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G720" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="721">
@@ -18913,7 +19000,7 @@
         <v>王清月</v>
       </c>
       <c r="G722" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="723">
@@ -18936,7 +19023,7 @@
         <v>王涛</v>
       </c>
       <c r="G723" t="str">
-        <v>新店</v>
+        <v>无效店铺</v>
       </c>
     </row>
     <row r="724">
@@ -18982,7 +19069,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G725" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="726">
@@ -19005,7 +19092,7 @@
         <v>王涛</v>
       </c>
       <c r="G726" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="727">
@@ -19025,10 +19112,10 @@
         <v>武力力</v>
       </c>
       <c r="F727" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G727" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="728">
@@ -19048,10 +19135,10 @@
         <v>杨译博</v>
       </c>
       <c r="F728" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G728" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="729">
@@ -19074,7 +19161,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G729" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="730">
@@ -19097,7 +19184,7 @@
         <v>王涛</v>
       </c>
       <c r="G730" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="731">
@@ -19120,7 +19207,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G731" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="732">
@@ -19140,10 +19227,10 @@
         <v>杨译博</v>
       </c>
       <c r="F732" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G732" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="733">
@@ -19163,7 +19250,7 @@
         <v>张兴岚</v>
       </c>
       <c r="F733" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G733" t="str">
         <v>已解约</v>
@@ -19212,7 +19299,7 @@
         <v>王清月</v>
       </c>
       <c r="G735" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="736">
@@ -19235,7 +19322,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G736" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="737">
@@ -19258,7 +19345,7 @@
         <v>袁丽妮</v>
       </c>
       <c r="G737" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="738">
@@ -19278,7 +19365,7 @@
         <v>陈冉</v>
       </c>
       <c r="F738" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G738" t="str">
         <v>新店</v>
@@ -19304,7 +19391,7 @@
         <v>王清月</v>
       </c>
       <c r="G739" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="740">
@@ -19373,7 +19460,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G742" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="743">
@@ -19462,7 +19549,7 @@
         <v>梁智</v>
       </c>
       <c r="F746" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G746" t="str">
         <v>新店</v>
@@ -19531,7 +19618,7 @@
         <v>梁智</v>
       </c>
       <c r="F749" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G749" t="str">
         <v>已解约</v>
@@ -19557,7 +19644,7 @@
         <v>王清月</v>
       </c>
       <c r="G750" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="751">
@@ -19577,7 +19664,7 @@
         <v>吴销</v>
       </c>
       <c r="F751" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G751" t="str">
         <v>新店</v>
@@ -19626,7 +19713,7 @@
         <v>王清月</v>
       </c>
       <c r="G753" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="754">
@@ -19672,7 +19759,7 @@
         <v>杨有淇</v>
       </c>
       <c r="G755" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="756">
@@ -19692,7 +19779,7 @@
         <v>向文强</v>
       </c>
       <c r="F756" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G756" t="str">
         <v>新店</v>
@@ -19738,7 +19825,7 @@
         <v>杨译博</v>
       </c>
       <c r="F758" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G758" t="str">
         <v>已解约</v>
@@ -19764,7 +19851,7 @@
         <v>王清月</v>
       </c>
       <c r="G759" t="str">
-        <v>新店</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="760">
@@ -20051,7 +20138,7 @@
         <v>543027067</v>
       </c>
       <c r="C772" t="str">
-        <v>饿了么26/4.27虾掌门·龙虾馆 8%</v>
+        <v>虾掌门·龙虾馆</v>
       </c>
       <c r="D772" t="str">
         <v>饿了么</v>
@@ -20221,7 +20308,7 @@
         <v>向文强</v>
       </c>
       <c r="F779" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G779" t="str">
         <v>新店</v>
@@ -20267,7 +20354,7 @@
         <v>向文强</v>
       </c>
       <c r="F781" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G781" t="str">
         <v>新店</v>
@@ -20313,7 +20400,7 @@
         <v>向文强</v>
       </c>
       <c r="F783" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G783" t="str">
         <v>新店</v>
@@ -20405,7 +20492,7 @@
         <v>朱雯雯</v>
       </c>
       <c r="F787" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G787" t="str">
         <v>新店</v>
@@ -20465,7 +20552,7 @@
         <v>1315317237</v>
       </c>
       <c r="C790" t="str">
-        <v>香襄湘煲仔饭</v>
+        <v>香襄湘现炒盖饭</v>
       </c>
       <c r="D790" t="str">
         <v>饿了么</v>
@@ -20520,7 +20607,7 @@
         <v>韩大武</v>
       </c>
       <c r="F792" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G792" t="str">
         <v>新店</v>
@@ -20612,7 +20699,7 @@
         <v>梁智</v>
       </c>
       <c r="F796" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G796" t="str">
         <v>新店</v>
@@ -20750,7 +20837,7 @@
         <v>向文强</v>
       </c>
       <c r="F802" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G802" t="str">
         <v>新店</v>
@@ -20957,7 +21044,7 @@
         <v>赵春燕</v>
       </c>
       <c r="F811" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G811" t="str">
         <v>新店</v>
@@ -21325,7 +21412,7 @@
         <v>梁智</v>
       </c>
       <c r="F827" t="str">
-        <v>张玉莲</v>
+        <v>黄兆微</v>
       </c>
       <c r="G827" t="str">
         <v>新店</v>
@@ -21374,7 +21461,7 @@
         <v>王涛</v>
       </c>
       <c r="G829" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="830">
@@ -21788,7 +21875,7 @@
         <v>王郡江</v>
       </c>
       <c r="G847" t="str">
-        <v>新店</v>
+        <v>已解约</v>
       </c>
     </row>
     <row r="848">
@@ -22251,9 +22338,32 @@
         <v>新店</v>
       </c>
     </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="B868" t="str">
+        <v>1340939828</v>
+      </c>
+      <c r="C868" t="str">
+        <v>虾享美味小龙虾</v>
+      </c>
+      <c r="D868" t="str">
+        <v>饿了么</v>
+      </c>
+      <c r="E868" t="str">
+        <v>梁智</v>
+      </c>
+      <c r="F868" t="str">
+        <v>杨有淇</v>
+      </c>
+      <c r="G868" t="str">
+        <v>新店</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G867"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G868"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -22287,7 +22397,7 @@
         <v>开单店铺范围</v>
       </c>
       <c r="B3" t="str">
-        <v>统计 2026-03-01 到 2026-04-30 之间开单的全部店铺。</v>
+        <v>统计 2026-03-01 到 2026-05-03 之间开单的全部店铺。</v>
       </c>
     </row>
     <row r="4">
